--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$803</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$876</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.66 · 802 textos</t>
+          <t>Inventario generado de la versión de prueba 0.67 · 875 textos</t>
         </is>
       </c>
     </row>
@@ -761,23 +761,23 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A21)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A21)</f>
         <v/>
       </c>
       <c r="C21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A21,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A21,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A21,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A21,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A21,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A21,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A21,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A21,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A21,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A21,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -788,23 +788,23 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A22)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A22)</f>
         <v/>
       </c>
       <c r="C22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A22,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A22,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A22,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A22,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A22,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A22,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A22,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A22,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A22,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A22,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -815,23 +815,23 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A23)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A23)</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A23,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A23,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A23,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A23,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A23,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A23,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A23,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A23,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A23,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A23,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -842,23 +842,23 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A24)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A24)</f>
         <v/>
       </c>
       <c r="C24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A24,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A24,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A24,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A24,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A24,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A24,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A24,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A24,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A24,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A24,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -869,23 +869,23 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A25)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A25)</f>
         <v/>
       </c>
       <c r="C25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A25,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A25,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A25,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A25,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A25,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A25,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A25,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A25,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A25,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A25,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -896,23 +896,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A26)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A26)</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A26,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A26,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A26,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A26,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A26,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A26,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A26,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A26,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A26,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A26,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -923,23 +923,23 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A27)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A27)</f>
         <v/>
       </c>
       <c r="C27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A27,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A27,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A27,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A27,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A27,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A27,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A27,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A27,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A27,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A27,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -950,23 +950,23 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A28)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A28)</f>
         <v/>
       </c>
       <c r="C28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A28,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A28,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A28,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A28,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A28,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A28,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A28,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A28,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A28,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A28,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -977,23 +977,23 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A29)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A29)</f>
         <v/>
       </c>
       <c r="C29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A29,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A29,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A29,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A29,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A29,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A29,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A29,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A29,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A29,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A29,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A30)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A30)</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A30,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A30,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A30,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A30,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A30,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A30,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A30,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A30,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A30,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A30,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$803,A31)</f>
+        <f>COUNTIF(Textos!$B$2:$B$876,A31)</f>
         <v/>
       </c>
       <c r="C31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A31,Textos!$H$2:$H$803,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A31,Textos!$H$2:$H$876,"Pendiente")</f>
         <v/>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A31,Textos!$H$2:$H$803,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A31,Textos!$H$2:$H$876,"OK")</f>
         <v/>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A31,Textos!$H$2:$H$803,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A31,Textos!$H$2:$H$876,"Cambiar")</f>
         <v/>
       </c>
       <c r="F31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$803,A31,Textos!$H$2:$H$803,"Quitar")+COUNTIFS(Textos!$B$2:$B$803,A31,Textos!$H$2:$H$803,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$876,A31,Textos!$H$2:$H$876,"Quitar")+COUNTIFS(Textos!$B$2:$B$876,A31,Textos!$H$2:$H$876,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L803"/>
+  <dimension ref="A1:L876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -41180,12 +41180,12 @@
       </c>
       <c r="B801" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C801" s="15" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D801" s="15" t="inlineStr">
@@ -41195,12 +41195,12 @@
       </c>
       <c r="E801" s="15" t="inlineStr">
         <is>
-          <t>Al pedirla o al cargar el acta corregida</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F801" s="15" t="inlineStr">
         <is>
-          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="G801" s="13" t="inlineStr"/>
@@ -41213,12 +41213,12 @@
       <c r="J801" s="15" t="inlineStr"/>
       <c r="K801" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L801" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -41230,27 +41230,27 @@
       </c>
       <c r="B802" s="12" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C802" s="12" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D802" s="12" t="inlineStr">
         <is>
-          <t>Pasos</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E802" s="12" t="inlineStr">
         <is>
-          <t>Al pedirla</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F802" s="12" t="inlineStr">
         <is>
-          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
+          <t>Cargando los grupos…</t>
         </is>
       </c>
       <c r="G802" s="13" t="inlineStr"/>
@@ -41260,15 +41260,19 @@
         </is>
       </c>
       <c r="I802" s="13" t="inlineStr"/>
-      <c r="J802" s="12" t="inlineStr"/>
+      <c r="J802" s="17" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K802" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L802" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -41280,27 +41284,27 @@
       </c>
       <c r="B803" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C803" s="15" t="inlineStr">
         <is>
-          <t>Acreditación</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D803" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E803" s="15" t="inlineStr">
         <is>
-          <t>Credencial del sistema que todavía no se entrega</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F803" s="15" t="inlineStr">
         <is>
-          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
+          <t>Ver los grupos programados</t>
         </is>
       </c>
       <c r="G803" s="13" t="inlineStr"/>
@@ -41313,18 +41317,3668 @@
       <c r="J803" s="15" t="inlineStr"/>
       <c r="K803" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L803" s="16" t="inlineStr">
         <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="12" t="inlineStr">
+        <is>
+          <t>T803</t>
+        </is>
+      </c>
+      <c r="B804" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C804" s="12" t="inlineStr">
+        <is>
+          <t>Armar un grupo</t>
+        </is>
+      </c>
+      <c r="D804" s="12" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E804" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F804" s="12" t="inlineStr">
+        <is>
+          <t>Armar un grupo</t>
+        </is>
+      </c>
+      <c r="G804" s="13" t="inlineStr"/>
+      <c r="H804" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I804" s="13" t="inlineStr"/>
+      <c r="J804" s="12" t="inlineStr"/>
+      <c r="K804" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L804" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="15" t="inlineStr">
+        <is>
+          <t>T804</t>
+        </is>
+      </c>
+      <c r="B805" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C805" s="15" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D805" s="15" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E805" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F805" s="15" t="inlineStr">
+        <is>
+          <t>¿Para qué curso?</t>
+        </is>
+      </c>
+      <c r="G805" s="13" t="inlineStr"/>
+      <c r="H805" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I805" s="13" t="inlineStr"/>
+      <c r="J805" s="15" t="inlineStr"/>
+      <c r="K805" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L805" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="12" t="inlineStr">
+        <is>
+          <t>T805</t>
+        </is>
+      </c>
+      <c r="B806" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C806" s="12" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D806" s="12" t="inlineStr">
+        <is>
+          <t>Introducción</t>
+        </is>
+      </c>
+      <c r="E806" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F806" s="12" t="inlineStr">
+        <is>
+          <t>Cada curso arma sus grupos por separado: nunca se mezclan.</t>
+        </is>
+      </c>
+      <c r="G806" s="13" t="inlineStr"/>
+      <c r="H806" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I806" s="13" t="inlineStr"/>
+      <c r="J806" s="12" t="inlineStr"/>
+      <c r="K806" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L806" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="15" t="inlineStr">
+        <is>
+          <t>T806</t>
+        </is>
+      </c>
+      <c r="B807" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C807" s="15" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D807" s="15" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E807" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F807" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poda y derribo · nueva — </t>
+        </is>
+      </c>
+      <c r="G807" s="13" t="inlineStr"/>
+      <c r="H807" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I807" s="13" t="inlineStr"/>
+      <c r="J807" s="15" t="inlineStr"/>
+      <c r="K807" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L807" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="12" t="inlineStr">
+        <is>
+          <t>T807</t>
+        </is>
+      </c>
+      <c r="B808" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C808" s="12" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D808" s="12" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E808" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F808" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poda y derribo · renovación — </t>
+        </is>
+      </c>
+      <c r="G808" s="13" t="inlineStr"/>
+      <c r="H808" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I808" s="13" t="inlineStr"/>
+      <c r="J808" s="12" t="inlineStr"/>
+      <c r="K808" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L808" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="15" t="inlineStr">
+        <is>
+          <t>T808</t>
+        </is>
+      </c>
+      <c r="B809" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C809" s="15" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D809" s="15" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E809" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F809" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dictaminador técnico · nueva — </t>
+        </is>
+      </c>
+      <c r="G809" s="13" t="inlineStr"/>
+      <c r="H809" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I809" s="13" t="inlineStr"/>
+      <c r="J809" s="15" t="inlineStr"/>
+      <c r="K809" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L809" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="12" t="inlineStr">
+        <is>
+          <t>T809</t>
+        </is>
+      </c>
+      <c r="B810" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C810" s="12" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D810" s="12" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E810" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F810" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dictaminador técnico · renovación — </t>
+        </is>
+      </c>
+      <c r="G810" s="13" t="inlineStr"/>
+      <c r="H810" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I810" s="13" t="inlineStr"/>
+      <c r="J810" s="12" t="inlineStr"/>
+      <c r="K810" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L810" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="15" t="inlineStr">
+        <is>
+          <t>T810</t>
+        </is>
+      </c>
+      <c r="B811" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C811" s="15" t="inlineStr">
+        <is>
+          <t>El curso</t>
+        </is>
+      </c>
+      <c r="D811" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E811" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F811" s="15" t="inlineStr">
+        <is>
+          <t>Siguiente</t>
+        </is>
+      </c>
+      <c r="G811" s="13" t="inlineStr"/>
+      <c r="H811" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I811" s="13" t="inlineStr"/>
+      <c r="J811" s="15" t="inlineStr"/>
+      <c r="K811" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L811" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="12" t="inlineStr">
+        <is>
+          <t>T811</t>
+        </is>
+      </c>
+      <c r="B812" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C812" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D812" s="12" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E812" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F812" s="12" t="inlineStr">
+        <is>
+          <t>¿Qué semana?</t>
+        </is>
+      </c>
+      <c r="G812" s="13" t="inlineStr"/>
+      <c r="H812" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I812" s="13" t="inlineStr"/>
+      <c r="J812" s="12" t="inlineStr"/>
+      <c r="K812" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L812" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="15" t="inlineStr">
+        <is>
+          <t>T812</t>
+        </is>
+      </c>
+      <c r="B813" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C813" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D813" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E813" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F813" s="15" t="inlineStr">
+        <is>
+          <t>Semana elegida</t>
+        </is>
+      </c>
+      <c r="G813" s="13" t="inlineStr"/>
+      <c r="H813" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I813" s="13" t="inlineStr"/>
+      <c r="J813" s="15" t="inlineStr"/>
+      <c r="K813" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L813" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="12" t="inlineStr">
+        <is>
+          <t>T813</t>
+        </is>
+      </c>
+      <c r="B814" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C814" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D814" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E814" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F814" s="12" t="inlineStr">
+        <is>
+          <t>Ninguna todavía</t>
+        </is>
+      </c>
+      <c r="G814" s="13" t="inlineStr"/>
+      <c r="H814" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I814" s="13" t="inlineStr"/>
+      <c r="J814" s="12" t="inlineStr"/>
+      <c r="K814" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L814" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="15" t="inlineStr">
+        <is>
+          <t>T814</t>
+        </is>
+      </c>
+      <c r="B815" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C815" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D815" s="15" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
+        </is>
+      </c>
+      <c r="E815" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F815" s="15" t="inlineStr">
+        <is>
+          <t>Primer día del curso</t>
+        </is>
+      </c>
+      <c r="G815" s="13" t="inlineStr"/>
+      <c r="H815" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I815" s="13" t="inlineStr"/>
+      <c r="J815" s="15" t="inlineStr"/>
+      <c r="K815" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L815" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="12" t="inlineStr">
+        <is>
+          <t>T815</t>
+        </is>
+      </c>
+      <c r="B816" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C816" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D816" s="12" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E816" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F816" s="12" t="inlineStr">
+        <is>
+          <t>Se llena al elegir la semana en el calendario.</t>
+        </is>
+      </c>
+      <c r="G816" s="13" t="inlineStr"/>
+      <c r="H816" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I816" s="13" t="inlineStr"/>
+      <c r="J816" s="12" t="inlineStr"/>
+      <c r="K816" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L816" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="15" t="inlineStr">
+        <is>
+          <t>T816</t>
+        </is>
+      </c>
+      <c r="B817" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C817" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D817" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E817" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F817" s="15" t="inlineStr">
+        <is>
+          <t>Semana libre: toque «Libre» para elegirla</t>
+        </is>
+      </c>
+      <c r="G817" s="13" t="inlineStr"/>
+      <c r="H817" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I817" s="13" t="inlineStr"/>
+      <c r="J817" s="15" t="inlineStr"/>
+      <c r="K817" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L817" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="12" t="inlineStr">
+        <is>
+          <t>T817</t>
+        </is>
+      </c>
+      <c r="B818" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C818" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D818" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E818" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F818" s="12" t="inlineStr">
+        <is>
+          <t>El grupo nuevo</t>
+        </is>
+      </c>
+      <c r="G818" s="13" t="inlineStr"/>
+      <c r="H818" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I818" s="13" t="inlineStr"/>
+      <c r="J818" s="12" t="inlineStr"/>
+      <c r="K818" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L818" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="15" t="inlineStr">
+        <is>
+          <t>T818</t>
+        </is>
+      </c>
+      <c r="B819" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C819" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D819" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E819" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F819" s="15" t="inlineStr">
+        <is>
+          <t>Grupo por confirmar</t>
+        </is>
+      </c>
+      <c r="G819" s="13" t="inlineStr"/>
+      <c r="H819" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I819" s="13" t="inlineStr"/>
+      <c r="J819" s="15" t="inlineStr"/>
+      <c r="K819" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L819" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="12" t="inlineStr">
+        <is>
+          <t>T819</t>
+        </is>
+      </c>
+      <c r="B820" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C820" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D820" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E820" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F820" s="12" t="inlineStr">
+        <is>
+          <t>Grupo confirmado</t>
+        </is>
+      </c>
+      <c r="G820" s="13" t="inlineStr"/>
+      <c r="H820" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I820" s="13" t="inlineStr"/>
+      <c r="J820" s="12" t="inlineStr"/>
+      <c r="K820" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L820" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="15" t="inlineStr">
+        <is>
+          <t>T820</t>
+        </is>
+      </c>
+      <c r="B821" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C821" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D821" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E821" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F821" s="15" t="inlineStr">
+        <is>
+          <t>Grupo en curso</t>
+        </is>
+      </c>
+      <c r="G821" s="13" t="inlineStr"/>
+      <c r="H821" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I821" s="13" t="inlineStr"/>
+      <c r="J821" s="15" t="inlineStr"/>
+      <c r="K821" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L821" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="12" t="inlineStr">
+        <is>
+          <t>T821</t>
+        </is>
+      </c>
+      <c r="B822" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C822" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D822" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E822" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F822" s="12" t="inlineStr">
+        <is>
+          <t>Grupo que ya terminó</t>
+        </is>
+      </c>
+      <c r="G822" s="13" t="inlineStr"/>
+      <c r="H822" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I822" s="13" t="inlineStr"/>
+      <c r="J822" s="12" t="inlineStr"/>
+      <c r="K822" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L822" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="15" t="inlineStr">
+        <is>
+          <t>T822</t>
+        </is>
+      </c>
+      <c r="B823" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C823" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D823" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E823" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F823" s="15" t="inlineStr">
+        <is>
+          <t>Grupo de otro curso: también cuenta para el máximo</t>
+        </is>
+      </c>
+      <c r="G823" s="13" t="inlineStr"/>
+      <c r="H823" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I823" s="13" t="inlineStr"/>
+      <c r="J823" s="15" t="inlineStr"/>
+      <c r="K823" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L823" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="12" t="inlineStr">
+        <is>
+          <t>T823</t>
+        </is>
+      </c>
+      <c r="B824" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C824" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D824" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E824" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F824" s="12" t="inlineStr">
+        <is>
+          <t>No disponible: ya pasó, faltan menos de 7 días o ya hay 2 grupos</t>
+        </is>
+      </c>
+      <c r="G824" s="13" t="inlineStr"/>
+      <c r="H824" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I824" s="13" t="inlineStr"/>
+      <c r="J824" s="12" t="inlineStr"/>
+      <c r="K824" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L824" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="15" t="inlineStr">
+        <is>
+          <t>T824</t>
+        </is>
+      </c>
+      <c r="B825" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C825" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D825" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E825" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F825" s="15" t="inlineStr">
+        <is>
+          <t>Sábado y domingo: no hay curso</t>
+        </is>
+      </c>
+      <c r="G825" s="13" t="inlineStr"/>
+      <c r="H825" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I825" s="13" t="inlineStr"/>
+      <c r="J825" s="15" t="inlineStr"/>
+      <c r="K825" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L825" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="12" t="inlineStr">
+        <is>
+          <t>T825</t>
+        </is>
+      </c>
+      <c r="B826" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C826" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D826" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E826" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F826" s="12" t="inlineStr">
+        <is>
+          <t>Día inhábil [por confirmar con el calendario oficial de la Secretaría]</t>
+        </is>
+      </c>
+      <c r="G826" s="13" t="inlineStr"/>
+      <c r="H826" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I826" s="13" t="inlineStr"/>
+      <c r="J826" s="12" t="inlineStr"/>
+      <c r="K826" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L826" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="15" t="inlineStr">
+        <is>
+          <t>T826</t>
+        </is>
+      </c>
+      <c r="B827" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C827" s="15" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D827" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E827" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F827" s="15" t="inlineStr">
+        <is>
+          <t>Atrás</t>
+        </is>
+      </c>
+      <c r="G827" s="13" t="inlineStr"/>
+      <c r="H827" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I827" s="13" t="inlineStr"/>
+      <c r="J827" s="15" t="inlineStr"/>
+      <c r="K827" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L827" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="12" t="inlineStr">
+        <is>
+          <t>T827</t>
+        </is>
+      </c>
+      <c r="B828" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C828" s="12" t="inlineStr">
+        <is>
+          <t>La semana</t>
+        </is>
+      </c>
+      <c r="D828" s="12" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E828" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F828" s="12" t="inlineStr">
+        <is>
+          <t>Siguiente</t>
+        </is>
+      </c>
+      <c r="G828" s="13" t="inlineStr"/>
+      <c r="H828" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I828" s="13" t="inlineStr"/>
+      <c r="J828" s="12" t="inlineStr"/>
+      <c r="K828" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L828" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="15" t="inlineStr">
+        <is>
+          <t>T828</t>
+        </is>
+      </c>
+      <c r="B829" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C829" s="15" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D829" s="15" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E829" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F829" s="15" t="inlineStr">
+        <is>
+          <t>¿Quiénes van?</t>
+        </is>
+      </c>
+      <c r="G829" s="13" t="inlineStr"/>
+      <c r="H829" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I829" s="13" t="inlineStr"/>
+      <c r="J829" s="15" t="inlineStr"/>
+      <c r="K829" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L829" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="12" t="inlineStr">
+        <is>
+          <t>T829</t>
+        </is>
+      </c>
+      <c r="B830" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C830" s="12" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D830" s="12" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E830" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F830" s="12" t="inlineStr">
+        <is>
+          <t>Si hay más de 25, entran las que más esperan y las de una misma institución de gobierno van juntas; el resto sigue en espera para otra semana.</t>
+        </is>
+      </c>
+      <c r="G830" s="13" t="inlineStr"/>
+      <c r="H830" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I830" s="13" t="inlineStr"/>
+      <c r="J830" s="12" t="inlineStr"/>
+      <c r="K830" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L830" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="15" t="inlineStr">
+        <is>
+          <t>T830</t>
+        </is>
+      </c>
+      <c r="B831" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C831" s="15" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D831" s="15" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
+        </is>
+      </c>
+      <c r="E831" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F831" s="15" t="inlineStr">
+        <is>
+          <t>¿De quiénes es el grupo?</t>
+        </is>
+      </c>
+      <c r="G831" s="13" t="inlineStr"/>
+      <c r="H831" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I831" s="13" t="inlineStr"/>
+      <c r="J831" s="15" t="inlineStr"/>
+      <c r="K831" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L831" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="12" t="inlineStr">
+        <is>
+          <t>T831</t>
+        </is>
+      </c>
+      <c r="B832" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C832" s="12" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D832" s="12" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E832" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F832" s="12" t="inlineStr">
+        <is>
+          <t>Combinado — Recibe personas de cualquier organización e independientes.</t>
+        </is>
+      </c>
+      <c r="G832" s="13" t="inlineStr"/>
+      <c r="H832" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I832" s="13" t="inlineStr"/>
+      <c r="J832" s="12" t="inlineStr"/>
+      <c r="K832" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L832" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="15" t="inlineStr">
+        <is>
+          <t>T832</t>
+        </is>
+      </c>
+      <c r="B833" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C833" s="15" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D833" s="15" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="E833" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F833" s="15" t="inlineStr">
+        <is>
+          <t>Sólo de una organización — Recibe únicamente a la gente de esa organización: todas las elegidas tienen que ser de ella.</t>
+        </is>
+      </c>
+      <c r="G833" s="13" t="inlineStr"/>
+      <c r="H833" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I833" s="13" t="inlineStr"/>
+      <c r="J833" s="15" t="inlineStr"/>
+      <c r="K833" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L833" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="12" t="inlineStr">
+        <is>
+          <t>T833</t>
+        </is>
+      </c>
+      <c r="B834" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C834" s="12" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D834" s="12" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E834" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F834" s="12" t="inlineStr">
+        <is>
+          <t>Atrás</t>
+        </is>
+      </c>
+      <c r="G834" s="13" t="inlineStr"/>
+      <c r="H834" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I834" s="13" t="inlineStr"/>
+      <c r="J834" s="12" t="inlineStr"/>
+      <c r="K834" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L834" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="15" t="inlineStr">
+        <is>
+          <t>T834</t>
+        </is>
+      </c>
+      <c r="B835" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C835" s="15" t="inlineStr">
+        <is>
+          <t>Quiénes van</t>
+        </is>
+      </c>
+      <c r="D835" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E835" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F835" s="15" t="inlineStr">
+        <is>
+          <t>Siguiente</t>
+        </is>
+      </c>
+      <c r="G835" s="13" t="inlineStr"/>
+      <c r="H835" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I835" s="13" t="inlineStr"/>
+      <c r="J835" s="15" t="inlineStr"/>
+      <c r="K835" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L835" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="12" t="inlineStr">
+        <is>
+          <t>T835</t>
+        </is>
+      </c>
+      <c r="B836" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C836" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D836" s="12" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E836" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F836" s="12" t="inlineStr">
+        <is>
+          <t>Revise y confirme</t>
+        </is>
+      </c>
+      <c r="G836" s="13" t="inlineStr"/>
+      <c r="H836" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I836" s="13" t="inlineStr"/>
+      <c r="J836" s="12" t="inlineStr"/>
+      <c r="K836" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L836" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="15" t="inlineStr">
+        <is>
+          <t>T836</t>
+        </is>
+      </c>
+      <c r="B837" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C837" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D837" s="15" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
+        </is>
+      </c>
+      <c r="E837" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F837" s="15" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="G837" s="13" t="inlineStr"/>
+      <c r="H837" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I837" s="13" t="inlineStr"/>
+      <c r="J837" s="15" t="inlineStr"/>
+      <c r="K837" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L837" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="12" t="inlineStr">
+        <is>
+          <t>T837</t>
+        </is>
+      </c>
+      <c r="B838" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C838" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D838" s="12" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E838" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F838" s="12" t="inlineStr">
+        <is>
+          <t>Se indica si ya tiene otro curso esas fechas.</t>
+        </is>
+      </c>
+      <c r="G838" s="13" t="inlineStr"/>
+      <c r="H838" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I838" s="13" t="inlineStr"/>
+      <c r="J838" s="12" t="inlineStr"/>
+      <c r="K838" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L838" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="15" t="inlineStr">
+        <is>
+          <t>T838</t>
+        </is>
+      </c>
+      <c r="B839" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C839" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D839" s="15" t="inlineStr">
+        <is>
+          <t>Indicación de lista</t>
+        </is>
+      </c>
+      <c r="E839" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F839" s="15" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="G839" s="13" t="inlineStr"/>
+      <c r="H839" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I839" s="13" t="inlineStr"/>
+      <c r="J839" s="15" t="inlineStr"/>
+      <c r="K839" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L839" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="12" t="inlineStr">
+        <is>
+          <t>T839</t>
+        </is>
+      </c>
+      <c r="B840" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C840" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D840" s="12" t="inlineStr">
+        <is>
+          <t>Opción de lista</t>
+        </is>
+      </c>
+      <c r="E840" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F840" s="12" t="inlineStr">
+        <is>
+          <t>Laura Ejemplo Instructora</t>
+        </is>
+      </c>
+      <c r="G840" s="13" t="inlineStr"/>
+      <c r="H840" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I840" s="13" t="inlineStr"/>
+      <c r="J840" s="12" t="inlineStr"/>
+      <c r="K840" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L840" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="15" t="inlineStr">
+        <is>
+          <t>T840</t>
+        </is>
+      </c>
+      <c r="B841" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C841" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D841" s="15" t="inlineStr">
+        <is>
+          <t>Opción de lista</t>
+        </is>
+      </c>
+      <c r="E841" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F841" s="15" t="inlineStr">
+        <is>
+          <t>Instructor Ejemplo Dos</t>
+        </is>
+      </c>
+      <c r="G841" s="13" t="inlineStr"/>
+      <c r="H841" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I841" s="13" t="inlineStr"/>
+      <c r="J841" s="15" t="inlineStr"/>
+      <c r="K841" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L841" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="12" t="inlineStr">
+        <is>
+          <t>T841</t>
+        </is>
+      </c>
+      <c r="B842" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C842" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D842" s="12" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
+        </is>
+      </c>
+      <c r="E842" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F842" s="12" t="inlineStr">
+        <is>
+          <t>Hora de entrada</t>
+        </is>
+      </c>
+      <c r="G842" s="13" t="inlineStr"/>
+      <c r="H842" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I842" s="13" t="inlineStr"/>
+      <c r="J842" s="12" t="inlineStr"/>
+      <c r="K842" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L842" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="15" t="inlineStr">
+        <is>
+          <t>T842</t>
+        </is>
+      </c>
+      <c r="B843" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C843" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D843" s="15" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E843" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F843" s="15" t="inlineStr">
+        <is>
+          <t>El curso es de 9:00 a 15:00 todos sus días.</t>
+        </is>
+      </c>
+      <c r="G843" s="13" t="inlineStr"/>
+      <c r="H843" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I843" s="13" t="inlineStr"/>
+      <c r="J843" s="15" t="inlineStr"/>
+      <c r="K843" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L843" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="12" t="inlineStr">
+        <is>
+          <t>T843</t>
+        </is>
+      </c>
+      <c r="B844" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C844" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D844" s="12" t="inlineStr">
+        <is>
+          <t>Indicación de lista</t>
+        </is>
+      </c>
+      <c r="E844" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F844" s="12" t="inlineStr">
+        <is>
+          <t>Elija</t>
+        </is>
+      </c>
+      <c r="G844" s="13" t="inlineStr"/>
+      <c r="H844" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I844" s="13" t="inlineStr"/>
+      <c r="J844" s="12" t="inlineStr"/>
+      <c r="K844" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L844" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="15" t="inlineStr">
+        <is>
+          <t>T844</t>
+        </is>
+      </c>
+      <c r="B845" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C845" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D845" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E845" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F845" s="15" t="inlineStr">
+        <is>
+          <t>Atrás</t>
+        </is>
+      </c>
+      <c r="G845" s="13" t="inlineStr"/>
+      <c r="H845" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I845" s="13" t="inlineStr"/>
+      <c r="J845" s="15" t="inlineStr"/>
+      <c r="K845" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L845" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="12" t="inlineStr">
+        <is>
+          <t>T845</t>
+        </is>
+      </c>
+      <c r="B846" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C846" s="12" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D846" s="12" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E846" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F846" s="12" t="inlineStr">
+        <is>
+          <t>Crear sin confirmar</t>
+        </is>
+      </c>
+      <c r="G846" s="13" t="inlineStr"/>
+      <c r="H846" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I846" s="13" t="inlineStr"/>
+      <c r="J846" s="12" t="inlineStr"/>
+      <c r="K846" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L846" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="15" t="inlineStr">
+        <is>
+          <t>T846</t>
+        </is>
+      </c>
+      <c r="B847" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C847" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="D847" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E847" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F847" s="15" t="inlineStr">
+        <is>
+          <t>Crear el grupo</t>
+        </is>
+      </c>
+      <c r="G847" s="13" t="inlineStr"/>
+      <c r="H847" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I847" s="13" t="inlineStr"/>
+      <c r="J847" s="15" t="inlineStr"/>
+      <c r="K847" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L847" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="12" t="inlineStr">
+        <is>
+          <t>T847</t>
+        </is>
+      </c>
+      <c r="B848" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C848" s="12" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D848" s="12" t="inlineStr">
+        <is>
+          <t>Subtítulo</t>
+        </is>
+      </c>
+      <c r="E848" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F848" s="12" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="G848" s="13" t="inlineStr"/>
+      <c r="H848" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I848" s="13" t="inlineStr"/>
+      <c r="J848" s="12" t="inlineStr"/>
+      <c r="K848" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L848" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="15" t="inlineStr">
+        <is>
+          <t>T848</t>
+        </is>
+      </c>
+      <c r="B849" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C849" s="15" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D849" s="15" t="inlineStr">
+        <is>
+          <t>Introducción</t>
+        </is>
+      </c>
+      <c r="E849" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F849" s="15" t="inlineStr">
+        <is>
+          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta.</t>
+        </is>
+      </c>
+      <c r="G849" s="13" t="inlineStr"/>
+      <c r="H849" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I849" s="13" t="inlineStr"/>
+      <c r="J849" s="15" t="inlineStr"/>
+      <c r="K849" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L849" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="12" t="inlineStr">
+        <is>
+          <t>T849</t>
+        </is>
+      </c>
+      <c r="B850" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C850" s="12" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D850" s="12" t="inlineStr">
+        <is>
+          <t>Título desplegable</t>
+        </is>
+      </c>
+      <c r="E850" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F850" s="12" t="inlineStr">
+        <is>
+          <t>Grupos que ya terminaron</t>
+        </is>
+      </c>
+      <c r="G850" s="13" t="inlineStr"/>
+      <c r="H850" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I850" s="13" t="inlineStr"/>
+      <c r="J850" s="12" t="inlineStr"/>
+      <c r="K850" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L850" s="14" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="15" t="inlineStr">
+        <is>
+          <t>T850</t>
+        </is>
+      </c>
+      <c r="B851" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C851" s="15" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D851" s="15" t="inlineStr">
+        <is>
+          <t>Ayuda</t>
+        </is>
+      </c>
+      <c r="E851" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F851" s="15" t="inlineStr">
+        <is>
+          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas, hora de entrada e instructor, y recibe hasta 25. Pendiente (P92): quién arma los grupos (hoy, el perfil de revisión y cotejo) y quién asigna a los instructores.</t>
+        </is>
+      </c>
+      <c r="G851" s="13" t="inlineStr"/>
+      <c r="H851" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I851" s="13" t="inlineStr"/>
+      <c r="J851" s="15" t="inlineStr"/>
+      <c r="K851" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L851" s="16" t="inlineStr">
+        <is>
+          <t>Página (sitio/grupos.html)</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="12" t="inlineStr">
+        <is>
+          <t>T851</t>
+        </is>
+      </c>
+      <c r="B852" s="12" t="inlineStr">
+        <is>
+          <t>Reposición de tu credencial</t>
+        </is>
+      </c>
+      <c r="C852" s="12" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="D852" s="12" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="E852" s="12" t="inlineStr">
+        <is>
+          <t>Al pedirla o al cargar el acta corregida</t>
+        </is>
+      </c>
+      <c r="F852" s="12" t="inlineStr">
+        <is>
+          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
+        </is>
+      </c>
+      <c r="G852" s="13" t="inlineStr"/>
+      <c r="H852" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I852" s="13" t="inlineStr"/>
+      <c r="J852" s="12" t="inlineStr"/>
+      <c r="K852" s="14" t="inlineStr">
+        <is>
+          <t>Persona solicitante</t>
+        </is>
+      </c>
+      <c r="L852" s="14" t="inlineStr">
+        <is>
           <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
+    <row r="853">
+      <c r="A853" s="15" t="inlineStr">
+        <is>
+          <t>T852</t>
+        </is>
+      </c>
+      <c r="B853" s="15" t="inlineStr">
+        <is>
+          <t>Reposición de tu credencial</t>
+        </is>
+      </c>
+      <c r="C853" s="15" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="D853" s="15" t="inlineStr">
+        <is>
+          <t>Pasos</t>
+        </is>
+      </c>
+      <c r="E853" s="15" t="inlineStr">
+        <is>
+          <t>Al pedirla</t>
+        </is>
+      </c>
+      <c r="F853" s="15" t="inlineStr">
+        <is>
+          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
+        </is>
+      </c>
+      <c r="G853" s="13" t="inlineStr"/>
+      <c r="H853" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I853" s="13" t="inlineStr"/>
+      <c r="J853" s="15" t="inlineStr"/>
+      <c r="K853" s="16" t="inlineStr">
+        <is>
+          <t>Persona solicitante</t>
+        </is>
+      </c>
+      <c r="L853" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="12" t="inlineStr">
+        <is>
+          <t>T853</t>
+        </is>
+      </c>
+      <c r="B854" s="12" t="inlineStr">
+        <is>
+          <t>Reposición de tu credencial</t>
+        </is>
+      </c>
+      <c r="C854" s="12" t="inlineStr">
+        <is>
+          <t>Acreditación</t>
+        </is>
+      </c>
+      <c r="D854" s="12" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E854" s="12" t="inlineStr">
+        <is>
+          <t>Credencial del sistema que todavía no se entrega</t>
+        </is>
+      </c>
+      <c r="F854" s="12" t="inlineStr">
+        <is>
+          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
+        </is>
+      </c>
+      <c r="G854" s="13" t="inlineStr"/>
+      <c r="H854" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I854" s="13" t="inlineStr"/>
+      <c r="J854" s="12" t="inlineStr"/>
+      <c r="K854" s="14" t="inlineStr">
+        <is>
+          <t>Persona solicitante</t>
+        </is>
+      </c>
+      <c r="L854" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="15" t="inlineStr">
+        <is>
+          <t>T854</t>
+        </is>
+      </c>
+      <c r="B855" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C855" s="15" t="inlineStr">
+        <is>
+          <t>Cabecera</t>
+        </is>
+      </c>
+      <c r="D855" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E855" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F855" s="15" t="inlineStr">
+        <is>
+          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
+        </is>
+      </c>
+      <c r="G855" s="13" t="inlineStr"/>
+      <c r="H855" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I855" s="13" t="inlineStr"/>
+      <c r="J855" s="15" t="inlineStr"/>
+      <c r="K855" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L855" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="12" t="inlineStr">
+        <is>
+          <t>T855</t>
+        </is>
+      </c>
+      <c r="B856" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C856" s="12" t="inlineStr">
+        <is>
+          <t>Paso 1 · el curso</t>
+        </is>
+      </c>
+      <c r="D856" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E856" s="12" t="inlineStr">
+        <is>
+          <t>En cada curso</t>
+        </is>
+      </c>
+      <c r="F856" s="12" t="inlineStr">
+        <is>
+          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
+        </is>
+      </c>
+      <c r="G856" s="13" t="inlineStr"/>
+      <c r="H856" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I856" s="13" t="inlineStr"/>
+      <c r="J856" s="12" t="inlineStr"/>
+      <c r="K856" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L856" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="15" t="inlineStr">
+        <is>
+          <t>T856</t>
+        </is>
+      </c>
+      <c r="B857" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C857" s="15" t="inlineStr">
+        <is>
+          <t>Paso 2 · la semana</t>
+        </is>
+      </c>
+      <c r="D857" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E857" s="15" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F857" s="15" t="inlineStr">
+        <is>
+          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
+        </is>
+      </c>
+      <c r="G857" s="13" t="inlineStr"/>
+      <c r="H857" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I857" s="13" t="inlineStr"/>
+      <c r="J857" s="15" t="inlineStr"/>
+      <c r="K857" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L857" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="12" t="inlineStr">
+        <is>
+          <t>T857</t>
+        </is>
+      </c>
+      <c r="B858" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C858" s="12" t="inlineStr">
+        <is>
+          <t>Paso 2 · columna «Semana»</t>
+        </is>
+      </c>
+      <c r="D858" s="12" t="inlineStr">
+        <is>
+          <t>Botón</t>
+        </is>
+      </c>
+      <c r="E858" s="12" t="inlineStr">
+        <is>
+          <t>Semana que se puede elegir</t>
+        </is>
+      </c>
+      <c r="F858" s="12" t="inlineStr">
+        <is>
+          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
+        </is>
+      </c>
+      <c r="G858" s="13" t="inlineStr"/>
+      <c r="H858" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I858" s="13" t="inlineStr"/>
+      <c r="J858" s="12" t="inlineStr"/>
+      <c r="K858" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L858" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="15" t="inlineStr">
+        <is>
+          <t>T858</t>
+        </is>
+      </c>
+      <c r="B859" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C859" s="15" t="inlineStr">
+        <is>
+          <t>Paso 2 · columna «Semana»</t>
+        </is>
+      </c>
+      <c r="D859" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E859" s="15" t="inlineStr">
+        <is>
+          <t>Semana que no se puede elegir</t>
+        </is>
+      </c>
+      <c r="F859" s="15" t="inlineStr">
+        <is>
+          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
+        </is>
+      </c>
+      <c r="G859" s="13" t="inlineStr"/>
+      <c r="H859" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I859" s="13" t="inlineStr"/>
+      <c r="J859" s="15" t="inlineStr"/>
+      <c r="K859" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L859" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="12" t="inlineStr">
+        <is>
+          <t>T859</t>
+        </is>
+      </c>
+      <c r="B860" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C860" s="12" t="inlineStr">
+        <is>
+          <t>Paso 2 · calendario</t>
+        </is>
+      </c>
+      <c r="D860" s="12" t="inlineStr">
+        <is>
+          <t>Etiqueta</t>
+        </is>
+      </c>
+      <c r="E860" s="12" t="inlineStr">
+        <is>
+          <t>En los días</t>
+        </is>
+      </c>
+      <c r="F860" s="12" t="inlineStr">
+        <is>
+          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
+        </is>
+      </c>
+      <c r="G860" s="13" t="inlineStr"/>
+      <c r="H860" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I860" s="13" t="inlineStr"/>
+      <c r="J860" s="12" t="inlineStr"/>
+      <c r="K860" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L860" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="15" t="inlineStr">
+        <is>
+          <t>T860</t>
+        </is>
+      </c>
+      <c r="B861" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C861" s="15" t="inlineStr">
+        <is>
+          <t>Paso 2 · semana elegida</t>
+        </is>
+      </c>
+      <c r="D861" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E861" s="15" t="inlineStr">
+        <is>
+          <t>Con una semana elegida</t>
+        </is>
+      </c>
+      <c r="F861" s="15" t="inlineStr">
+        <is>
+          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
+        </is>
+      </c>
+      <c r="G861" s="13" t="inlineStr"/>
+      <c r="H861" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I861" s="13" t="inlineStr"/>
+      <c r="J861" s="15" t="inlineStr"/>
+      <c r="K861" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L861" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="12" t="inlineStr">
+        <is>
+          <t>T861</t>
+        </is>
+      </c>
+      <c r="B862" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C862" s="12" t="inlineStr">
+        <is>
+          <t>Paso 2 · semana elegida</t>
+        </is>
+      </c>
+      <c r="D862" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E862" s="12" t="inlineStr">
+        <is>
+          <t>Sin semana</t>
+        </is>
+      </c>
+      <c r="F862" s="12" t="inlineStr">
+        <is>
+          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
+        </is>
+      </c>
+      <c r="G862" s="13" t="inlineStr"/>
+      <c r="H862" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I862" s="13" t="inlineStr"/>
+      <c r="J862" s="12" t="inlineStr"/>
+      <c r="K862" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L862" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="15" t="inlineStr">
+        <is>
+          <t>T862</t>
+        </is>
+      </c>
+      <c r="B863" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C863" s="15" t="inlineStr">
+        <is>
+          <t>Paso 2</t>
+        </is>
+      </c>
+      <c r="D863" s="15" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E863" s="15" t="inlineStr">
+        <is>
+          <t>Siguiente sin semana</t>
+        </is>
+      </c>
+      <c r="F863" s="15" t="inlineStr">
+        <is>
+          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
+        </is>
+      </c>
+      <c r="G863" s="13" t="inlineStr"/>
+      <c r="H863" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I863" s="13" t="inlineStr"/>
+      <c r="J863" s="15" t="inlineStr"/>
+      <c r="K863" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L863" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="12" t="inlineStr">
+        <is>
+          <t>T863</t>
+        </is>
+      </c>
+      <c r="B864" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C864" s="12" t="inlineStr">
+        <is>
+          <t>Paso 2</t>
+        </is>
+      </c>
+      <c r="D864" s="12" t="inlineStr">
+        <is>
+          <t>Aviso</t>
+        </is>
+      </c>
+      <c r="E864" s="12" t="inlineStr">
+        <is>
+          <t>Al tocar un día que no se puede</t>
+        </is>
+      </c>
+      <c r="F864" s="12" t="inlineStr">
+        <is>
+          <t>El DÍA no se puede: RAZÓN.</t>
+        </is>
+      </c>
+      <c r="G864" s="13" t="inlineStr"/>
+      <c r="H864" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I864" s="13" t="inlineStr"/>
+      <c r="J864" s="12" t="inlineStr"/>
+      <c r="K864" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L864" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="15" t="inlineStr">
+        <is>
+          <t>T864</t>
+        </is>
+      </c>
+      <c r="B865" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C865" s="15" t="inlineStr">
+        <is>
+          <t>Paso 3 · quiénes van</t>
+        </is>
+      </c>
+      <c r="D865" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E865" s="15" t="inlineStr">
+        <is>
+          <t>Grupo nuevo</t>
+        </is>
+      </c>
+      <c r="F865" s="15" t="inlineStr">
+        <is>
+          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
+        </is>
+      </c>
+      <c r="G865" s="13" t="inlineStr"/>
+      <c r="H865" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I865" s="13" t="inlineStr"/>
+      <c r="J865" s="15" t="inlineStr"/>
+      <c r="K865" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L865" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="12" t="inlineStr">
+        <is>
+          <t>T865</t>
+        </is>
+      </c>
+      <c r="B866" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C866" s="12" t="inlineStr">
+        <is>
+          <t>Paso 3 · quiénes van</t>
+        </is>
+      </c>
+      <c r="D866" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E866" s="12" t="inlineStr">
+        <is>
+          <t>Siempre</t>
+        </is>
+      </c>
+      <c r="F866" s="12" t="inlineStr">
+        <is>
+          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
+        </is>
+      </c>
+      <c r="G866" s="13" t="inlineStr"/>
+      <c r="H866" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I866" s="13" t="inlineStr"/>
+      <c r="J866" s="12" t="inlineStr"/>
+      <c r="K866" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L866" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="15" t="inlineStr">
+        <is>
+          <t>T866</t>
+        </is>
+      </c>
+      <c r="B867" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C867" s="15" t="inlineStr">
+        <is>
+          <t>Paso 3 · quiénes van</t>
+        </is>
+      </c>
+      <c r="D867" s="15" t="inlineStr">
+        <is>
+          <t>Plegable</t>
+        </is>
+      </c>
+      <c r="E867" s="15" t="inlineStr">
+        <is>
+          <t>Con más en espera que las propuestas</t>
+        </is>
+      </c>
+      <c r="F867" s="15" t="inlineStr">
+        <is>
+          <t>Cambiar a quiénes van (N más en espera)</t>
+        </is>
+      </c>
+      <c r="G867" s="13" t="inlineStr"/>
+      <c r="H867" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I867" s="13" t="inlineStr"/>
+      <c r="J867" s="15" t="inlineStr"/>
+      <c r="K867" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L867" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="12" t="inlineStr">
+        <is>
+          <t>T867</t>
+        </is>
+      </c>
+      <c r="B868" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C868" s="12" t="inlineStr">
+        <is>
+          <t>Paso 3</t>
+        </is>
+      </c>
+      <c r="D868" s="12" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E868" s="12" t="inlineStr">
+        <is>
+          <t>Siguiente sin nadie</t>
+        </is>
+      </c>
+      <c r="F868" s="12" t="inlineStr">
+        <is>
+          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
+        </is>
+      </c>
+      <c r="G868" s="13" t="inlineStr"/>
+      <c r="H868" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I868" s="13" t="inlineStr"/>
+      <c r="J868" s="12" t="inlineStr"/>
+      <c r="K868" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L868" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="15" t="inlineStr">
+        <is>
+          <t>T868</t>
+        </is>
+      </c>
+      <c r="B869" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C869" s="15" t="inlineStr">
+        <is>
+          <t>Paso 4 · confirmar</t>
+        </is>
+      </c>
+      <c r="D869" s="15" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E869" s="15" t="inlineStr">
+        <is>
+          <t>Antes de crearlo</t>
+        </is>
+      </c>
+      <c r="F869" s="15" t="inlineStr">
+        <is>
+          <t>Se crea confirmado · Cada persona verá en «Mis trámites» la fecha, la hora y el lugar. / Se crea por confirmar · Para confirmarlo le falta …</t>
+        </is>
+      </c>
+      <c r="G869" s="13" t="inlineStr"/>
+      <c r="H869" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I869" s="13" t="inlineStr"/>
+      <c r="J869" s="15" t="inlineStr"/>
+      <c r="K869" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L869" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="12" t="inlineStr">
+        <is>
+          <t>T869</t>
+        </is>
+      </c>
+      <c r="B870" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C870" s="12" t="inlineStr">
+        <is>
+          <t>Paso 4 · confirmar</t>
+        </is>
+      </c>
+      <c r="D870" s="12" t="inlineStr">
+        <is>
+          <t>Botón</t>
+        </is>
+      </c>
+      <c r="E870" s="12" t="inlineStr">
+        <is>
+          <t>Grupo nuevo</t>
+        </is>
+      </c>
+      <c r="F870" s="12" t="inlineStr">
+        <is>
+          <t>Crear el grupo · Crear sin confirmar (sólo si podría confirmarse)</t>
+        </is>
+      </c>
+      <c r="G870" s="13" t="inlineStr"/>
+      <c r="H870" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I870" s="13" t="inlineStr"/>
+      <c r="J870" s="12" t="inlineStr"/>
+      <c r="K870" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L870" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="15" t="inlineStr">
+        <is>
+          <t>T870</t>
+        </is>
+      </c>
+      <c r="B871" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C871" s="15" t="inlineStr">
+        <is>
+          <t>Paso 4 · confirmar</t>
+        </is>
+      </c>
+      <c r="D871" s="15" t="inlineStr">
+        <is>
+          <t>Botón</t>
+        </is>
+      </c>
+      <c r="E871" s="15" t="inlineStr">
+        <is>
+          <t>Grupo que ya existe</t>
+        </is>
+      </c>
+      <c r="F871" s="15" t="inlineStr">
+        <is>
+          <t>Confirmar el grupo / Guardar los cambios / Guardar sin confirmar / Agregar al grupo (confirmado)</t>
+        </is>
+      </c>
+      <c r="G871" s="13" t="inlineStr"/>
+      <c r="H871" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I871" s="13" t="inlineStr"/>
+      <c r="J871" s="15" t="inlineStr"/>
+      <c r="K871" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L871" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="12" t="inlineStr">
+        <is>
+          <t>T871</t>
+        </is>
+      </c>
+      <c r="B872" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C872" s="12" t="inlineStr">
+        <is>
+          <t>Paso 4 · instructor</t>
+        </is>
+      </c>
+      <c r="D872" s="12" t="inlineStr">
+        <is>
+          <t>Ayuda (cambia)</t>
+        </is>
+      </c>
+      <c r="E872" s="12" t="inlineStr">
+        <is>
+          <t>Instructor «Por asignar»</t>
+        </is>
+      </c>
+      <c r="F872" s="12" t="inlineStr">
+        <is>
+          <t>Por asignar: el grupo se crea, pero no se confirma sin instructor. La asignación de instructores la hará el área de capacitación (pendiente P92).</t>
+        </is>
+      </c>
+      <c r="G872" s="13" t="inlineStr"/>
+      <c r="H872" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I872" s="13" t="inlineStr"/>
+      <c r="J872" s="12" t="inlineStr"/>
+      <c r="K872" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L872" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="15" t="inlineStr">
+        <is>
+          <t>T872</t>
+        </is>
+      </c>
+      <c r="B873" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C873" s="15" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D873" s="15" t="inlineStr">
+        <is>
+          <t>Aviso</t>
+        </is>
+      </c>
+      <c r="E873" s="15" t="inlineStr">
+        <is>
+          <t>Al crear un grupo</t>
+        </is>
+      </c>
+      <c r="F873" s="15" t="inlineStr">
+        <is>
+          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
+        </is>
+      </c>
+      <c r="G873" s="13" t="inlineStr"/>
+      <c r="H873" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I873" s="13" t="inlineStr"/>
+      <c r="J873" s="15" t="inlineStr"/>
+      <c r="K873" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L873" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="12" t="inlineStr">
+        <is>
+          <t>T873</t>
+        </is>
+      </c>
+      <c r="B874" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C874" s="12" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D874" s="12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E874" s="12" t="inlineStr">
+        <is>
+          <t>Situación de cada grupo</t>
+        </is>
+      </c>
+      <c r="F874" s="12" t="inlineStr">
+        <is>
+          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
+        </is>
+      </c>
+      <c r="G874" s="13" t="inlineStr"/>
+      <c r="H874" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I874" s="13" t="inlineStr"/>
+      <c r="J874" s="12" t="inlineStr"/>
+      <c r="K874" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L874" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="15" t="inlineStr">
+        <is>
+          <t>T874</t>
+        </is>
+      </c>
+      <c r="B875" s="15" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C875" s="15" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D875" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E875" s="15" t="inlineStr">
+        <is>
+          <t>Acciones de cada grupo</t>
+        </is>
+      </c>
+      <c r="F875" s="15" t="inlineStr">
+        <is>
+          <t>Completar con las N que más esperan · Confirmar el grupo · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
+        </is>
+      </c>
+      <c r="G875" s="13" t="inlineStr"/>
+      <c r="H875" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I875" s="13" t="inlineStr"/>
+      <c r="J875" s="15" t="inlineStr"/>
+      <c r="K875" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L875" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="12" t="inlineStr">
+        <is>
+          <t>T875</t>
+        </is>
+      </c>
+      <c r="B876" s="12" t="inlineStr">
+        <is>
+          <t>Grupos (personal)</t>
+        </is>
+      </c>
+      <c r="C876" s="12" t="inlineStr">
+        <is>
+          <t>Grupos programados</t>
+        </is>
+      </c>
+      <c r="D876" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E876" s="12" t="inlineStr">
+        <is>
+          <t>Lo que falta</t>
+        </is>
+      </c>
+      <c r="F876" s="12" t="inlineStr">
+        <is>
+          <t>Semana, N personas, hora e instructor / Confirmarlo / —</t>
+        </is>
+      </c>
+      <c r="G876" s="13" t="inlineStr"/>
+      <c r="H876" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I876" s="13" t="inlineStr"/>
+      <c r="J876" s="12" t="inlineStr"/>
+      <c r="K876" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L876" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L803"/>
-  <conditionalFormatting sqref="H2:H803">
+  <autoFilter ref="A1:L876"/>
+  <conditionalFormatting sqref="H2:H876">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -41338,13 +44992,13 @@
       <formula>"Duda"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G803">
+  <conditionalFormatting sqref="G2:G876">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(LEN(G2)&gt;0,H2="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
+    <dataValidation sqref="H2:H876" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
       <formula1>"Pendiente,OK,Cambiar,Quitar,Duda"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$886</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$883</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.67 · 885 textos</t>
+          <t>Inventario generado de la versión de prueba 0.68 · 882 textos</t>
         </is>
       </c>
     </row>
@@ -761,23 +761,23 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A21)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A21)</f>
         <v/>
       </c>
       <c r="C21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A21,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A21,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A21,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A21,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A21,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A21,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A21,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A21,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A21,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A21,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -788,23 +788,23 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A22)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A22)</f>
         <v/>
       </c>
       <c r="C22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A22,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A22,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A22,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A22,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A22,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A22,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A22,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A22,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A22,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A22,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -815,23 +815,23 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A23)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A23)</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A23,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A23,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A23,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A23,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A23,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A23,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A23,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A23,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A23,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A23,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -842,23 +842,23 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A24)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A24)</f>
         <v/>
       </c>
       <c r="C24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A24,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A24,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A24,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A24,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A24,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A24,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A24,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A24,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A24,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A24,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -869,23 +869,23 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A25)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A25)</f>
         <v/>
       </c>
       <c r="C25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A25,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A25,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A25,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A25,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A25,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A25,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A25,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A25,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A25,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A25,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -896,23 +896,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A26)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A26)</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A26,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A26,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A26,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A26,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A26,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A26,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A26,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A26,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A26,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A26,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -923,23 +923,23 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A27)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A27)</f>
         <v/>
       </c>
       <c r="C27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A27,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A27,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A27,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A27,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A27,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A27,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A27,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A27,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A27,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A27,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -950,23 +950,23 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A28)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A28)</f>
         <v/>
       </c>
       <c r="C28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A28,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A28,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A28,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A28,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A28,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A28,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A28,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A28,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A28,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A28,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -977,23 +977,23 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A29)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A29)</f>
         <v/>
       </c>
       <c r="C29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A29,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A29,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A29,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A29,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A29,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A29,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A29,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A29,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A29,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A29,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A30)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A30)</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A30,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A30,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A30,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A30,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A30,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A30,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A30,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A30,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A30,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A30,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$886,A31)</f>
+        <f>COUNTIF(Textos!$B$2:$B$883,A31)</f>
         <v/>
       </c>
       <c r="C31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A31,Textos!$H$2:$H$886,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A31,Textos!$H$2:$H$883,"Pendiente")</f>
         <v/>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A31,Textos!$H$2:$H$886,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A31,Textos!$H$2:$H$883,"OK")</f>
         <v/>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A31,Textos!$H$2:$H$886,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A31,Textos!$H$2:$H$883,"Cambiar")</f>
         <v/>
       </c>
       <c r="F31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$886,A31,Textos!$H$2:$H$886,"Quitar")+COUNTIFS(Textos!$B$2:$B$886,A31,Textos!$H$2:$H$886,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$883,A31,Textos!$H$2:$H$883,"Quitar")+COUNTIFS(Textos!$B$2:$B$883,A31,Textos!$H$2:$H$883,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L886"/>
+  <dimension ref="A1:L883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -43744,7 +43744,7 @@
       </c>
       <c r="D852" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E852" s="12" t="inlineStr">
@@ -43754,7 +43754,7 @@
       </c>
       <c r="F852" s="12" t="inlineStr">
         <is>
-          <t>Hora de entrada</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G852" s="13" t="inlineStr"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="D853" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E853" s="15" t="inlineStr">
@@ -43804,7 +43804,7 @@
       </c>
       <c r="F853" s="15" t="inlineStr">
         <is>
-          <t>El curso es de 9:00 a 15:00 todos sus días.</t>
+          <t>Crear sin confirmar</t>
         </is>
       </c>
       <c r="G853" s="13" t="inlineStr"/>
@@ -43844,7 +43844,7 @@
       </c>
       <c r="D854" s="12" t="inlineStr">
         <is>
-          <t>Indicación de lista</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E854" s="12" t="inlineStr">
@@ -43854,7 +43854,7 @@
       </c>
       <c r="F854" s="12" t="inlineStr">
         <is>
-          <t>Elija</t>
+          <t>Crear el grupo</t>
         </is>
       </c>
       <c r="G854" s="13" t="inlineStr"/>
@@ -43889,12 +43889,12 @@
       </c>
       <c r="C855" s="15" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D855" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E855" s="15" t="inlineStr">
@@ -43904,7 +43904,7 @@
       </c>
       <c r="F855" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="G855" s="13" t="inlineStr"/>
@@ -43939,12 +43939,12 @@
       </c>
       <c r="C856" s="12" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D856" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E856" s="12" t="inlineStr">
@@ -43954,7 +43954,7 @@
       </c>
       <c r="F856" s="12" t="inlineStr">
         <is>
-          <t>Crear sin confirmar</t>
+          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta.</t>
         </is>
       </c>
       <c r="G856" s="13" t="inlineStr"/>
@@ -43989,12 +43989,12 @@
       </c>
       <c r="C857" s="15" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D857" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Título desplegable</t>
         </is>
       </c>
       <c r="E857" s="15" t="inlineStr">
@@ -44004,7 +44004,7 @@
       </c>
       <c r="F857" s="15" t="inlineStr">
         <is>
-          <t>Crear el grupo</t>
+          <t>Grupos que ya terminaron</t>
         </is>
       </c>
       <c r="G857" s="13" t="inlineStr"/>
@@ -44044,7 +44044,7 @@
       </c>
       <c r="D858" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E858" s="12" t="inlineStr">
@@ -44054,7 +44054,7 @@
       </c>
       <c r="F858" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas e instructor, y recibe hasta 25. Pendiente (P92): quién arma los grupos (hoy, el perfil de revisión y cotejo) y quién asigna a los instructores.</t>
         </is>
       </c>
       <c r="G858" s="13" t="inlineStr"/>
@@ -44084,27 +44084,27 @@
       </c>
       <c r="B859" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C859" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="D859" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E859" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Al pedirla o al cargar el acta corregida</t>
         </is>
       </c>
       <c r="F859" s="15" t="inlineStr">
         <is>
-          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta.</t>
+          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
         </is>
       </c>
       <c r="G859" s="13" t="inlineStr"/>
@@ -44117,12 +44117,12 @@
       <c r="J859" s="15" t="inlineStr"/>
       <c r="K859" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L859" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/grupos.html)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -44134,27 +44134,27 @@
       </c>
       <c r="B860" s="12" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C860" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="D860" s="12" t="inlineStr">
         <is>
-          <t>Título desplegable</t>
+          <t>Pasos</t>
         </is>
       </c>
       <c r="E860" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Al pedirla</t>
         </is>
       </c>
       <c r="F860" s="12" t="inlineStr">
         <is>
-          <t>Grupos que ya terminaron</t>
+          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
         </is>
       </c>
       <c r="G860" s="13" t="inlineStr"/>
@@ -44167,12 +44167,12 @@
       <c r="J860" s="12" t="inlineStr"/>
       <c r="K860" s="14" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L860" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/grupos.html)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -44184,27 +44184,27 @@
       </c>
       <c r="B861" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C861" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Acreditación</t>
         </is>
       </c>
       <c r="D861" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E861" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Credencial del sistema que todavía no se entrega</t>
         </is>
       </c>
       <c r="F861" s="15" t="inlineStr">
         <is>
-          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas, hora de entrada e instructor, y recibe hasta 25. Pendiente (P92): quién arma los grupos (hoy, el perfil de revisión y cotejo) y quién asigna a los instructores.</t>
+          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
         </is>
       </c>
       <c r="G861" s="13" t="inlineStr"/>
@@ -44217,12 +44217,12 @@
       <c r="J861" s="15" t="inlineStr"/>
       <c r="K861" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L861" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/grupos.html)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -44234,27 +44234,27 @@
       </c>
       <c r="B862" s="12" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C862" s="12" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Cabecera</t>
         </is>
       </c>
       <c r="D862" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E862" s="12" t="inlineStr">
         <is>
-          <t>Al pedirla o al cargar el acta corregida</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F862" s="12" t="inlineStr">
         <is>
-          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
+          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
         </is>
       </c>
       <c r="G862" s="13" t="inlineStr"/>
@@ -44267,12 +44267,12 @@
       <c r="J862" s="12" t="inlineStr"/>
       <c r="K862" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L862" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -44284,27 +44284,27 @@
       </c>
       <c r="B863" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C863" s="15" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Paso 1 · el curso</t>
         </is>
       </c>
       <c r="D863" s="15" t="inlineStr">
         <is>
-          <t>Pasos</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E863" s="15" t="inlineStr">
         <is>
-          <t>Al pedirla</t>
+          <t>En cada curso</t>
         </is>
       </c>
       <c r="F863" s="15" t="inlineStr">
         <is>
-          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
+          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
         </is>
       </c>
       <c r="G863" s="13" t="inlineStr"/>
@@ -44317,12 +44317,12 @@
       <c r="J863" s="15" t="inlineStr"/>
       <c r="K863" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L863" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -44334,27 +44334,27 @@
       </c>
       <c r="B864" s="12" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C864" s="12" t="inlineStr">
         <is>
-          <t>Acreditación</t>
+          <t>Paso 2 · la semana</t>
         </is>
       </c>
       <c r="D864" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E864" s="12" t="inlineStr">
         <is>
-          <t>Credencial del sistema que todavía no se entrega</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F864" s="12" t="inlineStr">
         <is>
-          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
+          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
         </is>
       </c>
       <c r="G864" s="13" t="inlineStr"/>
@@ -44367,12 +44367,12 @@
       <c r="J864" s="12" t="inlineStr"/>
       <c r="K864" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L864" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -44389,22 +44389,22 @@
       </c>
       <c r="C865" s="15" t="inlineStr">
         <is>
-          <t>Cabecera</t>
+          <t>Paso 2 · columna «Semana»</t>
         </is>
       </c>
       <c r="D865" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E865" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Semana que se puede elegir</t>
         </is>
       </c>
       <c r="F865" s="15" t="inlineStr">
         <is>
-          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
+          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
         </is>
       </c>
       <c r="G865" s="13" t="inlineStr"/>
@@ -44439,22 +44439,22 @@
       </c>
       <c r="C866" s="12" t="inlineStr">
         <is>
-          <t>Paso 1 · el curso</t>
+          <t>Paso 2 · columna «Semana»</t>
         </is>
       </c>
       <c r="D866" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E866" s="12" t="inlineStr">
         <is>
-          <t>En cada curso</t>
+          <t>Semana que no se puede elegir</t>
         </is>
       </c>
       <c r="F866" s="12" t="inlineStr">
         <is>
-          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
+          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
         </is>
       </c>
       <c r="G866" s="13" t="inlineStr"/>
@@ -44489,22 +44489,22 @@
       </c>
       <c r="C867" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · la semana</t>
+          <t>Paso 2 · calendario</t>
         </is>
       </c>
       <c r="D867" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Etiqueta</t>
         </is>
       </c>
       <c r="E867" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>En los días</t>
         </is>
       </c>
       <c r="F867" s="15" t="inlineStr">
         <is>
-          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
+          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
         </is>
       </c>
       <c r="G867" s="13" t="inlineStr"/>
@@ -44539,22 +44539,22 @@
       </c>
       <c r="C868" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · columna «Semana»</t>
+          <t>Paso 2 · semana elegida</t>
         </is>
       </c>
       <c r="D868" s="12" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E868" s="12" t="inlineStr">
         <is>
-          <t>Semana que se puede elegir</t>
+          <t>Con una semana elegida</t>
         </is>
       </c>
       <c r="F868" s="12" t="inlineStr">
         <is>
-          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
+          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
         </is>
       </c>
       <c r="G868" s="13" t="inlineStr"/>
@@ -44589,22 +44589,22 @@
       </c>
       <c r="C869" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · columna «Semana»</t>
+          <t>Paso 2 · semana elegida</t>
         </is>
       </c>
       <c r="D869" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E869" s="15" t="inlineStr">
         <is>
-          <t>Semana que no se puede elegir</t>
+          <t>Sin semana</t>
         </is>
       </c>
       <c r="F869" s="15" t="inlineStr">
         <is>
-          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
+          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
         </is>
       </c>
       <c r="G869" s="13" t="inlineStr"/>
@@ -44639,22 +44639,22 @@
       </c>
       <c r="C870" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · calendario</t>
+          <t>Paso 2</t>
         </is>
       </c>
       <c r="D870" s="12" t="inlineStr">
         <is>
-          <t>Etiqueta</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E870" s="12" t="inlineStr">
         <is>
-          <t>En los días</t>
+          <t>Siguiente sin semana</t>
         </is>
       </c>
       <c r="F870" s="12" t="inlineStr">
         <is>
-          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
+          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
         </is>
       </c>
       <c r="G870" s="13" t="inlineStr"/>
@@ -44689,22 +44689,22 @@
       </c>
       <c r="C871" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · semana elegida</t>
+          <t>Paso 2</t>
         </is>
       </c>
       <c r="D871" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E871" s="15" t="inlineStr">
         <is>
-          <t>Con una semana elegida</t>
+          <t>Al tocar un día que no se puede</t>
         </is>
       </c>
       <c r="F871" s="15" t="inlineStr">
         <is>
-          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
+          <t>El DÍA no se puede: RAZÓN.</t>
         </is>
       </c>
       <c r="G871" s="13" t="inlineStr"/>
@@ -44739,7 +44739,7 @@
       </c>
       <c r="C872" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · semana elegida</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D872" s="12" t="inlineStr">
@@ -44749,12 +44749,12 @@
       </c>
       <c r="E872" s="12" t="inlineStr">
         <is>
-          <t>Sin semana</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F872" s="12" t="inlineStr">
         <is>
-          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
+          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
         </is>
       </c>
       <c r="G872" s="13" t="inlineStr"/>
@@ -44789,22 +44789,22 @@
       </c>
       <c r="C873" s="15" t="inlineStr">
         <is>
-          <t>Paso 2</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D873" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E873" s="15" t="inlineStr">
         <is>
-          <t>Siguiente sin semana</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F873" s="15" t="inlineStr">
         <is>
-          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
+          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
         </is>
       </c>
       <c r="G873" s="13" t="inlineStr"/>
@@ -44839,22 +44839,22 @@
       </c>
       <c r="C874" s="12" t="inlineStr">
         <is>
-          <t>Paso 2</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D874" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Plegable</t>
         </is>
       </c>
       <c r="E874" s="12" t="inlineStr">
         <is>
-          <t>Al tocar un día que no se puede</t>
+          <t>Con más en espera que las propuestas</t>
         </is>
       </c>
       <c r="F874" s="12" t="inlineStr">
         <is>
-          <t>El DÍA no se puede: RAZÓN.</t>
+          <t>Cambiar a quiénes van (N más en espera)</t>
         </is>
       </c>
       <c r="G874" s="13" t="inlineStr"/>
@@ -44889,22 +44889,22 @@
       </c>
       <c r="C875" s="15" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 3</t>
         </is>
       </c>
       <c r="D875" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E875" s="15" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Siguiente sin nadie</t>
         </is>
       </c>
       <c r="F875" s="15" t="inlineStr">
         <is>
-          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
+          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
         </is>
       </c>
       <c r="G875" s="13" t="inlineStr"/>
@@ -44939,22 +44939,22 @@
       </c>
       <c r="C876" s="12" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D876" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E876" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Antes de crearlo</t>
         </is>
       </c>
       <c r="F876" s="12" t="inlineStr">
         <is>
-          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
+          <t>Se crea confirmado · Cada persona verá en «Mis trámites» la fecha, la hora y el lugar. / Se crea por confirmar · Para confirmarlo le falta …</t>
         </is>
       </c>
       <c r="G876" s="13" t="inlineStr"/>
@@ -44989,22 +44989,22 @@
       </c>
       <c r="C877" s="15" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D877" s="15" t="inlineStr">
         <is>
-          <t>Plegable</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E877" s="15" t="inlineStr">
         <is>
-          <t>Con más en espera que las propuestas</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F877" s="15" t="inlineStr">
         <is>
-          <t>Cambiar a quiénes van (N más en espera)</t>
+          <t>Crear el grupo · Crear sin confirmar (sólo si podría confirmarse)</t>
         </is>
       </c>
       <c r="G877" s="13" t="inlineStr"/>
@@ -45039,22 +45039,22 @@
       </c>
       <c r="C878" s="12" t="inlineStr">
         <is>
-          <t>Paso 3</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D878" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E878" s="12" t="inlineStr">
         <is>
-          <t>Siguiente sin nadie</t>
+          <t>Grupo que ya existe</t>
         </is>
       </c>
       <c r="F878" s="12" t="inlineStr">
         <is>
-          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
+          <t>Confirmar el grupo / Guardar los cambios / Guardar sin confirmar / Agregar al grupo (confirmado)</t>
         </is>
       </c>
       <c r="G878" s="13" t="inlineStr"/>
@@ -45089,22 +45089,22 @@
       </c>
       <c r="C879" s="15" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Paso 4 · instructor</t>
         </is>
       </c>
       <c r="D879" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Ayuda (cambia)</t>
         </is>
       </c>
       <c r="E879" s="15" t="inlineStr">
         <is>
-          <t>Antes de crearlo</t>
+          <t>Instructor «Por asignar»</t>
         </is>
       </c>
       <c r="F879" s="15" t="inlineStr">
         <is>
-          <t>Se crea confirmado · Cada persona verá en «Mis trámites» la fecha, la hora y el lugar. / Se crea por confirmar · Para confirmarlo le falta …</t>
+          <t>Por asignar: el grupo se crea, pero no se confirma sin instructor. La asignación de instructores la hará el área de capacitación (pendiente P92).</t>
         </is>
       </c>
       <c r="G879" s="13" t="inlineStr"/>
@@ -45139,22 +45139,22 @@
       </c>
       <c r="C880" s="12" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D880" s="12" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E880" s="12" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Al crear un grupo</t>
         </is>
       </c>
       <c r="F880" s="12" t="inlineStr">
         <is>
-          <t>Crear el grupo · Crear sin confirmar (sólo si podría confirmarse)</t>
+          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
         </is>
       </c>
       <c r="G880" s="13" t="inlineStr"/>
@@ -45189,22 +45189,22 @@
       </c>
       <c r="C881" s="15" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D881" s="15" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E881" s="15" t="inlineStr">
         <is>
-          <t>Grupo que ya existe</t>
+          <t>Situación de cada grupo</t>
         </is>
       </c>
       <c r="F881" s="15" t="inlineStr">
         <is>
-          <t>Confirmar el grupo / Guardar los cambios / Guardar sin confirmar / Agregar al grupo (confirmado)</t>
+          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
         </is>
       </c>
       <c r="G881" s="13" t="inlineStr"/>
@@ -45239,22 +45239,22 @@
       </c>
       <c r="C882" s="12" t="inlineStr">
         <is>
-          <t>Paso 4 · instructor</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D882" s="12" t="inlineStr">
         <is>
-          <t>Ayuda (cambia)</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E882" s="12" t="inlineStr">
         <is>
-          <t>Instructor «Por asignar»</t>
+          <t>Acciones de cada grupo</t>
         </is>
       </c>
       <c r="F882" s="12" t="inlineStr">
         <is>
-          <t>Por asignar: el grupo se crea, pero no se confirma sin instructor. La asignación de instructores la hará el área de capacitación (pendiente P92).</t>
+          <t>Completar con las N que más esperan · Confirmar el grupo · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
         </is>
       </c>
       <c r="G882" s="13" t="inlineStr"/>
@@ -45294,17 +45294,17 @@
       </c>
       <c r="D883" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E883" s="15" t="inlineStr">
         <is>
-          <t>Al crear un grupo</t>
+          <t>Lo que falta</t>
         </is>
       </c>
       <c r="F883" s="15" t="inlineStr">
         <is>
-          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
+          <t>Semana, N personas, hora e instructor / Confirmarlo / —</t>
         </is>
       </c>
       <c r="G883" s="13" t="inlineStr"/>
@@ -45326,159 +45326,9 @@
         </is>
       </c>
     </row>
-    <row r="884">
-      <c r="A884" s="12" t="inlineStr">
-        <is>
-          <t>T883</t>
-        </is>
-      </c>
-      <c r="B884" s="12" t="inlineStr">
-        <is>
-          <t>Grupos (personal)</t>
-        </is>
-      </c>
-      <c r="C884" s="12" t="inlineStr">
-        <is>
-          <t>Grupos programados</t>
-        </is>
-      </c>
-      <c r="D884" s="12" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E884" s="12" t="inlineStr">
-        <is>
-          <t>Situación de cada grupo</t>
-        </is>
-      </c>
-      <c r="F884" s="12" t="inlineStr">
-        <is>
-          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
-        </is>
-      </c>
-      <c r="G884" s="13" t="inlineStr"/>
-      <c r="H884" s="13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I884" s="13" t="inlineStr"/>
-      <c r="J884" s="12" t="inlineStr"/>
-      <c r="K884" s="14" t="inlineStr">
-        <is>
-          <t>Personal de la Secretaría</t>
-        </is>
-      </c>
-      <c r="L884" s="14" t="inlineStr">
-        <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" s="15" t="inlineStr">
-        <is>
-          <t>T884</t>
-        </is>
-      </c>
-      <c r="B885" s="15" t="inlineStr">
-        <is>
-          <t>Grupos (personal)</t>
-        </is>
-      </c>
-      <c r="C885" s="15" t="inlineStr">
-        <is>
-          <t>Grupos programados</t>
-        </is>
-      </c>
-      <c r="D885" s="15" t="inlineStr">
-        <is>
-          <t>Botón o enlace</t>
-        </is>
-      </c>
-      <c r="E885" s="15" t="inlineStr">
-        <is>
-          <t>Acciones de cada grupo</t>
-        </is>
-      </c>
-      <c r="F885" s="15" t="inlineStr">
-        <is>
-          <t>Completar con las N que más esperan · Confirmar el grupo · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
-        </is>
-      </c>
-      <c r="G885" s="13" t="inlineStr"/>
-      <c r="H885" s="13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I885" s="13" t="inlineStr"/>
-      <c r="J885" s="15" t="inlineStr"/>
-      <c r="K885" s="16" t="inlineStr">
-        <is>
-          <t>Personal de la Secretaría</t>
-        </is>
-      </c>
-      <c r="L885" s="16" t="inlineStr">
-        <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
-        </is>
-      </c>
-    </row>
-    <row r="886">
-      <c r="A886" s="12" t="inlineStr">
-        <is>
-          <t>T885</t>
-        </is>
-      </c>
-      <c r="B886" s="12" t="inlineStr">
-        <is>
-          <t>Grupos (personal)</t>
-        </is>
-      </c>
-      <c r="C886" s="12" t="inlineStr">
-        <is>
-          <t>Grupos programados</t>
-        </is>
-      </c>
-      <c r="D886" s="12" t="inlineStr">
-        <is>
-          <t>Texto</t>
-        </is>
-      </c>
-      <c r="E886" s="12" t="inlineStr">
-        <is>
-          <t>Lo que falta</t>
-        </is>
-      </c>
-      <c r="F886" s="12" t="inlineStr">
-        <is>
-          <t>Semana, N personas, hora e instructor / Confirmarlo / —</t>
-        </is>
-      </c>
-      <c r="G886" s="13" t="inlineStr"/>
-      <c r="H886" s="13" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I886" s="13" t="inlineStr"/>
-      <c r="J886" s="12" t="inlineStr"/>
-      <c r="K886" s="14" t="inlineStr">
-        <is>
-          <t>Personal de la Secretaría</t>
-        </is>
-      </c>
-      <c r="L886" s="14" t="inlineStr">
-        <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L886"/>
-  <conditionalFormatting sqref="H2:H886">
+  <autoFilter ref="A1:L883"/>
+  <conditionalFormatting sqref="H2:H883">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -45492,13 +45342,13 @@
       <formula>"Duda"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G886">
+  <conditionalFormatting sqref="G2:G883">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(LEN(G2)&gt;0,H2="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H886" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
+    <dataValidation sqref="H2:H883" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
       <formula1>"Pendiente,OK,Cambiar,Quitar,Duda"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.68 · 882 textos</t>
+          <t>Inventario generado de la versión de prueba 0.69 · 882 textos</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>Al escribir aparecen las ya registradas. Escribe la de tu posgrado (por ejemplo, Ciencias Forestales): cuenta aunque tu licenciatura sea de otra área.</t>
+          <t>Al escribir aparecen las ya registradas. Si la tuya no aparece, escríbela completa, como viene en tu título o cédula: la Secretaría la revisa. Escribe la de tu posgrado (por ejemplo, Ciencias Forestales): cuenta aunque tu licenciatura sea de otra área.</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$1003</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$1004</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.69 · 1002 textos</t>
+          <t>Inventario generado de la versión de prueba 0.69 · 1003 textos</t>
         </is>
       </c>
     </row>
@@ -761,23 +761,23 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A21)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A21)</f>
         <v/>
       </c>
       <c r="C21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A21,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A21,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A21,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A21,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A21,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -788,23 +788,23 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A22)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A22)</f>
         <v/>
       </c>
       <c r="C22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A22,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A22,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A22,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A22,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A22,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -815,23 +815,23 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A23)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A23)</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A23,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A23,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A23,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A23,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A23,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -842,23 +842,23 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A24)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A24)</f>
         <v/>
       </c>
       <c r="C24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A24,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A24,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A24,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A24,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A24,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -869,23 +869,23 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A25)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A25)</f>
         <v/>
       </c>
       <c r="C25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A25,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A25,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A25,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A25,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A25,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -896,23 +896,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A26)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A26)</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A26,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A26,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A26,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A26,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A26,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -923,23 +923,23 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A27)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A27)</f>
         <v/>
       </c>
       <c r="C27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A27,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A27,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A27,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A27,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A27,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -950,23 +950,23 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A28)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A28)</f>
         <v/>
       </c>
       <c r="C28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A28,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A28,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A28,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A28,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A28,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -977,23 +977,23 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A29)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A29)</f>
         <v/>
       </c>
       <c r="C29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A29,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A29,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A29,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A29,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A29,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A30)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A30)</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A30,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A30,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A30,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A30,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A30,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1003,A31)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1004,A31)</f>
         <v/>
       </c>
       <c r="C31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A31,Textos!$H$2:$H$1003,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Pendiente")</f>
         <v/>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A31,Textos!$H$2:$H$1003,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"OK")</f>
         <v/>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A31,Textos!$H$2:$H$1003,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Cambiar")</f>
         <v/>
       </c>
       <c r="F31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1003,A31,Textos!$H$2:$H$1003,"Quitar")+COUNTIFS(Textos!$B$2:$B$1003,A31,Textos!$H$2:$H$1003,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1003"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -50762,7 +50762,7 @@
       </c>
       <c r="F992" s="12" t="inlineStr">
         <is>
-          <t>Solicitud con observaciones · Cerrada por no corregir a tiempo · Cita de cotejo · Solicitud rechazada · Resultado de la cita de cotejo · Cuenta bloqueada por identidad · Grupo asignado · Cambio en su grupo · Resultado del examen · Acreditación entregada · Acreditación cancelada · Reposición de la credencial</t>
+          <t>Solicitud con observaciones · Cerrada por no corregir a tiempo · Cita de cotejo · Solicitud rechazada · Cerrada: sin más oportunidades de corrección · Resultado de la cita de cotejo · Cuenta bloqueada por identidad · Grupo asignado · Cambio en su grupo · Resultado del examen · Acreditación entregada · Acreditación cancelada · Reposición de la credencial</t>
         </is>
       </c>
       <c r="G992" s="13" t="inlineStr"/>
@@ -50812,7 +50812,7 @@
       </c>
       <c r="F993" s="15" t="inlineStr">
         <is>
-          <t>A tu solicitud FOLIO le falta corregir algo: DOCUMENTOS. Ven a la ventanilla del SEDE, HORARIO, para que te digamos qué falta y lo corrijamos contigo. Hay un plazo para corregir.</t>
+          <t>A tu solicitud FOLIO le falta corregir algo: DOCUMENTOS. Ven a la ventanilla del SEDE, HORARIO, para que te digamos qué falta y lo corrijamos contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. / Esta es tu última oportunidad para corregir. Si en la revisión siguen las observaciones, tu solicitud se cierra y tienes que iniciar una nueva.</t>
         </is>
       </c>
       <c r="G993" s="13" t="inlineStr"/>
@@ -50857,12 +50857,12 @@
       </c>
       <c r="E994" s="12" t="inlineStr">
         <is>
-          <t>Cita de cotejo</t>
+          <t>Cerrada al agotar las oportunidades de corrección</t>
         </is>
       </c>
       <c r="F994" s="12" t="inlineStr">
         <is>
-          <t>Tus documentos están completos. Tu cita de cotejo es el DÍA a las HH:MM, en el SEDE. Lleva los mismos documentos impresos, tu identificación oficial y el comprobante del pago de $MONTO con la referencia REFERENCIA.</t>
+          <t>Tu solicitud FOLIO se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva en la ventanilla del SEDE, HORARIO.</t>
         </is>
       </c>
       <c r="G994" s="13" t="inlineStr"/>
@@ -50907,12 +50907,12 @@
       </c>
       <c r="E995" s="15" t="inlineStr">
         <is>
-          <t>Resultado de la cita</t>
+          <t>Cita de cotejo</t>
         </is>
       </c>
       <c r="F995" s="15" t="inlineStr">
         <is>
-          <t>Tu cotejo terminó; tu expediente es el EXP-… / En tu cita faltó un documento: …; tráelo hoy mismo … / En tu cita, un documento no coincidió … / Como no llegaste a tu cita (o no llevaste el comprobante de pago), te dimos una cita nueva: … / Tu solicitud FOLIO se cerró porque no llegaste dos veces a tu cita de cotejo.</t>
+          <t>Tus documentos están completos. Tu cita de cotejo es el DÍA a las HH:MM, en el SEDE. Lleva los mismos documentos impresos, tu identificación oficial y el comprobante del pago de $MONTO con la referencia REFERENCIA.</t>
         </is>
       </c>
       <c r="G995" s="13" t="inlineStr"/>
@@ -50957,12 +50957,12 @@
       </c>
       <c r="E996" s="12" t="inlineStr">
         <is>
-          <t>Otros avisos</t>
+          <t>Resultado de la cita</t>
         </is>
       </c>
       <c r="F996" s="12" t="inlineStr">
         <is>
-          <t>Cerrada sin corregir · Rechazada (con el motivo) · Cuenta bloqueada · Grupo asignado (día, hora y sede) · Baja, cambio o grupo por confirmar · Resultado del examen · Acreditación entregada o cancelada · Reposición de la credencial</t>
+          <t>Tu cotejo terminó; tu expediente es el EXP-… / En tu cita faltó un documento: …; tráelo hoy mismo … / En tu cita, un documento no coincidió … / Como no llegaste a tu cita (o no llevaste el comprobante de pago), te dimos una cita nueva: … / Tu solicitud FOLIO se cerró porque no llegaste dos veces a tu cita de cotejo.</t>
         </is>
       </c>
       <c r="G996" s="13" t="inlineStr"/>
@@ -50997,22 +50997,22 @@
       </c>
       <c r="C997" s="15" t="inlineStr">
         <is>
-          <t>Al registrar</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D997" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E997" s="15" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Otros avisos</t>
         </is>
       </c>
       <c r="F997" s="15" t="inlineStr">
         <is>
-          <t>Se registró que se le avisó · NOMBRE: aviso hecho. / Se registró que no contestó · NOMBRE no contestó. Lo que se le iba a decir se le dice cuando vaya a la ventanilla. / Ya estaba registrado · Otra persona del personal ya registró el aviso de NOMBRE.</t>
+          <t>Cerrada sin corregir · Rechazada (con el motivo) · Cuenta bloqueada · Grupo asignado (día, hora y sede) · Baja, cambio o grupo por confirmar · Resultado del examen · Acreditación entregada o cancelada · Reposición de la credencial</t>
         </is>
       </c>
       <c r="G997" s="13" t="inlineStr"/>
@@ -51042,27 +51042,27 @@
       </c>
       <c r="B998" s="12" t="inlineStr">
         <is>
-          <t>Revisar una solicitud y Cita de cotejo (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C998" s="12" t="inlineStr">
         <is>
-          <t>Cabecera</t>
+          <t>Al registrar</t>
         </is>
       </c>
       <c r="D998" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E998" s="12" t="inlineStr">
         <is>
-          <t>Persona del registro asistido sin activar</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="F998" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido: avisar por teléfono, 55 1234 5678</t>
+          <t>Se registró que se le avisó · NOMBRE: aviso hecho. / Se registró que no contestó · NOMBRE no contestó. Lo que se le iba a decir se le dice cuando vaya a la ventanilla. / Ya estaba registrado · Otra persona del personal ya registró el aviso de NOMBRE.</t>
         </is>
       </c>
       <c r="G998" s="13" t="inlineStr"/>
@@ -51092,27 +51092,27 @@
       </c>
       <c r="B999" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Revisar una solicitud y Cita de cotejo (personal)</t>
         </is>
       </c>
       <c r="C999" s="15" t="inlineStr">
         <is>
-          <t>Búsqueda</t>
+          <t>Cabecera</t>
         </is>
       </c>
       <c r="D999" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E999" s="15" t="inlineStr">
         <is>
-          <t>Al buscar</t>
+          <t>Persona del registro asistido sin activar</t>
         </is>
       </c>
       <c r="F999" s="15" t="inlineStr">
         <is>
-          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
+          <t>Registro asistido: avisar por teléfono, 55 1234 5678</t>
         </is>
       </c>
       <c r="G999" s="13" t="inlineStr"/>
@@ -51130,7 +51130,7 @@
       </c>
       <c r="L999" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -51147,22 +51147,22 @@
       </c>
       <c r="C1000" s="12" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Búsqueda</t>
         </is>
       </c>
       <c r="D1000" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E1000" s="12" t="inlineStr">
         <is>
-          <t>Según la cuenta</t>
+          <t>Al buscar</t>
         </is>
       </c>
       <c r="F1000" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido · avisos por teléfono / Registro asistido · ya activó su cuenta / Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
+          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
         </is>
       </c>
       <c r="G1000" s="13" t="inlineStr"/>
@@ -51202,17 +51202,17 @@
       </c>
       <c r="D1001" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E1001" s="15" t="inlineStr">
         <is>
-          <t>Con avisos por teléfono pendientes</t>
+          <t>Según la cuenta</t>
         </is>
       </c>
       <c r="F1001" s="15" t="inlineStr">
         <is>
-          <t>Tiene un aviso por teléfono pendiente (Tiene N avisos…) · Si está aquí, dígaselo y regístrelo en la lista de avisos por teléfono pendientes.</t>
+          <t>Registro asistido · avisos por teléfono / Registro asistido · ya activó su cuenta / Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
         </is>
       </c>
       <c r="G1001" s="13" t="inlineStr"/>
@@ -51247,22 +51247,22 @@
       </c>
       <c r="C1002" s="12" t="inlineStr">
         <is>
-          <t>Ficha · Qué decirle (de tú)</t>
+          <t>Ficha</t>
         </is>
       </c>
       <c r="D1002" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E1002" s="12" t="inlineStr">
         <is>
-          <t>Según el estado</t>
+          <t>Con avisos por teléfono pendientes</t>
         </is>
       </c>
       <c r="F1002" s="12" t="inlineStr">
         <is>
-          <t>Tu solicitud todavía no se envía: falta terminar de capturarla contigo. / La Secretaría está revisando tus documentos. … / A tu solicitud le falta corregir un documento: … Lo corregimos aquí contigo. Hay un plazo para corregir. / Tu cita de cotejo es el … / Tu curso empieza el … / Tu cotejo terminó. Estás en espera de un grupo del curso … (y los «qué sigue» de «Mis trámites»)</t>
+          <t>Tiene un aviso por teléfono pendiente (Tiene N avisos…) · Si está aquí, dígaselo y regístrelo en la lista de avisos por teléfono pendientes.</t>
         </is>
       </c>
       <c r="G1002" s="13" t="inlineStr"/>
@@ -51280,7 +51280,7 @@
       </c>
       <c r="L1002" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/ventanilla.js)</t>
         </is>
       </c>
     </row>
@@ -51297,22 +51297,22 @@
       </c>
       <c r="C1003" s="15" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Ficha · Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1003" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E1003" s="15" t="inlineStr">
         <is>
-          <t>Persona del registro asistido</t>
+          <t>Según el estado</t>
         </is>
       </c>
       <c r="F1003" s="15" t="inlineStr">
         <is>
-          <t>Leerle lo que falta y cargar lo corregido · Seguir capturando su solicitud · Capturar una solicitud nueva</t>
+          <t>Tu solicitud todavía no se envía: falta terminar de capturarla contigo. / La Secretaría está revisando tus documentos. … / A tu solicitud le falta corregir un documento: … Lo corregimos aquí contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. (o: Esta es tu última oportunidad para corregir. …) / Tu solicitud se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva aquí mismo. / Tu cita de cotejo es el … / Tu curso empieza el … / Tu cotejo terminó. Estás en espera de un grupo del curso … (y los «qué sigue» de «Mis trámites»)</t>
         </is>
       </c>
       <c r="G1003" s="13" t="inlineStr"/>
@@ -51330,13 +51330,63 @@
       </c>
       <c r="L1003" s="16" t="inlineStr">
         <is>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="12" t="inlineStr">
+        <is>
+          <t>T1003</t>
+        </is>
+      </c>
+      <c r="B1004" s="12" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1004" s="12" t="inlineStr">
+        <is>
+          <t>Ficha</t>
+        </is>
+      </c>
+      <c r="D1004" s="12" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E1004" s="12" t="inlineStr">
+        <is>
+          <t>Persona del registro asistido</t>
+        </is>
+      </c>
+      <c r="F1004" s="12" t="inlineStr">
+        <is>
+          <t>Leerle lo que falta y cargar lo corregido · Seguir capturando su solicitud · Capturar una solicitud nueva</t>
+        </is>
+      </c>
+      <c r="G1004" s="13" t="inlineStr"/>
+      <c r="H1004" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1004" s="13" t="inlineStr"/>
+      <c r="J1004" s="12" t="inlineStr"/>
+      <c r="K1004" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1004" s="14" t="inlineStr">
+        <is>
           <t>Código del sitio (sitio/app/ventanilla.js)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1003"/>
-  <conditionalFormatting sqref="H2:H1003">
+  <autoFilter ref="A1:L1004"/>
+  <conditionalFormatting sqref="H2:H1004">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -51350,13 +51400,13 @@
       <formula>"Duda"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G1003">
+  <conditionalFormatting sqref="G2:G1004">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(LEN(G2)&gt;0,H2="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H1003" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
+    <dataValidation sqref="H2:H1004" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
       <formula1>"Pendiente,OK,Cambiar,Quitar,Duda"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.69 · 1003 textos</t>
+          <t>Inventario generado de la versión de prueba 0.70 · 1003 textos</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="F267" s="15" t="inlineStr">
         <is>
-          <t>Tuya, como persona solicitante, emitida en el mes en curso. De ella se toman tu nombre, tu régimen y tu domicilio fiscal para la factura del pago.</t>
+          <t>Tuya, como persona solicitante, emitida en el mes en curso. De ella se toman tu nombre, tu régimen y tu domicilio fiscal para la factura del pago. Cómo generar tu constancia de situación fiscal en el SAT.</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr"/>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$1004</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$1011</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.69 · 1003 textos</t>
+          <t>Inventario generado de la versión de prueba 0.70 · 1010 textos</t>
         </is>
       </c>
     </row>
@@ -761,23 +761,23 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A21)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A21)</f>
         <v/>
       </c>
       <c r="C21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A21,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A21,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A21,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A21,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A21,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A21,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -788,23 +788,23 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A22)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A22)</f>
         <v/>
       </c>
       <c r="C22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A22,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A22,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A22,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A22,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A22,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A22,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -815,23 +815,23 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A23)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A23)</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A23,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A23,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A23,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A23,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A23,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A23,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -842,23 +842,23 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A24)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A24)</f>
         <v/>
       </c>
       <c r="C24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A24,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A24,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A24,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A24,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A24,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A24,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -869,23 +869,23 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A25)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A25)</f>
         <v/>
       </c>
       <c r="C25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A25,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A25,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A25,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A25,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A25,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A25,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -896,23 +896,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A26)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A26)</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A26,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A26,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A26,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A26,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A26,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A26,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -923,23 +923,23 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A27)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A27)</f>
         <v/>
       </c>
       <c r="C27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A27,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A27,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A27,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A27,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A27,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A27,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -950,23 +950,23 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A28)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A28)</f>
         <v/>
       </c>
       <c r="C28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A28,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A28,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A28,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A28,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A28,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A28,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -977,23 +977,23 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A29)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A29)</f>
         <v/>
       </c>
       <c r="C29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A29,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A29,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A29,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A29,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A29,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A29,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A30)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A30)</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A30,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A30,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A30,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A30,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A30,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A30,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$1004,A31)</f>
+        <f>COUNTIF(Textos!$B$2:$B$1011,A31)</f>
         <v/>
       </c>
       <c r="C31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A31,Textos!$H$2:$H$1011,"Pendiente")</f>
         <v/>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A31,Textos!$H$2:$H$1011,"OK")</f>
         <v/>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A31,Textos!$H$2:$H$1011,"Cambiar")</f>
         <v/>
       </c>
       <c r="F31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Quitar")+COUNTIFS(Textos!$B$2:$B$1004,A31,Textos!$H$2:$H$1004,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$1011,A31,Textos!$H$2:$H$1011,"Quitar")+COUNTIFS(Textos!$B$2:$B$1011,A31,Textos!$H$2:$H$1011,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1004"/>
+  <dimension ref="A1:L1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -43339,12 +43339,12 @@
       </c>
       <c r="C844" s="12" t="inlineStr">
         <is>
-          <t>Armar un grupo</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D844" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E844" s="12" t="inlineStr">
@@ -43389,12 +43389,12 @@
       </c>
       <c r="C845" s="15" t="inlineStr">
         <is>
-          <t>El curso</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D845" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E845" s="15" t="inlineStr">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="F845" s="15" t="inlineStr">
         <is>
-          <t>¿Para qué curso?</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="G845" s="13" t="inlineStr"/>
@@ -43439,12 +43439,12 @@
       </c>
       <c r="C846" s="12" t="inlineStr">
         <is>
-          <t>El curso</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D846" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E846" s="12" t="inlineStr">
@@ -43454,7 +43454,7 @@
       </c>
       <c r="F846" s="12" t="inlineStr">
         <is>
-          <t>Cada curso arma sus grupos por separado: nunca se mezclan.</t>
+          <t>Ya terminaron</t>
         </is>
       </c>
       <c r="G846" s="13" t="inlineStr"/>
@@ -43489,12 +43489,12 @@
       </c>
       <c r="C847" s="15" t="inlineStr">
         <is>
-          <t>El curso</t>
+          <t>Armar un grupo</t>
         </is>
       </c>
       <c r="D847" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E847" s="15" t="inlineStr">
@@ -43504,7 +43504,7 @@
       </c>
       <c r="F847" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poda y derribo · nueva — </t>
+          <t>Armar un grupo</t>
         </is>
       </c>
       <c r="G847" s="13" t="inlineStr"/>
@@ -43544,7 +43544,7 @@
       </c>
       <c r="D848" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E848" s="12" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="F848" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poda y derribo · renovación — </t>
+          <t>¿Para qué curso?</t>
         </is>
       </c>
       <c r="G848" s="13" t="inlineStr"/>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="D849" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E849" s="15" t="inlineStr">
@@ -43604,7 +43604,7 @@
       </c>
       <c r="F849" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dictaminador técnico · nueva — </t>
+          <t>Cada curso arma sus grupos por separado: nunca se mezclan.</t>
         </is>
       </c>
       <c r="G849" s="13" t="inlineStr"/>
@@ -43654,7 +43654,7 @@
       </c>
       <c r="F850" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dictaminador técnico · renovación — </t>
+          <t xml:space="preserve">Poda y derribo · nueva — </t>
         </is>
       </c>
       <c r="G850" s="13" t="inlineStr"/>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="D851" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E851" s="15" t="inlineStr">
@@ -43704,7 +43704,7 @@
       </c>
       <c r="F851" s="15" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t xml:space="preserve">Poda y derribo · renovación — </t>
         </is>
       </c>
       <c r="G851" s="13" t="inlineStr"/>
@@ -43739,12 +43739,12 @@
       </c>
       <c r="C852" s="12" t="inlineStr">
         <is>
-          <t>La semana</t>
+          <t>El curso</t>
         </is>
       </c>
       <c r="D852" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E852" s="12" t="inlineStr">
@@ -43754,7 +43754,7 @@
       </c>
       <c r="F852" s="12" t="inlineStr">
         <is>
-          <t>¿Qué semana?</t>
+          <t xml:space="preserve">Dictaminador técnico · nueva — </t>
         </is>
       </c>
       <c r="G852" s="13" t="inlineStr"/>
@@ -43789,12 +43789,12 @@
       </c>
       <c r="C853" s="15" t="inlineStr">
         <is>
-          <t>La semana</t>
+          <t>El curso</t>
         </is>
       </c>
       <c r="D853" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E853" s="15" t="inlineStr">
@@ -43804,7 +43804,7 @@
       </c>
       <c r="F853" s="15" t="inlineStr">
         <is>
-          <t>Semana elegida</t>
+          <t xml:space="preserve">Dictaminador técnico · renovación — </t>
         </is>
       </c>
       <c r="G853" s="13" t="inlineStr"/>
@@ -43839,12 +43839,12 @@
       </c>
       <c r="C854" s="12" t="inlineStr">
         <is>
-          <t>La semana</t>
+          <t>El curso</t>
         </is>
       </c>
       <c r="D854" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E854" s="12" t="inlineStr">
@@ -43854,7 +43854,7 @@
       </c>
       <c r="F854" s="12" t="inlineStr">
         <is>
-          <t>Ninguna todavía</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G854" s="13" t="inlineStr"/>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="D855" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E855" s="15" t="inlineStr">
@@ -43904,7 +43904,7 @@
       </c>
       <c r="F855" s="15" t="inlineStr">
         <is>
-          <t>Primer día del curso</t>
+          <t>¿Qué semana?</t>
         </is>
       </c>
       <c r="G855" s="13" t="inlineStr"/>
@@ -43944,7 +43944,7 @@
       </c>
       <c r="D856" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E856" s="12" t="inlineStr">
@@ -43954,7 +43954,7 @@
       </c>
       <c r="F856" s="12" t="inlineStr">
         <is>
-          <t>Se llena al elegir la semana en el calendario.</t>
+          <t>Semana elegida</t>
         </is>
       </c>
       <c r="G856" s="13" t="inlineStr"/>
@@ -44004,7 +44004,7 @@
       </c>
       <c r="F857" s="15" t="inlineStr">
         <is>
-          <t>Semana libre: toque «Libre» para elegirla</t>
+          <t>Ninguna todavía</t>
         </is>
       </c>
       <c r="G857" s="13" t="inlineStr"/>
@@ -44044,7 +44044,7 @@
       </c>
       <c r="D858" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E858" s="12" t="inlineStr">
@@ -44054,7 +44054,7 @@
       </c>
       <c r="F858" s="12" t="inlineStr">
         <is>
-          <t>El grupo nuevo</t>
+          <t>Primer día del curso</t>
         </is>
       </c>
       <c r="G858" s="13" t="inlineStr"/>
@@ -44094,7 +44094,7 @@
       </c>
       <c r="D859" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E859" s="15" t="inlineStr">
@@ -44104,7 +44104,7 @@
       </c>
       <c r="F859" s="15" t="inlineStr">
         <is>
-          <t>Grupo por confirmar</t>
+          <t>Se llena al elegir la semana en el calendario.</t>
         </is>
       </c>
       <c r="G859" s="13" t="inlineStr"/>
@@ -44154,7 +44154,7 @@
       </c>
       <c r="F860" s="12" t="inlineStr">
         <is>
-          <t>Grupo confirmado</t>
+          <t>Semana libre: toque «Libre» para elegirla</t>
         </is>
       </c>
       <c r="G860" s="13" t="inlineStr"/>
@@ -44204,7 +44204,7 @@
       </c>
       <c r="F861" s="15" t="inlineStr">
         <is>
-          <t>Grupo en curso</t>
+          <t>El grupo nuevo</t>
         </is>
       </c>
       <c r="G861" s="13" t="inlineStr"/>
@@ -44254,7 +44254,7 @@
       </c>
       <c r="F862" s="12" t="inlineStr">
         <is>
-          <t>Grupo que ya terminó</t>
+          <t>Grupo por confirmar</t>
         </is>
       </c>
       <c r="G862" s="13" t="inlineStr"/>
@@ -44304,7 +44304,7 @@
       </c>
       <c r="F863" s="15" t="inlineStr">
         <is>
-          <t>Grupo de otro curso: también cuenta para el máximo</t>
+          <t>Grupo confirmado</t>
         </is>
       </c>
       <c r="G863" s="13" t="inlineStr"/>
@@ -44354,7 +44354,7 @@
       </c>
       <c r="F864" s="12" t="inlineStr">
         <is>
-          <t>No disponible: ya pasó, faltan menos de 7 días o ya hay 2 grupos</t>
+          <t>Grupo en curso</t>
         </is>
       </c>
       <c r="G864" s="13" t="inlineStr"/>
@@ -44404,7 +44404,7 @@
       </c>
       <c r="F865" s="15" t="inlineStr">
         <is>
-          <t>Sábado y domingo: no hay curso</t>
+          <t>Grupo que ya terminó</t>
         </is>
       </c>
       <c r="G865" s="13" t="inlineStr"/>
@@ -44454,7 +44454,7 @@
       </c>
       <c r="F866" s="12" t="inlineStr">
         <is>
-          <t>Día inhábil [por confirmar con el calendario oficial de la Secretaría]</t>
+          <t>Grupo de otro curso: también cuenta para el máximo</t>
         </is>
       </c>
       <c r="G866" s="13" t="inlineStr"/>
@@ -44494,7 +44494,7 @@
       </c>
       <c r="D867" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E867" s="15" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="F867" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>No disponible: ya pasó, faltan menos de 7 días o ya hay 2 grupos</t>
         </is>
       </c>
       <c r="G867" s="13" t="inlineStr"/>
@@ -44544,7 +44544,7 @@
       </c>
       <c r="D868" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E868" s="12" t="inlineStr">
@@ -44554,7 +44554,7 @@
       </c>
       <c r="F868" s="12" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Sábado y domingo: no hay curso</t>
         </is>
       </c>
       <c r="G868" s="13" t="inlineStr"/>
@@ -44589,12 +44589,12 @@
       </c>
       <c r="C869" s="15" t="inlineStr">
         <is>
-          <t>Quiénes van</t>
+          <t>La semana</t>
         </is>
       </c>
       <c r="D869" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E869" s="15" t="inlineStr">
@@ -44604,7 +44604,7 @@
       </c>
       <c r="F869" s="15" t="inlineStr">
         <is>
-          <t>¿Quiénes van?</t>
+          <t>Día inhábil [por confirmar con el calendario oficial de la Secretaría]</t>
         </is>
       </c>
       <c r="G869" s="13" t="inlineStr"/>
@@ -44639,12 +44639,12 @@
       </c>
       <c r="C870" s="12" t="inlineStr">
         <is>
-          <t>Quiénes van</t>
+          <t>La semana</t>
         </is>
       </c>
       <c r="D870" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E870" s="12" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="F870" s="12" t="inlineStr">
         <is>
-          <t>Si hay más de 25, entran las que más esperan y las de una misma institución de gobierno van juntas; el resto sigue en espera para otra semana.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G870" s="13" t="inlineStr"/>
@@ -44689,12 +44689,12 @@
       </c>
       <c r="C871" s="15" t="inlineStr">
         <is>
-          <t>Quiénes van</t>
+          <t>La semana</t>
         </is>
       </c>
       <c r="D871" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E871" s="15" t="inlineStr">
@@ -44704,7 +44704,7 @@
       </c>
       <c r="F871" s="15" t="inlineStr">
         <is>
-          <t>¿De quiénes es el grupo?</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G871" s="13" t="inlineStr"/>
@@ -44744,7 +44744,7 @@
       </c>
       <c r="D872" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E872" s="12" t="inlineStr">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="F872" s="12" t="inlineStr">
         <is>
-          <t>Combinado — Recibe personas de cualquier organización e independientes.</t>
+          <t>¿Quiénes van?</t>
         </is>
       </c>
       <c r="G872" s="13" t="inlineStr"/>
@@ -44794,7 +44794,7 @@
       </c>
       <c r="D873" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E873" s="15" t="inlineStr">
@@ -44804,7 +44804,7 @@
       </c>
       <c r="F873" s="15" t="inlineStr">
         <is>
-          <t>Sólo de una institución de gobierno — Recibe únicamente a la gente de esa institución: todas las elegidas tienen que ser de ella.</t>
+          <t>Si hay más de 25, entran las que más esperan y las de una misma institución de gobierno van juntas; el resto sigue en espera para otra semana.</t>
         </is>
       </c>
       <c r="G873" s="13" t="inlineStr"/>
@@ -44844,7 +44844,7 @@
       </c>
       <c r="D874" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E874" s="12" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="F874" s="12" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>¿De quiénes es el grupo?</t>
         </is>
       </c>
       <c r="G874" s="13" t="inlineStr"/>
@@ -44894,7 +44894,7 @@
       </c>
       <c r="D875" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E875" s="15" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="F875" s="15" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Combinado — Recibe personas de cualquier organización e independientes.</t>
         </is>
       </c>
       <c r="G875" s="13" t="inlineStr"/>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="C876" s="12" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Quiénes van</t>
         </is>
       </c>
       <c r="D876" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E876" s="12" t="inlineStr">
@@ -44954,7 +44954,7 @@
       </c>
       <c r="F876" s="12" t="inlineStr">
         <is>
-          <t>Revise y confirme</t>
+          <t>Sólo de una institución de gobierno — Recibe únicamente a la gente de esa institución: todas las elegidas tienen que ser de ella.</t>
         </is>
       </c>
       <c r="G876" s="13" t="inlineStr"/>
@@ -44989,12 +44989,12 @@
       </c>
       <c r="C877" s="15" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Quiénes van</t>
         </is>
       </c>
       <c r="D877" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E877" s="15" t="inlineStr">
@@ -45004,7 +45004,7 @@
       </c>
       <c r="F877" s="15" t="inlineStr">
         <is>
-          <t>La persona instructora la asigna el área de Instructores y Capacitación, que también confirma el grupo.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G877" s="13" t="inlineStr"/>
@@ -45039,7 +45039,7 @@
       </c>
       <c r="C878" s="12" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Quiénes van</t>
         </is>
       </c>
       <c r="D878" s="12" t="inlineStr">
@@ -45054,7 +45054,7 @@
       </c>
       <c r="F878" s="12" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G878" s="13" t="inlineStr"/>
@@ -45094,7 +45094,7 @@
       </c>
       <c r="D879" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E879" s="15" t="inlineStr">
@@ -45104,7 +45104,7 @@
       </c>
       <c r="F879" s="15" t="inlineStr">
         <is>
-          <t>Crear el grupo</t>
+          <t>Revise y confirme</t>
         </is>
       </c>
       <c r="G879" s="13" t="inlineStr"/>
@@ -45139,12 +45139,12 @@
       </c>
       <c r="C880" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D880" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E880" s="12" t="inlineStr">
@@ -45154,7 +45154,7 @@
       </c>
       <c r="F880" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>La persona instructora la asigna el área de Instructores y Capacitación, que también confirma el grupo.</t>
         </is>
       </c>
       <c r="G880" s="13" t="inlineStr"/>
@@ -45189,12 +45189,12 @@
       </c>
       <c r="C881" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D881" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E881" s="15" t="inlineStr">
@@ -45204,7 +45204,7 @@
       </c>
       <c r="F881" s="15" t="inlineStr">
         <is>
-          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G881" s="13" t="inlineStr"/>
@@ -45239,12 +45239,12 @@
       </c>
       <c r="C882" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D882" s="12" t="inlineStr">
         <is>
-          <t>Título desplegable</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E882" s="12" t="inlineStr">
@@ -45254,7 +45254,7 @@
       </c>
       <c r="F882" s="12" t="inlineStr">
         <is>
-          <t>Grupos que ya terminaron</t>
+          <t>Crear el grupo</t>
         </is>
       </c>
       <c r="G882" s="13" t="inlineStr"/>
@@ -45289,12 +45289,12 @@
       </c>
       <c r="C883" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="D883" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E883" s="15" t="inlineStr">
@@ -45304,7 +45304,7 @@
       </c>
       <c r="F883" s="15" t="inlineStr">
         <is>
-          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas y su persona instructora, y recibe hasta 25. Sólo las instituciones de gobierno tienen grupo propio. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="G883" s="13" t="inlineStr"/>
@@ -45334,17 +45334,17 @@
       </c>
       <c r="B884" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C884" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="D884" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E884" s="12" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="F884" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G884" s="13" t="inlineStr"/>
@@ -45372,7 +45372,7 @@
       </c>
       <c r="L884" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45384,17 +45384,17 @@
       </c>
       <c r="B885" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C885" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="D885" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E885" s="15" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="F885" s="15" t="inlineStr">
         <is>
-          <t>Los grupos que esperan persona instructora o confirmación, del que empieza antes al más lejano. En la ficha de cada uno se asigna a la persona instructora, libre esas fechas, y se confirma el grupo.</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G885" s="13" t="inlineStr"/>
@@ -45422,7 +45422,7 @@
       </c>
       <c r="L885" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45434,17 +45434,17 @@
       </c>
       <c r="B886" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C886" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D886" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E886" s="12" t="inlineStr">
@@ -45454,7 +45454,7 @@
       </c>
       <c r="F886" s="12" t="inlineStr">
         <is>
-          <t>Cargando los grupos…</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="G886" s="13" t="inlineStr"/>
@@ -45464,11 +45464,7 @@
         </is>
       </c>
       <c r="I886" s="13" t="inlineStr"/>
-      <c r="J886" s="17" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J886" s="12" t="inlineStr"/>
       <c r="K886" s="14" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -45476,7 +45472,7 @@
       </c>
       <c r="L886" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45488,17 +45484,17 @@
       </c>
       <c r="B887" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C887" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D887" s="15" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E887" s="15" t="inlineStr">
@@ -45508,7 +45504,7 @@
       </c>
       <c r="F887" s="15" t="inlineStr">
         <is>
-          <t>Grupo</t>
+          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
         </is>
       </c>
       <c r="G887" s="13" t="inlineStr"/>
@@ -45526,7 +45522,7 @@
       </c>
       <c r="L887" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45538,17 +45534,17 @@
       </c>
       <c r="B888" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C888" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D888" s="12" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Título desplegable</t>
         </is>
       </c>
       <c r="E888" s="12" t="inlineStr">
@@ -45558,7 +45554,7 @@
       </c>
       <c r="F888" s="12" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Grupos que ya terminaron</t>
         </is>
       </c>
       <c r="G888" s="13" t="inlineStr"/>
@@ -45576,7 +45572,7 @@
       </c>
       <c r="L888" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45588,17 +45584,17 @@
       </c>
       <c r="B889" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C889" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D889" s="15" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E889" s="15" t="inlineStr">
@@ -45608,7 +45604,7 @@
       </c>
       <c r="F889" s="15" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Todavía no hay grupos que hayan terminado.</t>
         </is>
       </c>
       <c r="G889" s="13" t="inlineStr"/>
@@ -45626,7 +45622,7 @@
       </c>
       <c r="L889" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45638,17 +45634,17 @@
       </c>
       <c r="B890" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C890" s="12" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D890" s="12" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E890" s="12" t="inlineStr">
@@ -45658,7 +45654,7 @@
       </c>
       <c r="F890" s="12" t="inlineStr">
         <is>
-          <t>Persona instructora</t>
+          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas y su persona instructora, y recibe hasta 25. Sólo las instituciones de gobierno tienen grupo propio. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
         </is>
       </c>
       <c r="G890" s="13" t="inlineStr"/>
@@ -45676,7 +45672,7 @@
       </c>
       <c r="L890" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45698,7 +45694,7 @@
       </c>
       <c r="D891" s="15" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E891" s="15" t="inlineStr">
@@ -45708,7 +45704,7 @@
       </c>
       <c r="F891" s="15" t="inlineStr">
         <is>
-          <t>Lo que falta</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="G891" s="13" t="inlineStr"/>
@@ -45748,7 +45744,7 @@
       </c>
       <c r="D892" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E892" s="12" t="inlineStr">
@@ -45758,7 +45754,7 @@
       </c>
       <c r="F892" s="12" t="inlineStr">
         <is>
-          <t>Ningún grupo espera persona instructora ni confirmación.</t>
+          <t>Los grupos que esperan persona instructora o confirmación, del que empieza antes al más lejano. En la ficha de cada uno se asigna a la persona instructora, libre esas fechas, y se confirma el grupo.</t>
         </is>
       </c>
       <c r="G892" s="13" t="inlineStr"/>
@@ -45793,12 +45789,12 @@
       </c>
       <c r="C893" s="15" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D893" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E893" s="15" t="inlineStr">
@@ -45808,7 +45804,7 @@
       </c>
       <c r="F893" s="15" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Cargando los grupos…</t>
         </is>
       </c>
       <c r="G893" s="13" t="inlineStr"/>
@@ -45818,7 +45814,11 @@
         </is>
       </c>
       <c r="I893" s="13" t="inlineStr"/>
-      <c r="J893" s="15" t="inlineStr"/>
+      <c r="J893" s="18" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K893" s="16" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -45843,12 +45843,12 @@
       </c>
       <c r="C894" s="12" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D894" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E894" s="12" t="inlineStr">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="F894" s="12" t="inlineStr">
         <is>
-          <t>Si hace falta, cambie a la persona instructora, también durante el curso: el cambio queda en la bitácora.</t>
+          <t>Grupo</t>
         </is>
       </c>
       <c r="G894" s="13" t="inlineStr"/>
@@ -45893,7 +45893,7 @@
       </c>
       <c r="C895" s="15" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D895" s="15" t="inlineStr">
@@ -45908,7 +45908,7 @@
       </c>
       <c r="F895" s="15" t="inlineStr">
         <is>
-          <t>Grupo</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="G895" s="13" t="inlineStr"/>
@@ -45943,7 +45943,7 @@
       </c>
       <c r="C896" s="12" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D896" s="12" t="inlineStr">
@@ -45958,7 +45958,7 @@
       </c>
       <c r="F896" s="12" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="G896" s="13" t="inlineStr"/>
@@ -45993,7 +45993,7 @@
       </c>
       <c r="C897" s="15" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D897" s="15" t="inlineStr">
@@ -46008,7 +46008,7 @@
       </c>
       <c r="F897" s="15" t="inlineStr">
         <is>
-          <t>Situación</t>
+          <t>Persona instructora</t>
         </is>
       </c>
       <c r="G897" s="13" t="inlineStr"/>
@@ -46043,7 +46043,7 @@
       </c>
       <c r="C898" s="12" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D898" s="12" t="inlineStr">
@@ -46058,7 +46058,7 @@
       </c>
       <c r="F898" s="12" t="inlineStr">
         <is>
-          <t>Persona instructora</t>
+          <t>Lo que falta</t>
         </is>
       </c>
       <c r="G898" s="13" t="inlineStr"/>
@@ -46093,7 +46093,7 @@
       </c>
       <c r="C899" s="15" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D899" s="15" t="inlineStr">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="F899" s="15" t="inlineStr">
         <is>
-          <t>No hay grupos confirmados ni en curso.</t>
+          <t>Ningún grupo espera persona instructora ni confirmación.</t>
         </is>
       </c>
       <c r="G899" s="13" t="inlineStr"/>
@@ -46138,17 +46138,17 @@
       </c>
       <c r="B900" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C900" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D900" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E900" s="12" t="inlineStr">
@@ -46158,7 +46158,7 @@
       </c>
       <c r="F900" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="G900" s="13" t="inlineStr"/>
@@ -46176,7 +46176,7 @@
       </c>
       <c r="L900" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46188,17 +46188,17 @@
       </c>
       <c r="B901" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C901" s="15" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D901" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E901" s="15" t="inlineStr">
@@ -46208,7 +46208,7 @@
       </c>
       <c r="F901" s="15" t="inlineStr">
         <is>
-          <t>Léale el aviso de privacidad</t>
+          <t>Si hace falta, cambie a la persona instructora, también durante el curso: el cambio queda en la bitácora.</t>
         </is>
       </c>
       <c r="G901" s="13" t="inlineStr"/>
@@ -46226,7 +46226,7 @@
       </c>
       <c r="L901" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46238,17 +46238,17 @@
       </c>
       <c r="B902" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C902" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D902" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E902" s="12" t="inlineStr">
@@ -46258,7 +46258,7 @@
       </c>
       <c r="F902" s="12" t="inlineStr">
         <is>
-          <t>Para una persona que no sabe leer ni escribir, con ella presente. Usted crea su cuenta, captura su solicitud y le da seguimiento por teléfono y en la ventanilla. Empiece por leerle en voz alta el aviso.</t>
+          <t>Grupo</t>
         </is>
       </c>
       <c r="G902" s="13" t="inlineStr"/>
@@ -46276,7 +46276,7 @@
       </c>
       <c r="L902" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46288,17 +46288,17 @@
       </c>
       <c r="B903" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C903" s="15" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D903" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E903" s="15" t="inlineStr">
@@ -46308,7 +46308,7 @@
       </c>
       <c r="F903" s="15" t="inlineStr">
         <is>
-          <t>Versión de prueba: use datos inventados No capture datos ni fotografías de personas reales. Lo que capture se guarda sólo en este navegador y se borra solo cuando pasan 7 días sin usar la prueba.</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="G903" s="13" t="inlineStr"/>
@@ -46326,7 +46326,7 @@
       </c>
       <c r="L903" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46338,17 +46338,17 @@
       </c>
       <c r="B904" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C904" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D904" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E904" s="12" t="inlineStr">
@@ -46358,7 +46358,7 @@
       </c>
       <c r="F904" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad simplificado</t>
+          <t>Situación</t>
         </is>
       </c>
       <c r="G904" s="13" t="inlineStr"/>
@@ -46376,7 +46376,7 @@
       </c>
       <c r="L904" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46388,17 +46388,17 @@
       </c>
       <c r="B905" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C905" s="15" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D905" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E905" s="15" t="inlineStr">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="F905" s="15" t="inlineStr">
         <is>
-          <t>La Secretaría del Medio Ambiente recaba tu nombre, tu CURP (y de ella tu sexo y tu fecha de nacimiento), tu fotografía de frente, tu teléfono, tu correo si tienes y la institución para la que trabajas, si es el caso, para crear tu cuenta, tramitar tu acreditación, reconocerte en la cita, el curso y el examen, avisarte el avance por teléfono y llevar el padrón de personas acreditadas. Al entregarte la credencial te toma otra fotografía, que es la que se imprime en ella.</t>
+          <t>Persona instructora</t>
         </is>
       </c>
       <c r="G905" s="13" t="inlineStr"/>
@@ -46426,7 +46426,7 @@
       </c>
       <c r="L905" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46438,12 +46438,12 @@
       </c>
       <c r="B906" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C906" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D906" s="12" t="inlineStr">
@@ -46458,7 +46458,7 @@
       </c>
       <c r="F906" s="12" t="inlineStr">
         <is>
-          <t>Fundamento: [Art. __, fracc. __]. Pendiente: lo completa la Unidad de Transparencia.</t>
+          <t>No hay grupos confirmados ni en curso.</t>
         </is>
       </c>
       <c r="G906" s="13" t="inlineStr"/>
@@ -46468,11 +46468,7 @@
         </is>
       </c>
       <c r="I906" s="13" t="inlineStr"/>
-      <c r="J906" s="17" t="inlineStr">
-        <is>
-          <t>Lo completa la Unidad de Transparencia; no se inventa la cita.</t>
-        </is>
-      </c>
+      <c r="J906" s="12" t="inlineStr"/>
       <c r="K906" s="14" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -46480,7 +46476,7 @@
       </c>
       <c r="L906" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46497,12 +46493,12 @@
       </c>
       <c r="C907" s="15" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D907" s="15" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E907" s="15" t="inlineStr">
@@ -46512,7 +46508,7 @@
       </c>
       <c r="F907" s="15" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Inicio del personal</t>
         </is>
       </c>
       <c r="G907" s="13" t="inlineStr"/>
@@ -46547,12 +46543,12 @@
       </c>
       <c r="C908" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
         </is>
       </c>
       <c r="D908" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E908" s="12" t="inlineStr">
@@ -46562,7 +46558,7 @@
       </c>
       <c r="F908" s="12" t="inlineStr">
         <is>
-          <t>Le leí el aviso de privacidad a la persona y lo aceptó</t>
+          <t>Léale el aviso de privacidad</t>
         </is>
       </c>
       <c r="G908" s="13" t="inlineStr"/>
@@ -46597,12 +46593,12 @@
       </c>
       <c r="C909" s="15" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
         </is>
       </c>
       <c r="D909" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E909" s="15" t="inlineStr">
@@ -46612,7 +46608,7 @@
       </c>
       <c r="F909" s="15" t="inlineStr">
         <is>
-          <t>Queda registrado con su nombre y la hora. Sin esta marca no se continúa.</t>
+          <t>Para una persona que no sabe leer ni escribir, con ella presente. Usted crea su cuenta, captura su solicitud y le da seguimiento por teléfono y en la ventanilla. Empiece por leerle en voz alta el aviso.</t>
         </is>
       </c>
       <c r="G909" s="13" t="inlineStr"/>
@@ -46647,12 +46643,12 @@
       </c>
       <c r="C910" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
+          <t>Aviso de privacidad · Léale el aviso de privacidad</t>
         </is>
       </c>
       <c r="D910" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E910" s="12" t="inlineStr">
@@ -46662,7 +46658,7 @@
       </c>
       <c r="F910" s="12" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Versión de prueba: use datos inventados No capture datos ni fotografías de personas reales. Lo que capture se guarda sólo en este navegador y se borra solo cuando pasan 7 días sin usar la prueba.</t>
         </is>
       </c>
       <c r="G910" s="13" t="inlineStr"/>
@@ -46697,12 +46693,12 @@
       </c>
       <c r="C911" s="15" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D911" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E911" s="15" t="inlineStr">
@@ -46712,7 +46708,7 @@
       </c>
       <c r="F911" s="15" t="inlineStr">
         <is>
-          <t>Datos de la persona</t>
+          <t>Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="G911" s="13" t="inlineStr"/>
@@ -46747,12 +46743,12 @@
       </c>
       <c r="C912" s="12" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D912" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E912" s="12" t="inlineStr">
@@ -46762,7 +46758,7 @@
       </c>
       <c r="F912" s="12" t="inlineStr">
         <is>
-          <t>Capture los datos como vienen en su CURP. Las preguntas de la adscripción van escritas para la persona: léaselas tal cual.</t>
+          <t>La Secretaría del Medio Ambiente recaba tu nombre, tu CURP (y de ella tu sexo y tu fecha de nacimiento), tu fotografía de frente, tu teléfono, tu correo si tienes y la institución para la que trabajas, si es el caso, para crear tu cuenta, tramitar tu acreditación, reconocerte en la cita, el curso y el examen, avisarte el avance por teléfono y llevar el padrón de personas acreditadas. Al entregarte la credencial te toma otra fotografía, que es la que se imprime en ella.</t>
         </is>
       </c>
       <c r="G912" s="13" t="inlineStr"/>
@@ -46797,12 +46793,12 @@
       </c>
       <c r="C913" s="15" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D913" s="15" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E913" s="15" t="inlineStr">
@@ -46812,7 +46808,7 @@
       </c>
       <c r="F913" s="15" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Fundamento: [Art. __, fracc. __]. Pendiente: lo completa la Unidad de Transparencia.</t>
         </is>
       </c>
       <c r="G913" s="13" t="inlineStr"/>
@@ -46822,7 +46818,11 @@
         </is>
       </c>
       <c r="I913" s="13" t="inlineStr"/>
-      <c r="J913" s="15" t="inlineStr"/>
+      <c r="J913" s="18" t="inlineStr">
+        <is>
+          <t>Lo completa la Unidad de Transparencia; no se inventa la cita.</t>
+        </is>
+      </c>
       <c r="K913" s="16" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -46847,12 +46847,12 @@
       </c>
       <c r="C914" s="12" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D914" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E914" s="12" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="F914" s="12" t="inlineStr">
         <is>
-          <t>Nombre o nombres</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G914" s="13" t="inlineStr"/>
@@ -46897,7 +46897,7 @@
       </c>
       <c r="C915" s="15" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D915" s="15" t="inlineStr">
@@ -46912,7 +46912,7 @@
       </c>
       <c r="F915" s="15" t="inlineStr">
         <is>
-          <t>Primer apellido</t>
+          <t>Le leí el aviso de privacidad a la persona y lo aceptó</t>
         </is>
       </c>
       <c r="G915" s="13" t="inlineStr"/>
@@ -46947,12 +46947,12 @@
       </c>
       <c r="C916" s="12" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D916" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E916" s="12" t="inlineStr">
@@ -46962,7 +46962,7 @@
       </c>
       <c r="F916" s="12" t="inlineStr">
         <is>
-          <t>Segundo apellido</t>
+          <t>Queda registrado con su nombre y la hora. Sin esta marca no se continúa.</t>
         </is>
       </c>
       <c r="G916" s="13" t="inlineStr"/>
@@ -46997,12 +46997,12 @@
       </c>
       <c r="C917" s="15" t="inlineStr">
         <is>
-          <t>Datos · Datos de la persona</t>
+          <t>Aviso de privacidad · Aviso de privacidad simplificado</t>
         </is>
       </c>
       <c r="D917" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E917" s="15" t="inlineStr">
@@ -47012,7 +47012,7 @@
       </c>
       <c r="F917" s="15" t="inlineStr">
         <is>
-          <t>Si no tiene segundo apellido, déjelo vacío.</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G917" s="13" t="inlineStr"/>
@@ -47052,7 +47052,7 @@
       </c>
       <c r="D918" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E918" s="12" t="inlineStr">
@@ -47062,7 +47062,7 @@
       </c>
       <c r="F918" s="12" t="inlineStr">
         <is>
-          <t>CURP</t>
+          <t>Datos de la persona</t>
         </is>
       </c>
       <c r="G918" s="13" t="inlineStr"/>
@@ -47102,7 +47102,7 @@
       </c>
       <c r="D919" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E919" s="15" t="inlineStr">
@@ -47112,7 +47112,7 @@
       </c>
       <c r="F919" s="15" t="inlineStr">
         <is>
-          <t>18 caracteres, de su constancia de CURP o de su identificación. La persona necesita tener 18 años cumplidos.</t>
+          <t>Capture los datos como vienen en su CURP. Las preguntas de la adscripción van escritas para la persona: léaselas tal cual.</t>
         </is>
       </c>
       <c r="G919" s="13" t="inlineStr"/>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="D920" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E920" s="12" t="inlineStr">
@@ -47162,7 +47162,7 @@
       </c>
       <c r="F920" s="12" t="inlineStr">
         <is>
-          <t>Fecha de nacimiento</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G920" s="13" t="inlineStr"/>
@@ -47202,7 +47202,7 @@
       </c>
       <c r="D921" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E921" s="15" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="F921" s="15" t="inlineStr">
         <is>
-          <t>Se toma de la CURP.</t>
+          <t>Nombre o nombres</t>
         </is>
       </c>
       <c r="G921" s="13" t="inlineStr"/>
@@ -47262,7 +47262,7 @@
       </c>
       <c r="F922" s="12" t="inlineStr">
         <is>
-          <t>Sexo</t>
+          <t>Primer apellido</t>
         </is>
       </c>
       <c r="G922" s="13" t="inlineStr"/>
@@ -47297,12 +47297,12 @@
       </c>
       <c r="C923" s="15" t="inlineStr">
         <is>
-          <t>Datos · Cómo se le avisa</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D923" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E923" s="15" t="inlineStr">
@@ -47312,7 +47312,7 @@
       </c>
       <c r="F923" s="15" t="inlineStr">
         <is>
-          <t>Cómo se le avisa</t>
+          <t>Segundo apellido</t>
         </is>
       </c>
       <c r="G923" s="13" t="inlineStr"/>
@@ -47347,12 +47347,12 @@
       </c>
       <c r="C924" s="12" t="inlineStr">
         <is>
-          <t>Datos · Cómo se le avisa</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D924" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E924" s="12" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="F924" s="12" t="inlineStr">
         <is>
-          <t>Teléfono</t>
+          <t>Si no tiene segundo apellido, déjelo vacío.</t>
         </is>
       </c>
       <c r="G924" s="13" t="inlineStr"/>
@@ -47397,12 +47397,12 @@
       </c>
       <c r="C925" s="15" t="inlineStr">
         <is>
-          <t>Datos · Cómo se le avisa</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D925" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E925" s="15" t="inlineStr">
@@ -47412,7 +47412,7 @@
       </c>
       <c r="F925" s="15" t="inlineStr">
         <is>
-          <t>Diez dígitos. Por aquí se le avisan su cita, su curso y sus resultados.</t>
+          <t>CURP</t>
         </is>
       </c>
       <c r="G925" s="13" t="inlineStr"/>
@@ -47447,12 +47447,12 @@
       </c>
       <c r="C926" s="12" t="inlineStr">
         <is>
-          <t>Datos · Cómo se le avisa</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D926" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E926" s="12" t="inlineStr">
@@ -47462,7 +47462,7 @@
       </c>
       <c r="F926" s="12" t="inlineStr">
         <is>
-          <t>Correo electrónico (si tiene)</t>
+          <t>18 caracteres, de su constancia de CURP o de su identificación. La persona necesita tener 18 años cumplidos.</t>
         </is>
       </c>
       <c r="G926" s="13" t="inlineStr"/>
@@ -47497,12 +47497,12 @@
       </c>
       <c r="C927" s="15" t="inlineStr">
         <is>
-          <t>Datos · Cómo se le avisa</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D927" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E927" s="15" t="inlineStr">
@@ -47512,7 +47512,7 @@
       </c>
       <c r="F927" s="15" t="inlineStr">
         <is>
-          <t>Opcional. Si lo da, no puede ser el de otra cuenta.</t>
+          <t>Fecha de nacimiento</t>
         </is>
       </c>
       <c r="G927" s="13" t="inlineStr"/>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="C928" s="12" t="inlineStr">
         <is>
-          <t>Datos · Su adscripción</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D928" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E928" s="12" t="inlineStr">
@@ -47562,7 +47562,7 @@
       </c>
       <c r="F928" s="12" t="inlineStr">
         <is>
-          <t>Su adscripción</t>
+          <t>Se toma de la CURP.</t>
         </is>
       </c>
       <c r="G928" s="13" t="inlineStr"/>
@@ -47580,7 +47580,7 @@
       </c>
       <c r="L928" s="14" t="inlineStr">
         <is>
-          <t>Fragmento de adscripción (herramientas/plantillas/adscripcion.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -47597,12 +47597,12 @@
       </c>
       <c r="C929" s="15" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Datos de la persona</t>
         </is>
       </c>
       <c r="D929" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E929" s="15" t="inlineStr">
@@ -47612,7 +47612,7 @@
       </c>
       <c r="F929" s="15" t="inlineStr">
         <is>
-          <t>Su fotografía</t>
+          <t>Sexo</t>
         </is>
       </c>
       <c r="G929" s="13" t="inlineStr"/>
@@ -47647,12 +47647,12 @@
       </c>
       <c r="C930" s="12" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Cómo se le avisa</t>
         </is>
       </c>
       <c r="D930" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E930" s="12" t="inlineStr">
@@ -47662,7 +47662,7 @@
       </c>
       <c r="F930" s="12" t="inlineStr">
         <is>
-          <t>Fotografía de frente</t>
+          <t>Cómo se le avisa</t>
         </is>
       </c>
       <c r="G930" s="13" t="inlineStr"/>
@@ -47697,12 +47697,12 @@
       </c>
       <c r="C931" s="15" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Cómo se le avisa</t>
         </is>
       </c>
       <c r="D931" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E931" s="15" t="inlineStr">
@@ -47712,7 +47712,7 @@
       </c>
       <c r="F931" s="15" t="inlineStr">
         <is>
-          <t>De frente, con el rostro descubierto (sin lentes oscuros, gorra ni cubrebocas), fondo claro y buena luz. Tómela con la cámara de la computadora o cargue una. En el cotejo se confirma contra su identificación oficial.</t>
+          <t>Teléfono</t>
         </is>
       </c>
       <c r="G931" s="13" t="inlineStr"/>
@@ -47747,12 +47747,12 @@
       </c>
       <c r="C932" s="12" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Cómo se le avisa</t>
         </is>
       </c>
       <c r="D932" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E932" s="12" t="inlineStr">
@@ -47762,7 +47762,7 @@
       </c>
       <c r="F932" s="12" t="inlineStr">
         <is>
-          <t>Cargar una fotografía</t>
+          <t>Diez dígitos. Por aquí se le avisan su cita, su curso y sus resultados.</t>
         </is>
       </c>
       <c r="G932" s="13" t="inlineStr"/>
@@ -47797,22 +47797,22 @@
       </c>
       <c r="C933" s="15" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Cómo se le avisa</t>
         </is>
       </c>
       <c r="D933" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E933" s="15" t="inlineStr">
         <is>
-          <t>En teléfono o equipo con cámara</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F933" s="15" t="inlineStr">
         <is>
-          <t>Tomar fotografía</t>
+          <t>Correo electrónico (si tiene)</t>
         </is>
       </c>
       <c r="G933" s="13" t="inlineStr"/>
@@ -47847,12 +47847,12 @@
       </c>
       <c r="C934" s="12" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Cómo se le avisa</t>
         </is>
       </c>
       <c r="D934" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E934" s="12" t="inlineStr">
@@ -47862,7 +47862,7 @@
       </c>
       <c r="F934" s="12" t="inlineStr">
         <is>
-          <t>Usar la cámara de la computadora</t>
+          <t>Opcional. Si lo da, no puede ser el de otra cuenta.</t>
         </is>
       </c>
       <c r="G934" s="13" t="inlineStr"/>
@@ -47897,22 +47897,22 @@
       </c>
       <c r="C935" s="15" t="inlineStr">
         <is>
-          <t>Fotografía · Su fotografía</t>
+          <t>Datos · Su adscripción</t>
         </is>
       </c>
       <c r="D935" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E935" s="15" t="inlineStr">
         <is>
-          <t>Con la cámara de la computadora abierta</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F935" s="15" t="inlineStr">
         <is>
-          <t>Tomar la fotografía</t>
+          <t>Su adscripción</t>
         </is>
       </c>
       <c r="G935" s="13" t="inlineStr"/>
@@ -47930,7 +47930,7 @@
       </c>
       <c r="L935" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/asistido.html)</t>
+          <t>Fragmento de adscripción (herramientas/plantillas/adscripcion.html)</t>
         </is>
       </c>
     </row>
@@ -47952,17 +47952,17 @@
       </c>
       <c r="D936" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E936" s="12" t="inlineStr">
         <is>
-          <t>Con la cámara de la computadora abierta</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F936" s="12" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Su fotografía</t>
         </is>
       </c>
       <c r="G936" s="13" t="inlineStr"/>
@@ -48002,7 +48002,7 @@
       </c>
       <c r="D937" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E937" s="15" t="inlineStr">
@@ -48012,7 +48012,7 @@
       </c>
       <c r="F937" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Fotografía de frente</t>
         </is>
       </c>
       <c r="G937" s="13" t="inlineStr"/>
@@ -48052,7 +48052,7 @@
       </c>
       <c r="D938" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E938" s="12" t="inlineStr">
@@ -48062,7 +48062,7 @@
       </c>
       <c r="F938" s="12" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>De frente, con el rostro descubierto (sin lentes oscuros, gorra ni cubrebocas), fondo claro y buena luz. Tómela con la cámara de la computadora o cargue una. En el cotejo se confirma contra su identificación oficial.</t>
         </is>
       </c>
       <c r="G938" s="13" t="inlineStr"/>
@@ -48097,12 +48097,12 @@
       </c>
       <c r="C939" s="15" t="inlineStr">
         <is>
-          <t>Confirmar · Confirme los datos</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D939" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E939" s="15" t="inlineStr">
@@ -48112,7 +48112,7 @@
       </c>
       <c r="F939" s="15" t="inlineStr">
         <is>
-          <t>Confirme los datos</t>
+          <t>Cargar una fotografía</t>
         </is>
       </c>
       <c r="G939" s="13" t="inlineStr"/>
@@ -48147,22 +48147,22 @@
       </c>
       <c r="C940" s="12" t="inlineStr">
         <is>
-          <t>Confirmar · Confirme los datos</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D940" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E940" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>En teléfono o equipo con cámara</t>
         </is>
       </c>
       <c r="F940" s="12" t="inlineStr">
         <is>
-          <t>Léale a la persona sus datos. Si algo no está bien, cámbielo antes de registrarla. Después sigue directo su solicitud.</t>
+          <t>Tomar fotografía</t>
         </is>
       </c>
       <c r="G940" s="13" t="inlineStr"/>
@@ -48197,7 +48197,7 @@
       </c>
       <c r="C941" s="15" t="inlineStr">
         <is>
-          <t>Confirmar · Confirme los datos</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D941" s="15" t="inlineStr">
@@ -48212,7 +48212,7 @@
       </c>
       <c r="F941" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Usar la cámara de la computadora</t>
         </is>
       </c>
       <c r="G941" s="13" t="inlineStr"/>
@@ -48247,7 +48247,7 @@
       </c>
       <c r="C942" s="12" t="inlineStr">
         <is>
-          <t>Confirmar · Confirme los datos</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D942" s="12" t="inlineStr">
@@ -48257,12 +48257,12 @@
       </c>
       <c r="E942" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Con la cámara de la computadora abierta</t>
         </is>
       </c>
       <c r="F942" s="12" t="inlineStr">
         <is>
-          <t>Registrar y capturar su solicitud</t>
+          <t>Tomar la fotografía</t>
         </is>
       </c>
       <c r="G942" s="13" t="inlineStr"/>
@@ -48297,22 +48297,22 @@
       </c>
       <c r="C943" s="15" t="inlineStr">
         <is>
-          <t>Cuenta registrada</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D943" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E943" s="15" t="inlineStr">
         <is>
-          <t>Al enviar con éxito (acuse)</t>
+          <t>Con la cámara de la computadora abierta</t>
         </is>
       </c>
       <c r="F943" s="15" t="inlineStr">
         <is>
-          <t>Cuenta registrada</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="G943" s="13" t="inlineStr"/>
@@ -48347,22 +48347,22 @@
       </c>
       <c r="C944" s="12" t="inlineStr">
         <is>
-          <t>Cuenta registrada</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D944" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E944" s="12" t="inlineStr">
         <is>
-          <t>Al enviar con éxito (acuse)</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F944" s="12" t="inlineStr">
         <is>
-          <t>Sigue capturar su solicitud.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G944" s="13" t="inlineStr"/>
@@ -48397,7 +48397,7 @@
       </c>
       <c r="C945" s="15" t="inlineStr">
         <is>
-          <t>Cuenta registrada</t>
+          <t>Fotografía · Su fotografía</t>
         </is>
       </c>
       <c r="D945" s="15" t="inlineStr">
@@ -48407,12 +48407,12 @@
       </c>
       <c r="E945" s="15" t="inlineStr">
         <is>
-          <t>Al enviar con éxito (acuse)</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F945" s="15" t="inlineStr">
         <is>
-          <t>Capturar su solicitud</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G945" s="13" t="inlineStr"/>
@@ -48442,17 +48442,17 @@
       </c>
       <c r="B946" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C946" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Confirmar · Confirme los datos</t>
         </is>
       </c>
       <c r="D946" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E946" s="12" t="inlineStr">
@@ -48462,7 +48462,7 @@
       </c>
       <c r="F946" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal</t>
+          <t>Confirme los datos</t>
         </is>
       </c>
       <c r="G946" s="13" t="inlineStr"/>
@@ -48480,7 +48480,7 @@
       </c>
       <c r="L946" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48492,17 +48492,17 @@
       </c>
       <c r="B947" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C947" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Confirmar · Confirme los datos</t>
         </is>
       </c>
       <c r="D947" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E947" s="15" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="F947" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Léale a la persona sus datos. Si algo no está bien, cámbielo antes de registrarla. Después sigue directo su solicitud.</t>
         </is>
       </c>
       <c r="G947" s="13" t="inlineStr"/>
@@ -48530,7 +48530,7 @@
       </c>
       <c r="L947" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48542,17 +48542,17 @@
       </c>
       <c r="B948" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C948" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Confirmar · Confirme los datos</t>
         </is>
       </c>
       <c r="D948" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E948" s="12" t="inlineStr">
@@ -48562,7 +48562,7 @@
       </c>
       <c r="F948" s="12" t="inlineStr">
         <is>
-          <t>Busque a la persona y dígale en qué va su trámite. Lo de «Qué decirle» va escrito para ella: léaselo.</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G948" s="13" t="inlineStr"/>
@@ -48580,7 +48580,7 @@
       </c>
       <c r="L948" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48592,17 +48592,17 @@
       </c>
       <c r="B949" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C949" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Confirmar · Confirme los datos</t>
         </is>
       </c>
       <c r="D949" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E949" s="15" t="inlineStr">
@@ -48612,7 +48612,7 @@
       </c>
       <c r="F949" s="15" t="inlineStr">
         <is>
-          <t>CURP, nombre o folio</t>
+          <t>Registrar y capturar su solicitud</t>
         </is>
       </c>
       <c r="G949" s="13" t="inlineStr"/>
@@ -48630,7 +48630,7 @@
       </c>
       <c r="L949" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48642,27 +48642,27 @@
       </c>
       <c r="B950" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C950" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Cuenta registrada</t>
         </is>
       </c>
       <c r="D950" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E950" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Al enviar con éxito (acuse)</t>
         </is>
       </c>
       <c r="F950" s="12" t="inlineStr">
         <is>
-          <t>La CURP, el nombre (al menos 3 letras), el folio de su solicitud (APD-S-…) o su número de expediente (EXP-…).</t>
+          <t>Cuenta registrada</t>
         </is>
       </c>
       <c r="G950" s="13" t="inlineStr"/>
@@ -48680,7 +48680,7 @@
       </c>
       <c r="L950" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48692,27 +48692,27 @@
       </c>
       <c r="B951" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C951" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla</t>
+          <t>Cuenta registrada</t>
         </is>
       </c>
       <c r="D951" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E951" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Al enviar con éxito (acuse)</t>
         </is>
       </c>
       <c r="F951" s="15" t="inlineStr">
         <is>
-          <t>Escriba para buscar.</t>
+          <t>Sigue capturar su solicitud.</t>
         </is>
       </c>
       <c r="G951" s="13" t="inlineStr"/>
@@ -48730,7 +48730,7 @@
       </c>
       <c r="L951" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48742,27 +48742,27 @@
       </c>
       <c r="B952" s="12" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C952" s="12" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Cuenta registrada</t>
         </is>
       </c>
       <c r="D952" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E952" s="12" t="inlineStr">
         <is>
-          <t>Al pedirla o al cargar el acta corregida</t>
+          <t>Al enviar con éxito (acuse)</t>
         </is>
       </c>
       <c r="F952" s="12" t="inlineStr">
         <is>
-          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
+          <t>Capturar su solicitud</t>
         </is>
       </c>
       <c r="G952" s="13" t="inlineStr"/>
@@ -48775,12 +48775,12 @@
       <c r="J952" s="12" t="inlineStr"/>
       <c r="K952" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L952" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/asistido.html)</t>
         </is>
       </c>
     </row>
@@ -48792,27 +48792,27 @@
       </c>
       <c r="B953" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C953" s="15" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D953" s="15" t="inlineStr">
         <is>
-          <t>Pasos</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E953" s="15" t="inlineStr">
         <is>
-          <t>Al pedirla</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F953" s="15" t="inlineStr">
         <is>
-          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
+          <t>Inicio del personal</t>
         </is>
       </c>
       <c r="G953" s="13" t="inlineStr"/>
@@ -48825,12 +48825,12 @@
       <c r="J953" s="15" t="inlineStr"/>
       <c r="K953" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L953" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -48842,27 +48842,27 @@
       </c>
       <c r="B954" s="12" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C954" s="12" t="inlineStr">
         <is>
-          <t>Acreditación</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="D954" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E954" s="12" t="inlineStr">
         <is>
-          <t>Credencial del sistema que todavía no se entrega</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F954" s="12" t="inlineStr">
         <is>
-          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="G954" s="13" t="inlineStr"/>
@@ -48875,12 +48875,12 @@
       <c r="J954" s="12" t="inlineStr"/>
       <c r="K954" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L954" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -48892,17 +48892,17 @@
       </c>
       <c r="B955" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C955" s="15" t="inlineStr">
         <is>
-          <t>Cabecera</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="D955" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E955" s="15" t="inlineStr">
@@ -48912,7 +48912,7 @@
       </c>
       <c r="F955" s="15" t="inlineStr">
         <is>
-          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
+          <t>Busque a la persona y dígale en qué va su trámite. Lo de «Qué decirle» va escrito para ella: léaselo.</t>
         </is>
       </c>
       <c r="G955" s="13" t="inlineStr"/>
@@ -48930,7 +48930,7 @@
       </c>
       <c r="L955" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -48942,27 +48942,27 @@
       </c>
       <c r="B956" s="12" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C956" s="12" t="inlineStr">
         <is>
-          <t>Paso 1 · el curso</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="D956" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E956" s="12" t="inlineStr">
         <is>
-          <t>En cada curso</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F956" s="12" t="inlineStr">
         <is>
-          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
+          <t>CURP, nombre o folio</t>
         </is>
       </c>
       <c r="G956" s="13" t="inlineStr"/>
@@ -48980,7 +48980,7 @@
       </c>
       <c r="L956" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -48992,17 +48992,17 @@
       </c>
       <c r="B957" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C957" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · la semana</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="D957" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E957" s="15" t="inlineStr">
@@ -49012,7 +49012,7 @@
       </c>
       <c r="F957" s="15" t="inlineStr">
         <is>
-          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
+          <t>La CURP, el nombre (al menos 3 letras), el folio de su solicitud (APD-S-…) o su número de expediente (EXP-…).</t>
         </is>
       </c>
       <c r="G957" s="13" t="inlineStr"/>
@@ -49030,7 +49030,7 @@
       </c>
       <c r="L957" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -49042,27 +49042,27 @@
       </c>
       <c r="B958" s="12" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Ventanilla (personal)</t>
         </is>
       </c>
       <c r="C958" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · columna «Semana»</t>
+          <t>Ventanilla</t>
         </is>
       </c>
       <c r="D958" s="12" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E958" s="12" t="inlineStr">
         <is>
-          <t>Semana que se puede elegir</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F958" s="12" t="inlineStr">
         <is>
-          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
+          <t>Escriba para buscar.</t>
         </is>
       </c>
       <c r="G958" s="13" t="inlineStr"/>
@@ -49080,7 +49080,7 @@
       </c>
       <c r="L958" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -49092,27 +49092,27 @@
       </c>
       <c r="B959" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C959" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · columna «Semana»</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="D959" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E959" s="15" t="inlineStr">
         <is>
-          <t>Semana que no se puede elegir</t>
+          <t>Al pedirla o al cargar el acta corregida</t>
         </is>
       </c>
       <c r="F959" s="15" t="inlineStr">
         <is>
-          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
+          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
         </is>
       </c>
       <c r="G959" s="13" t="inlineStr"/>
@@ -49125,12 +49125,12 @@
       <c r="J959" s="15" t="inlineStr"/>
       <c r="K959" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L959" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -49142,27 +49142,27 @@
       </c>
       <c r="B960" s="12" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C960" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · calendario</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="D960" s="12" t="inlineStr">
         <is>
-          <t>Etiqueta</t>
+          <t>Pasos</t>
         </is>
       </c>
       <c r="E960" s="12" t="inlineStr">
         <is>
-          <t>En los días</t>
+          <t>Al pedirla</t>
         </is>
       </c>
       <c r="F960" s="12" t="inlineStr">
         <is>
-          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
+          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
         </is>
       </c>
       <c r="G960" s="13" t="inlineStr"/>
@@ -49175,12 +49175,12 @@
       <c r="J960" s="12" t="inlineStr"/>
       <c r="K960" s="14" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L960" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -49192,27 +49192,27 @@
       </c>
       <c r="B961" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C961" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · semana elegida</t>
+          <t>Acreditación</t>
         </is>
       </c>
       <c r="D961" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E961" s="15" t="inlineStr">
         <is>
-          <t>Con una semana elegida</t>
+          <t>Credencial del sistema que todavía no se entrega</t>
         </is>
       </c>
       <c r="F961" s="15" t="inlineStr">
         <is>
-          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
+          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
         </is>
       </c>
       <c r="G961" s="13" t="inlineStr"/>
@@ -49225,12 +49225,12 @@
       <c r="J961" s="15" t="inlineStr"/>
       <c r="K961" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L961" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -49247,7 +49247,7 @@
       </c>
       <c r="C962" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · semana elegida</t>
+          <t>Cabecera</t>
         </is>
       </c>
       <c r="D962" s="12" t="inlineStr">
@@ -49257,12 +49257,12 @@
       </c>
       <c r="E962" s="12" t="inlineStr">
         <is>
-          <t>Sin semana</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F962" s="12" t="inlineStr">
         <is>
-          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
+          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
         </is>
       </c>
       <c r="G962" s="13" t="inlineStr"/>
@@ -49297,22 +49297,22 @@
       </c>
       <c r="C963" s="15" t="inlineStr">
         <is>
-          <t>Paso 2</t>
+          <t>Paso 1 · el curso</t>
         </is>
       </c>
       <c r="D963" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E963" s="15" t="inlineStr">
         <is>
-          <t>Siguiente sin semana</t>
+          <t>En cada curso</t>
         </is>
       </c>
       <c r="F963" s="15" t="inlineStr">
         <is>
-          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
+          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
         </is>
       </c>
       <c r="G963" s="13" t="inlineStr"/>
@@ -49347,22 +49347,22 @@
       </c>
       <c r="C964" s="12" t="inlineStr">
         <is>
-          <t>Paso 2</t>
+          <t>Paso 2 · la semana</t>
         </is>
       </c>
       <c r="D964" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E964" s="12" t="inlineStr">
         <is>
-          <t>Al tocar un día que no se puede</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F964" s="12" t="inlineStr">
         <is>
-          <t>El DÍA no se puede: RAZÓN.</t>
+          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
         </is>
       </c>
       <c r="G964" s="13" t="inlineStr"/>
@@ -49397,22 +49397,22 @@
       </c>
       <c r="C965" s="15" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 2 · columna «Semana»</t>
         </is>
       </c>
       <c r="D965" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E965" s="15" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Semana que se puede elegir</t>
         </is>
       </c>
       <c r="F965" s="15" t="inlineStr">
         <is>
-          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
+          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
         </is>
       </c>
       <c r="G965" s="13" t="inlineStr"/>
@@ -49447,22 +49447,22 @@
       </c>
       <c r="C966" s="12" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 2 · columna «Semana»</t>
         </is>
       </c>
       <c r="D966" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E966" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Semana que no se puede elegir</t>
         </is>
       </c>
       <c r="F966" s="12" t="inlineStr">
         <is>
-          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
+          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
         </is>
       </c>
       <c r="G966" s="13" t="inlineStr"/>
@@ -49497,22 +49497,22 @@
       </c>
       <c r="C967" s="15" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 2 · calendario</t>
         </is>
       </c>
       <c r="D967" s="15" t="inlineStr">
         <is>
-          <t>Plegable</t>
+          <t>Etiqueta</t>
         </is>
       </c>
       <c r="E967" s="15" t="inlineStr">
         <is>
-          <t>Con más en espera que las propuestas</t>
+          <t>En los días</t>
         </is>
       </c>
       <c r="F967" s="15" t="inlineStr">
         <is>
-          <t>Cambiar a quiénes van (N más en espera)</t>
+          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
         </is>
       </c>
       <c r="G967" s="13" t="inlineStr"/>
@@ -49547,22 +49547,22 @@
       </c>
       <c r="C968" s="12" t="inlineStr">
         <is>
-          <t>Paso 3</t>
+          <t>Paso 2 · semana elegida</t>
         </is>
       </c>
       <c r="D968" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E968" s="12" t="inlineStr">
         <is>
-          <t>Siguiente sin nadie</t>
+          <t>Con una semana elegida</t>
         </is>
       </c>
       <c r="F968" s="12" t="inlineStr">
         <is>
-          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
+          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
         </is>
       </c>
       <c r="G968" s="13" t="inlineStr"/>
@@ -49597,22 +49597,22 @@
       </c>
       <c r="C969" s="15" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Paso 2 · semana elegida</t>
         </is>
       </c>
       <c r="D969" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E969" s="15" t="inlineStr">
         <is>
-          <t>Antes de crearlo</t>
+          <t>Sin semana</t>
         </is>
       </c>
       <c r="F969" s="15" t="inlineStr">
         <is>
-          <t>Se crea por confirmar / Sigue por confirmar · Le falta: …; después, el área de Instructores y Capacitación le asigna la persona instructora y lo confirma. Lo puede completar en «Grupos programados» o en su ficha; mientras, las personas no ven la fecha como segura.</t>
+          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
         </is>
       </c>
       <c r="G969" s="13" t="inlineStr"/>
@@ -49647,22 +49647,22 @@
       </c>
       <c r="C970" s="12" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Paso 2</t>
         </is>
       </c>
       <c r="D970" s="12" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E970" s="12" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Siguiente sin semana</t>
         </is>
       </c>
       <c r="F970" s="12" t="inlineStr">
         <is>
-          <t>Crear el grupo</t>
+          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
         </is>
       </c>
       <c r="G970" s="13" t="inlineStr"/>
@@ -49697,22 +49697,22 @@
       </c>
       <c r="C971" s="15" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Paso 2</t>
         </is>
       </c>
       <c r="D971" s="15" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E971" s="15" t="inlineStr">
         <is>
-          <t>Grupo que ya existe</t>
+          <t>Al tocar un día que no se puede</t>
         </is>
       </c>
       <c r="F971" s="15" t="inlineStr">
         <is>
-          <t>Guardar los cambios / Agregar al grupo (confirmado)</t>
+          <t>El DÍA no se puede: RAZÓN.</t>
         </is>
       </c>
       <c r="G971" s="13" t="inlineStr"/>
@@ -49747,22 +49747,22 @@
       </c>
       <c r="C972" s="12" t="inlineStr">
         <is>
-          <t>Paso 4 · resumen</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D972" s="12" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E972" s="12" t="inlineStr">
         <is>
-          <t>Grupo sin persona instructora</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F972" s="12" t="inlineStr">
         <is>
-          <t>Persona instructora · La asigna el área de Instructores y Capacitación</t>
+          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
         </is>
       </c>
       <c r="G972" s="13" t="inlineStr"/>
@@ -49797,22 +49797,22 @@
       </c>
       <c r="C973" s="15" t="inlineStr">
         <is>
-          <t>Paso 1 · tipo de grupo</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D973" s="15" t="inlineStr">
         <is>
-          <t>Ayuda (cambia)</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E973" s="15" t="inlineStr">
         <is>
-          <t>Elegidas de una organización que no es de gobierno</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F973" s="15" t="inlineStr">
         <is>
-          <t>NOMBRE no es una institución de gobierno: su gente va a un grupo combinado. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio.</t>
+          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
         </is>
       </c>
       <c r="G973" s="13" t="inlineStr"/>
@@ -49847,22 +49847,22 @@
       </c>
       <c r="C974" s="12" t="inlineStr">
         <is>
-          <t>Paso 1 · tipo de grupo</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D974" s="12" t="inlineStr">
         <is>
-          <t>Ayuda (cambia)</t>
+          <t>Plegable</t>
         </is>
       </c>
       <c r="E974" s="12" t="inlineStr">
         <is>
-          <t>Elegidas de varias organizaciones o independientes</t>
+          <t>Con más en espera que las propuestas</t>
         </is>
       </c>
       <c r="F974" s="12" t="inlineStr">
         <is>
-          <t>El grupo es combinado: las elegidas son de varias organizaciones o independientes. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio, con toda su gente.</t>
+          <t>Cambiar a quiénes van (N más en espera)</t>
         </is>
       </c>
       <c r="G974" s="13" t="inlineStr"/>
@@ -49897,7 +49897,7 @@
       </c>
       <c r="C975" s="15" t="inlineStr">
         <is>
-          <t>Paso 4</t>
+          <t>Paso 3</t>
         </is>
       </c>
       <c r="D975" s="15" t="inlineStr">
@@ -49907,12 +49907,12 @@
       </c>
       <c r="E975" s="15" t="inlineStr">
         <is>
-          <t>Grupo propio de quien no es de gobierno</t>
+          <t>Siguiente sin nadie</t>
         </is>
       </c>
       <c r="F975" s="15" t="inlineStr">
         <is>
-          <t>Un grupo propio es sólo de una institución de gobierno, con toda su gente. Elija «Combinado» o quite a quien no sea de esa institución.</t>
+          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
         </is>
       </c>
       <c r="G975" s="13" t="inlineStr"/>
@@ -49947,22 +49947,22 @@
       </c>
       <c r="C976" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D976" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E976" s="12" t="inlineStr">
         <is>
-          <t>Al crear un grupo</t>
+          <t>Antes de crearlo</t>
         </is>
       </c>
       <c r="F976" s="12" t="inlineStr">
         <is>
-          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
+          <t>Se crea por confirmar / Sigue por confirmar · Le falta: …; después, el área de Instructores y Capacitación le asigna la persona instructora y lo confirma. Lo puede completar en «Grupos programados» o en su ficha; mientras, las personas no ven la fecha como segura.</t>
         </is>
       </c>
       <c r="G976" s="13" t="inlineStr"/>
@@ -49997,22 +49997,22 @@
       </c>
       <c r="C977" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D977" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E977" s="15" t="inlineStr">
         <is>
-          <t>Situación de cada grupo</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F977" s="15" t="inlineStr">
         <is>
-          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
+          <t>Crear el grupo</t>
         </is>
       </c>
       <c r="G977" s="13" t="inlineStr"/>
@@ -50047,22 +50047,22 @@
       </c>
       <c r="C978" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D978" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E978" s="12" t="inlineStr">
         <is>
-          <t>Acciones de cada grupo</t>
+          <t>Grupo que ya existe</t>
         </is>
       </c>
       <c r="F978" s="12" t="inlineStr">
         <is>
-          <t>Completar con las N que más esperan · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
+          <t>Guardar los cambios / Agregar al grupo (confirmado)</t>
         </is>
       </c>
       <c r="G978" s="13" t="inlineStr"/>
@@ -50097,22 +50097,22 @@
       </c>
       <c r="C979" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Paso 4 · resumen</t>
         </is>
       </c>
       <c r="D979" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E979" s="15" t="inlineStr">
         <is>
-          <t>Lo que falta</t>
+          <t>Grupo sin persona instructora</t>
         </is>
       </c>
       <c r="F979" s="15" t="inlineStr">
         <is>
-          <t>Semana, N personas, hora y persona instructora / Que Capacitación lo confirme / —</t>
+          <t>Persona instructora · La asigna el área de Instructores y Capacitación</t>
         </is>
       </c>
       <c r="G979" s="13" t="inlineStr"/>
@@ -50142,27 +50142,27 @@
       </c>
       <c r="B980" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C980" s="12" t="inlineStr">
         <is>
-          <t>Datos de la persona</t>
+          <t>Paso 1 · tipo de grupo</t>
         </is>
       </c>
       <c r="D980" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Ayuda (cambia)</t>
         </is>
       </c>
       <c r="E980" s="12" t="inlineStr">
         <is>
-          <t>CURP de una persona menor de edad</t>
+          <t>Elegidas de una organización que no es de gobierno</t>
         </is>
       </c>
       <c r="F980" s="12" t="inlineStr">
         <is>
-          <t>Según su CURP, la persona todavía no tiene 18 años cumplidos: no se puede registrar ni solicitar una acreditación.</t>
+          <t>NOMBRE no es una institución de gobierno: su gente va a un grupo combinado. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio.</t>
         </is>
       </c>
       <c r="G980" s="13" t="inlineStr"/>
@@ -50180,7 +50180,7 @@
       </c>
       <c r="L980" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/cruzadas-propias.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50192,27 +50192,27 @@
       </c>
       <c r="B981" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C981" s="15" t="inlineStr">
         <is>
-          <t>Fotografía</t>
+          <t>Paso 1 · tipo de grupo</t>
         </is>
       </c>
       <c r="D981" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Ayuda (cambia)</t>
         </is>
       </c>
       <c r="E981" s="15" t="inlineStr">
         <is>
-          <t>Sin cámara o sin permiso</t>
+          <t>Elegidas de varias organizaciones o independientes</t>
         </is>
       </c>
       <c r="F981" s="15" t="inlineStr">
         <is>
-          <t>Esta computadora no deja usar la cámara · Cargue una fotografía con «Cargar una fotografía». / No se pudo usar la cámara · Revise que la computadora tenga cámara y que el navegador tenga permiso de usarla, o cargue una fotografía.</t>
+          <t>El grupo es combinado: las elegidas son de varias organizaciones o independientes. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio, con toda su gente.</t>
         </is>
       </c>
       <c r="G981" s="13" t="inlineStr"/>
@@ -50230,7 +50230,7 @@
       </c>
       <c r="L981" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/asistido.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50242,27 +50242,27 @@
       </c>
       <c r="B982" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C982" s="12" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Paso 4</t>
         </is>
       </c>
       <c r="D982" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E982" s="12" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>Grupo propio de quien no es de gobierno</t>
         </is>
       </c>
       <c r="F982" s="12" t="inlineStr">
         <is>
-          <t>Aviso de privacidad: Se le leyó y lo aceptó · Correo electrónico: No tiene (es opcional) · Cambiar</t>
+          <t>Un grupo propio es sólo de una institución de gobierno, con toda su gente. Elija «Combinado» o quite a quien no sea de esa institución.</t>
         </is>
       </c>
       <c r="G982" s="13" t="inlineStr"/>
@@ -50280,7 +50280,7 @@
       </c>
       <c r="L982" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/asistido.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50292,27 +50292,27 @@
       </c>
       <c r="B983" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C983" s="15" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D983" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E983" s="15" t="inlineStr">
         <is>
-          <t>CURP ya registrada</t>
+          <t>Al crear un grupo</t>
         </is>
       </c>
       <c r="F983" s="15" t="inlineStr">
         <is>
-          <t>No se registró la cuenta. Ya hay una cuenta con esta CURP. Busque a la persona en la ventanilla para ver en qué va su trámite. / Esta CURP está en el registro anterior de la Secretaría (Kobo). Cómo se registra con ayuda a una persona del registro anterior está por decidir (P208).</t>
+          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
         </is>
       </c>
       <c r="G983" s="13" t="inlineStr"/>
@@ -50330,7 +50330,7 @@
       </c>
       <c r="L983" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/config-asistido.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50342,27 +50342,27 @@
       </c>
       <c r="B984" s="12" t="inlineStr">
         <is>
-          <t>Registro asistido (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C984" s="12" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D984" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E984" s="12" t="inlineStr">
         <is>
-          <t>Correo de otra cuenta</t>
+          <t>Situación de cada grupo</t>
         </is>
       </c>
       <c r="F984" s="12" t="inlineStr">
         <is>
-          <t>Este correo ya está registrado en otra cuenta. Escriba otro o déjelo vacío.</t>
+          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
         </is>
       </c>
       <c r="G984" s="13" t="inlineStr"/>
@@ -50380,7 +50380,7 @@
       </c>
       <c r="L984" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/config-asistido.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50392,27 +50392,27 @@
       </c>
       <c r="B985" s="15" t="inlineStr">
         <is>
-          <t>Solicitud (registro asistido)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C985" s="15" t="inlineStr">
         <is>
-          <t>Paso 1</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D985" s="15" t="inlineStr">
         <is>
-          <t>Texto (cambia)</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E985" s="15" t="inlineStr">
         <is>
-          <t>Adscripción en el registro asistido</t>
+          <t>Acciones de cada grupo</t>
         </is>
       </c>
       <c r="F985" s="15" t="inlineStr">
         <is>
-          <t>La solicitud se envía con la que se capturó al registrar a la persona en el Vivero.</t>
+          <t>Completar con las N que más esperan · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
         </is>
       </c>
       <c r="G985" s="13" t="inlineStr"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="L985" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/solicitud.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50442,27 +50442,27 @@
       </c>
       <c r="B986" s="12" t="inlineStr">
         <is>
-          <t>Solicitud (registro asistido)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C986" s="12" t="inlineStr">
         <is>
-          <t>Acuse</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D986" s="12" t="inlineStr">
         <is>
-          <t>Secuencia</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E986" s="12" t="inlineStr">
         <is>
-          <t>Solicitud capturada por el personal</t>
+          <t>Lo que falta</t>
         </is>
       </c>
       <c r="F986" s="12" t="inlineStr">
         <is>
-          <t>La Secretaría revisa tus documentos. · Te avisamos por teléfono: si falta algo, vienes a la ventanilla y lo corregimos contigo; si todo está completo, te damos una cita de cotejo. · Después de la cita, la Secretaría te asigna un grupo del curso y te avisamos las fechas por teléfono. El curso es de 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. (o: El curso es de un día y ese mismo día presentas el examen.) · Para preguntar en qué va tu trámite, ven a la ventanilla con tu folio.</t>
+          <t>Semana, N personas, hora y persona instructora / Que Capacitación lo confirme / —</t>
         </is>
       </c>
       <c r="G986" s="13" t="inlineStr"/>
@@ -50480,7 +50480,7 @@
       </c>
       <c r="L986" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/solicitud.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -50492,27 +50492,27 @@
       </c>
       <c r="B987" s="15" t="inlineStr">
         <is>
-          <t>Solicitud (registro asistido)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C987" s="15" t="inlineStr">
         <is>
-          <t>Acuse de una corrección</t>
+          <t>Datos de la persona</t>
         </is>
       </c>
       <c r="D987" s="15" t="inlineStr">
         <is>
-          <t>Secuencia</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E987" s="15" t="inlineStr">
         <is>
-          <t>Corrección cargada por el personal</t>
+          <t>CURP de una persona menor de edad</t>
         </is>
       </c>
       <c r="F987" s="15" t="inlineStr">
         <is>
-          <t>Si todavía falta algo, te avisamos por teléfono y lo corregimos contigo en la ventanilla.</t>
+          <t>Según su CURP, la persona todavía no tiene 18 años cumplidos: no se puede registrar ni solicitar una acreditación.</t>
         </is>
       </c>
       <c r="G987" s="13" t="inlineStr"/>
@@ -50530,7 +50530,7 @@
       </c>
       <c r="L987" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/solicitud.js)</t>
+          <t>Código del sitio (sitio/app/cruzadas-propias.js)</t>
         </is>
       </c>
     </row>
@@ -50542,27 +50542,27 @@
       </c>
       <c r="B988" s="12" t="inlineStr">
         <is>
-          <t>Solicitud (registro asistido)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C988" s="12" t="inlineStr">
         <is>
-          <t>Hoja para imprimir</t>
+          <t>Fotografía</t>
         </is>
       </c>
       <c r="D988" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E988" s="12" t="inlineStr">
         <is>
-          <t>Al imprimir el acuse</t>
+          <t>Sin cámara o sin permiso</t>
         </is>
       </c>
       <c r="F988" s="12" t="inlineStr">
         <is>
-          <t>Folio · Fecha · Nombre · Acreditación · Teléfono de informes: Pendiente (P132) · Pregunta por tu trámite en la ventanilla del SEDE, DIRECCIÓN, HORARIO. Lleva este acuse con tu folio.</t>
+          <t>Esta computadora no deja usar la cámara · Cargue una fotografía con «Cargar una fotografía». / No se pudo usar la cámara · Revise que la computadora tenga cámara y que el navegador tenga permiso de usarla, o cargue una fotografía.</t>
         </is>
       </c>
       <c r="G988" s="13" t="inlineStr"/>
@@ -50580,7 +50580,7 @@
       </c>
       <c r="L988" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/solicitud.js)</t>
+          <t>Código del sitio (sitio/app/asistido.js)</t>
         </is>
       </c>
     </row>
@@ -50592,27 +50592,27 @@
       </c>
       <c r="B989" s="15" t="inlineStr">
         <is>
-          <t>Solicitud (registro asistido)</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C989" s="15" t="inlineStr">
         <is>
-          <t>Solicitud</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D989" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E989" s="15" t="inlineStr">
         <is>
-          <t>Persona que no es del registro asistido</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="F989" s="15" t="inlineStr">
         <is>
-          <t>No encontramos a esta persona entre las registradas en el Vivero (registro asistido). Búsquela en la ventanilla.</t>
+          <t>Aviso de privacidad: Se le leyó y lo aceptó · Correo electrónico: No tiene (es opcional) · Cambiar</t>
         </is>
       </c>
       <c r="G989" s="13" t="inlineStr"/>
@@ -50630,7 +50630,7 @@
       </c>
       <c r="L989" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/solicitud.js)</t>
+          <t>Código del sitio (sitio/app/asistido.js)</t>
         </is>
       </c>
     </row>
@@ -50642,27 +50642,27 @@
       </c>
       <c r="B990" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C990" s="12" t="inlineStr">
         <is>
-          <t>Lista</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D990" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E990" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>CURP ya registrada</t>
         </is>
       </c>
       <c r="F990" s="12" t="inlineStr">
         <is>
-          <t>N avisos pendientes, del más antiguo al más reciente. / No hay avisos por teléfono pendientes.</t>
+          <t>No se registró la cuenta. Ya hay una cuenta con esta CURP. Busque a la persona en la ventanilla para ver en qué va su trámite. / Esta CURP está en el registro anterior de la Secretaría (Kobo). Cómo se registra con ayuda a una persona del registro anterior está por decidir (P208).</t>
         </is>
       </c>
       <c r="G990" s="13" t="inlineStr"/>
@@ -50680,7 +50680,7 @@
       </c>
       <c r="L990" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/config-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -50692,27 +50692,27 @@
       </c>
       <c r="B991" s="15" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Registro asistido (personal)</t>
         </is>
       </c>
       <c r="C991" s="15" t="inlineStr">
         <is>
-          <t>Cada aviso</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D991" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E991" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Correo de otra cuenta</t>
         </is>
       </c>
       <c r="F991" s="15" t="inlineStr">
         <is>
-          <t>NOMBRE · teléfono · TÍTULO · Solicitud FOLIO · Desde el DD/MM/AAAA HH:MM · Qué decirle: Hola, te llamamos de la Secretaría del Medio Ambiente. … · Se le avisó · No contestó</t>
+          <t>Este correo ya está registrado en otra cuenta. Escriba otro o déjelo vacío.</t>
         </is>
       </c>
       <c r="G991" s="13" t="inlineStr"/>
@@ -50730,7 +50730,7 @@
       </c>
       <c r="L991" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/config-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -50742,27 +50742,27 @@
       </c>
       <c r="B992" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Solicitud (registro asistido)</t>
         </is>
       </c>
       <c r="C992" s="12" t="inlineStr">
         <is>
-          <t>Cada aviso</t>
+          <t>Paso 1</t>
         </is>
       </c>
       <c r="D992" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Texto (cambia)</t>
         </is>
       </c>
       <c r="E992" s="12" t="inlineStr">
         <is>
-          <t>Según el aviso</t>
+          <t>Adscripción en el registro asistido</t>
         </is>
       </c>
       <c r="F992" s="12" t="inlineStr">
         <is>
-          <t>Solicitud con observaciones · Cerrada por no corregir a tiempo · Cita de cotejo · Solicitud rechazada · Cerrada: sin más oportunidades de corrección · Resultado de la cita de cotejo · Cuenta bloqueada por identidad · Grupo asignado · Cambio en su grupo · Resultado del examen · Acreditación entregada · Acreditación cancelada · Reposición de la credencial</t>
+          <t>La solicitud se envía con la que se capturó al registrar a la persona en el Vivero.</t>
         </is>
       </c>
       <c r="G992" s="13" t="inlineStr"/>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="L992" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/solicitud.js)</t>
         </is>
       </c>
     </row>
@@ -50792,27 +50792,27 @@
       </c>
       <c r="B993" s="15" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Solicitud (registro asistido)</t>
         </is>
       </c>
       <c r="C993" s="15" t="inlineStr">
         <is>
-          <t>Qué decirle (de tú)</t>
+          <t>Acuse</t>
         </is>
       </c>
       <c r="D993" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Secuencia</t>
         </is>
       </c>
       <c r="E993" s="15" t="inlineStr">
         <is>
-          <t>Con observaciones</t>
+          <t>Solicitud capturada por el personal</t>
         </is>
       </c>
       <c r="F993" s="15" t="inlineStr">
         <is>
-          <t>A tu solicitud FOLIO le falta corregir algo: DOCUMENTOS. Ven a la ventanilla del SEDE, HORARIO, para que te digamos qué falta y lo corrijamos contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. / Esta es tu última oportunidad para corregir. Si en la revisión siguen las observaciones, tu solicitud se cierra y tienes que iniciar una nueva.</t>
+          <t>La Secretaría revisa tus documentos. · Te avisamos por teléfono: si falta algo, vienes a la ventanilla y lo corregimos contigo; si todo está completo, te damos una cita de cotejo. · Después de la cita, la Secretaría te asigna un grupo del curso y te avisamos las fechas por teléfono. El curso es de 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. (o: El curso es de un día y ese mismo día presentas el examen.) · Para preguntar en qué va tu trámite, ven a la ventanilla con tu folio.</t>
         </is>
       </c>
       <c r="G993" s="13" t="inlineStr"/>
@@ -50830,7 +50830,7 @@
       </c>
       <c r="L993" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/solicitud.js)</t>
         </is>
       </c>
     </row>
@@ -50842,27 +50842,27 @@
       </c>
       <c r="B994" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Solicitud (registro asistido)</t>
         </is>
       </c>
       <c r="C994" s="12" t="inlineStr">
         <is>
-          <t>Qué decirle (de tú)</t>
+          <t>Acuse de una corrección</t>
         </is>
       </c>
       <c r="D994" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Secuencia</t>
         </is>
       </c>
       <c r="E994" s="12" t="inlineStr">
         <is>
-          <t>Cerrada al agotar las oportunidades de corrección</t>
+          <t>Corrección cargada por el personal</t>
         </is>
       </c>
       <c r="F994" s="12" t="inlineStr">
         <is>
-          <t>Tu solicitud FOLIO se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva en la ventanilla del SEDE, HORARIO.</t>
+          <t>Si todavía falta algo, te avisamos por teléfono y lo corregimos contigo en la ventanilla.</t>
         </is>
       </c>
       <c r="G994" s="13" t="inlineStr"/>
@@ -50880,7 +50880,7 @@
       </c>
       <c r="L994" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/solicitud.js)</t>
         </is>
       </c>
     </row>
@@ -50892,12 +50892,12 @@
       </c>
       <c r="B995" s="15" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Solicitud (registro asistido)</t>
         </is>
       </c>
       <c r="C995" s="15" t="inlineStr">
         <is>
-          <t>Qué decirle (de tú)</t>
+          <t>Hoja para imprimir</t>
         </is>
       </c>
       <c r="D995" s="15" t="inlineStr">
@@ -50907,12 +50907,12 @@
       </c>
       <c r="E995" s="15" t="inlineStr">
         <is>
-          <t>Cita de cotejo</t>
+          <t>Al imprimir el acuse</t>
         </is>
       </c>
       <c r="F995" s="15" t="inlineStr">
         <is>
-          <t>Tus documentos están completos. Tu cita de cotejo es el DÍA a las HH:MM, en el SEDE. Lleva los mismos documentos impresos, tu identificación oficial y el comprobante del pago de $MONTO con la referencia REFERENCIA.</t>
+          <t>Folio · Fecha · Nombre · Acreditación · Teléfono de informes: Pendiente (P132) · Pregunta por tu trámite en la ventanilla del SEDE, DIRECCIÓN, HORARIO. Lleva este acuse con tu folio.</t>
         </is>
       </c>
       <c r="G995" s="13" t="inlineStr"/>
@@ -50930,7 +50930,7 @@
       </c>
       <c r="L995" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/solicitud.js)</t>
         </is>
       </c>
     </row>
@@ -50942,27 +50942,27 @@
       </c>
       <c r="B996" s="12" t="inlineStr">
         <is>
-          <t>Inicio del personal · avisos por teléfono</t>
+          <t>Solicitud (registro asistido)</t>
         </is>
       </c>
       <c r="C996" s="12" t="inlineStr">
         <is>
-          <t>Qué decirle (de tú)</t>
+          <t>Solicitud</t>
         </is>
       </c>
       <c r="D996" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E996" s="12" t="inlineStr">
         <is>
-          <t>Resultado de la cita</t>
+          <t>Persona que no es del registro asistido</t>
         </is>
       </c>
       <c r="F996" s="12" t="inlineStr">
         <is>
-          <t>Tu cotejo terminó; tu expediente es el EXP-… / En tu cita faltó un documento: …; tráelo hoy mismo … / En tu cita, un documento no coincidió … / Como no llegaste a tu cita (o no llevaste el comprobante de pago), te dimos una cita nueva: … / Tu solicitud FOLIO se cerró porque no llegaste dos veces a tu cita de cotejo.</t>
+          <t>No encontramos a esta persona entre las registradas en el Vivero (registro asistido). Búsquela en la ventanilla.</t>
         </is>
       </c>
       <c r="G996" s="13" t="inlineStr"/>
@@ -50980,7 +50980,7 @@
       </c>
       <c r="L996" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+          <t>Código del sitio (sitio/app/solicitud.js)</t>
         </is>
       </c>
     </row>
@@ -50997,7 +50997,7 @@
       </c>
       <c r="C997" s="15" t="inlineStr">
         <is>
-          <t>Qué decirle (de tú)</t>
+          <t>Lista</t>
         </is>
       </c>
       <c r="D997" s="15" t="inlineStr">
@@ -51007,12 +51007,12 @@
       </c>
       <c r="E997" s="15" t="inlineStr">
         <is>
-          <t>Otros avisos</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F997" s="15" t="inlineStr">
         <is>
-          <t>Cerrada sin corregir · Rechazada (con el motivo) · Cuenta bloqueada · Grupo asignado (día, hora, sede y duración: Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Es un solo día y ese mismo día presentas el examen.) · Baja, cambio o grupo por confirmar · Resultado del examen · Acreditación entregada o cancelada · Reposición de la credencial</t>
+          <t>N avisos pendientes, del más antiguo al más reciente. / No hay avisos por teléfono pendientes.</t>
         </is>
       </c>
       <c r="G997" s="13" t="inlineStr"/>
@@ -51047,22 +51047,22 @@
       </c>
       <c r="C998" s="12" t="inlineStr">
         <is>
-          <t>Al registrar</t>
+          <t>Cada aviso</t>
         </is>
       </c>
       <c r="D998" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E998" s="12" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F998" s="12" t="inlineStr">
         <is>
-          <t>Se registró que se le avisó · NOMBRE: aviso hecho. / Se registró que no contestó · NOMBRE no contestó. Lo que se le iba a decir se le dice cuando vaya a la ventanilla. / Ya estaba registrado · Otra persona del personal ya registró el aviso de NOMBRE.</t>
+          <t>NOMBRE · teléfono · TÍTULO · Solicitud FOLIO · Desde el DD/MM/AAAA HH:MM · Qué decirle: Hola, te llamamos de la Secretaría del Medio Ambiente. … · Se le avisó · No contestó</t>
         </is>
       </c>
       <c r="G998" s="13" t="inlineStr"/>
@@ -51092,27 +51092,27 @@
       </c>
       <c r="B999" s="15" t="inlineStr">
         <is>
-          <t>Revisar una solicitud y Cita de cotejo (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C999" s="15" t="inlineStr">
         <is>
-          <t>Cabecera</t>
+          <t>Cada aviso</t>
         </is>
       </c>
       <c r="D999" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E999" s="15" t="inlineStr">
         <is>
-          <t>Persona del registro asistido sin activar</t>
+          <t>Según el aviso</t>
         </is>
       </c>
       <c r="F999" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido: avisar por teléfono, 55 1234 5678</t>
+          <t>Solicitud con observaciones · Cerrada por no corregir a tiempo · Cita de cotejo · Solicitud rechazada · Cerrada: sin más oportunidades de corrección · Resultado de la cita de cotejo · Cuenta bloqueada por identidad · Grupo asignado · Cambio en su grupo · Resultado del examen · Acreditación entregada · Acreditación cancelada · Reposición de la credencial</t>
         </is>
       </c>
       <c r="G999" s="13" t="inlineStr"/>
@@ -51142,12 +51142,12 @@
       </c>
       <c r="B1000" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C1000" s="12" t="inlineStr">
         <is>
-          <t>Búsqueda</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1000" s="12" t="inlineStr">
@@ -51157,12 +51157,12 @@
       </c>
       <c r="E1000" s="12" t="inlineStr">
         <is>
-          <t>Al buscar</t>
+          <t>Con observaciones</t>
         </is>
       </c>
       <c r="F1000" s="12" t="inlineStr">
         <is>
-          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
+          <t>A tu solicitud FOLIO le falta corregir algo: DOCUMENTOS. Ven a la ventanilla del SEDE, HORARIO, para que te digamos qué falta y lo corrijamos contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. / Esta es tu última oportunidad para corregir. Si en la revisión siguen las observaciones, tu solicitud se cierra y tienes que iniciar una nueva.</t>
         </is>
       </c>
       <c r="G1000" s="13" t="inlineStr"/>
@@ -51180,7 +51180,7 @@
       </c>
       <c r="L1000" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -51192,27 +51192,27 @@
       </c>
       <c r="B1001" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C1001" s="15" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1001" s="15" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E1001" s="15" t="inlineStr">
         <is>
-          <t>Según la cuenta</t>
+          <t>Cerrada al agotar las oportunidades de corrección</t>
         </is>
       </c>
       <c r="F1001" s="15" t="inlineStr">
         <is>
-          <t>Registro asistido · avisos por teléfono / Registro asistido · ya activó su cuenta / Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
+          <t>Tu solicitud FOLIO se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva en la ventanilla del SEDE, HORARIO.</t>
         </is>
       </c>
       <c r="G1001" s="13" t="inlineStr"/>
@@ -51230,7 +51230,7 @@
       </c>
       <c r="L1001" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -51242,27 +51242,27 @@
       </c>
       <c r="B1002" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C1002" s="12" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1002" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E1002" s="12" t="inlineStr">
         <is>
-          <t>Con avisos por teléfono pendientes</t>
+          <t>Cita de cotejo</t>
         </is>
       </c>
       <c r="F1002" s="12" t="inlineStr">
         <is>
-          <t>Tiene un aviso por teléfono pendiente (Tiene N avisos…) · Si está aquí, dígaselo y regístrelo en la lista de avisos por teléfono pendientes.</t>
+          <t>Tus documentos están completos. Tu cita de cotejo es el DÍA a las HH:MM, en el SEDE. Lleva los mismos documentos impresos, tu identificación oficial y el comprobante del pago de $MONTO con la referencia REFERENCIA.</t>
         </is>
       </c>
       <c r="G1002" s="13" t="inlineStr"/>
@@ -51280,7 +51280,7 @@
       </c>
       <c r="L1002" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
         </is>
       </c>
     </row>
@@ -51292,12 +51292,12 @@
       </c>
       <c r="B1003" s="15" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C1003" s="15" t="inlineStr">
         <is>
-          <t>Ficha · Qué decirle (de tú)</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1003" s="15" t="inlineStr">
@@ -51307,12 +51307,12 @@
       </c>
       <c r="E1003" s="15" t="inlineStr">
         <is>
-          <t>Según el estado</t>
+          <t>Resultado de la cita</t>
         </is>
       </c>
       <c r="F1003" s="15" t="inlineStr">
         <is>
-          <t>Tu solicitud todavía no se envía: falta terminar de capturarla contigo. / La Secretaría está revisando tus documentos. … / A tu solicitud le falta corregir un documento: … Lo corregimos aquí contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. (o: Esta es tu última oportunidad para corregir. …) / Tu solicitud se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva aquí mismo. / Tu cita de cotejo es el … / Tu curso empieza el … Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Tu cotejo terminó. Estás en espera de un grupo del curso … (y los «qué sigue» de «Mis trámites»)</t>
+          <t>Tu cotejo terminó; tu expediente es el EXP-… / En tu cita faltó un documento: …; tráelo hoy mismo … / En tu cita, un documento no coincidió … / Como no llegaste a tu cita (o no llevaste el comprobante de pago), te dimos una cita nueva: … / Tu solicitud FOLIO se cerró porque no llegaste dos veces a tu cita de cotejo.</t>
         </is>
       </c>
       <c r="G1003" s="13" t="inlineStr"/>
@@ -51342,27 +51342,27 @@
       </c>
       <c r="B1004" s="12" t="inlineStr">
         <is>
-          <t>Ventanilla (personal)</t>
+          <t>Inicio del personal · avisos por teléfono</t>
         </is>
       </c>
       <c r="C1004" s="12" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Qué decirle (de tú)</t>
         </is>
       </c>
       <c r="D1004" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E1004" s="12" t="inlineStr">
         <is>
-          <t>Persona del registro asistido</t>
+          <t>Otros avisos</t>
         </is>
       </c>
       <c r="F1004" s="12" t="inlineStr">
         <is>
-          <t>Leerle lo que falta y cargar lo corregido · Seguir capturando su solicitud · Capturar una solicitud nueva</t>
+          <t>Cerrada sin corregir · Rechazada (con el motivo) · Cuenta bloqueada · Grupo asignado (día, hora, sede y duración: Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Es un solo día y ese mismo día presentas el examen.) · Baja, cambio o grupo por confirmar · Resultado del examen · Acreditación entregada o cancelada · Reposición de la credencial</t>
         </is>
       </c>
       <c r="G1004" s="13" t="inlineStr"/>
@@ -51380,13 +51380,363 @@
       </c>
       <c r="L1004" s="14" t="inlineStr">
         <is>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="15" t="inlineStr">
+        <is>
+          <t>T1004</t>
+        </is>
+      </c>
+      <c r="B1005" s="15" t="inlineStr">
+        <is>
+          <t>Inicio del personal · avisos por teléfono</t>
+        </is>
+      </c>
+      <c r="C1005" s="15" t="inlineStr">
+        <is>
+          <t>Al registrar</t>
+        </is>
+      </c>
+      <c r="D1005" s="15" t="inlineStr">
+        <is>
+          <t>Aviso</t>
+        </is>
+      </c>
+      <c r="E1005" s="15" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="F1005" s="15" t="inlineStr">
+        <is>
+          <t>Se registró que se le avisó · NOMBRE: aviso hecho. / Se registró que no contestó · NOMBRE no contestó. Lo que se le iba a decir se le dice cuando vaya a la ventanilla. / Ya estaba registrado · Otra persona del personal ya registró el aviso de NOMBRE.</t>
+        </is>
+      </c>
+      <c r="G1005" s="13" t="inlineStr"/>
+      <c r="H1005" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1005" s="13" t="inlineStr"/>
+      <c r="J1005" s="15" t="inlineStr"/>
+      <c r="K1005" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1005" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="12" t="inlineStr">
+        <is>
+          <t>T1005</t>
+        </is>
+      </c>
+      <c r="B1006" s="12" t="inlineStr">
+        <is>
+          <t>Revisar una solicitud y Cita de cotejo (personal)</t>
+        </is>
+      </c>
+      <c r="C1006" s="12" t="inlineStr">
+        <is>
+          <t>Cabecera</t>
+        </is>
+      </c>
+      <c r="D1006" s="12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1006" s="12" t="inlineStr">
+        <is>
+          <t>Persona del registro asistido sin activar</t>
+        </is>
+      </c>
+      <c r="F1006" s="12" t="inlineStr">
+        <is>
+          <t>Registro asistido: avisar por teléfono, 55 1234 5678</t>
+        </is>
+      </c>
+      <c r="G1006" s="13" t="inlineStr"/>
+      <c r="H1006" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1006" s="13" t="inlineStr"/>
+      <c r="J1006" s="12" t="inlineStr"/>
+      <c r="K1006" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1006" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="15" t="inlineStr">
+        <is>
+          <t>T1006</t>
+        </is>
+      </c>
+      <c r="B1007" s="15" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1007" s="15" t="inlineStr">
+        <is>
+          <t>Búsqueda</t>
+        </is>
+      </c>
+      <c r="D1007" s="15" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E1007" s="15" t="inlineStr">
+        <is>
+          <t>Al buscar</t>
+        </is>
+      </c>
+      <c r="F1007" s="15" t="inlineStr">
+        <is>
+          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
+        </is>
+      </c>
+      <c r="G1007" s="13" t="inlineStr"/>
+      <c r="H1007" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1007" s="13" t="inlineStr"/>
+      <c r="J1007" s="15" t="inlineStr"/>
+      <c r="K1007" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1007" s="16" t="inlineStr">
+        <is>
           <t>Código del sitio (sitio/app/ventanilla.js)</t>
         </is>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" s="12" t="inlineStr">
+        <is>
+          <t>T1007</t>
+        </is>
+      </c>
+      <c r="B1008" s="12" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1008" s="12" t="inlineStr">
+        <is>
+          <t>Ficha</t>
+        </is>
+      </c>
+      <c r="D1008" s="12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E1008" s="12" t="inlineStr">
+        <is>
+          <t>Según la cuenta</t>
+        </is>
+      </c>
+      <c r="F1008" s="12" t="inlineStr">
+        <is>
+          <t>Registro asistido · avisos por teléfono / Registro asistido · ya activó su cuenta / Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
+        </is>
+      </c>
+      <c r="G1008" s="13" t="inlineStr"/>
+      <c r="H1008" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1008" s="13" t="inlineStr"/>
+      <c r="J1008" s="12" t="inlineStr"/>
+      <c r="K1008" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1008" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="15" t="inlineStr">
+        <is>
+          <t>T1008</t>
+        </is>
+      </c>
+      <c r="B1009" s="15" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1009" s="15" t="inlineStr">
+        <is>
+          <t>Ficha</t>
+        </is>
+      </c>
+      <c r="D1009" s="15" t="inlineStr">
+        <is>
+          <t>Aviso</t>
+        </is>
+      </c>
+      <c r="E1009" s="15" t="inlineStr">
+        <is>
+          <t>Con avisos por teléfono pendientes</t>
+        </is>
+      </c>
+      <c r="F1009" s="15" t="inlineStr">
+        <is>
+          <t>Tiene un aviso por teléfono pendiente (Tiene N avisos…) · Si está aquí, dígaselo y regístrelo en la lista de avisos por teléfono pendientes.</t>
+        </is>
+      </c>
+      <c r="G1009" s="13" t="inlineStr"/>
+      <c r="H1009" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1009" s="13" t="inlineStr"/>
+      <c r="J1009" s="15" t="inlineStr"/>
+      <c r="K1009" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1009" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="12" t="inlineStr">
+        <is>
+          <t>T1009</t>
+        </is>
+      </c>
+      <c r="B1010" s="12" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1010" s="12" t="inlineStr">
+        <is>
+          <t>Ficha · Qué decirle (de tú)</t>
+        </is>
+      </c>
+      <c r="D1010" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E1010" s="12" t="inlineStr">
+        <is>
+          <t>Según el estado</t>
+        </is>
+      </c>
+      <c r="F1010" s="12" t="inlineStr">
+        <is>
+          <t>Tu solicitud todavía no se envía: falta terminar de capturarla contigo. / La Secretaría está revisando tus documentos. … / A tu solicitud le falta corregir un documento: … Lo corregimos aquí contigo. Hay un plazo para corregir. Te quedan N oportunidades para corregir. (o: Esta es tu última oportunidad para corregir. …) / Tu solicitud se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva aquí mismo. / Tu cita de cotejo es el … / Tu curso empieza el … Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Tu cotejo terminó. Estás en espera de un grupo del curso … (y los «qué sigue» de «Mis trámites»)</t>
+        </is>
+      </c>
+      <c r="G1010" s="13" t="inlineStr"/>
+      <c r="H1010" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1010" s="13" t="inlineStr"/>
+      <c r="J1010" s="12" t="inlineStr"/>
+      <c r="K1010" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1010" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/registro-asistido.js)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="15" t="inlineStr">
+        <is>
+          <t>T1010</t>
+        </is>
+      </c>
+      <c r="B1011" s="15" t="inlineStr">
+        <is>
+          <t>Ventanilla (personal)</t>
+        </is>
+      </c>
+      <c r="C1011" s="15" t="inlineStr">
+        <is>
+          <t>Ficha</t>
+        </is>
+      </c>
+      <c r="D1011" s="15" t="inlineStr">
+        <is>
+          <t>Botón o enlace</t>
+        </is>
+      </c>
+      <c r="E1011" s="15" t="inlineStr">
+        <is>
+          <t>Persona del registro asistido</t>
+        </is>
+      </c>
+      <c r="F1011" s="15" t="inlineStr">
+        <is>
+          <t>Leerle lo que falta y cargar lo corregido · Seguir capturando su solicitud · Capturar una solicitud nueva</t>
+        </is>
+      </c>
+      <c r="G1011" s="13" t="inlineStr"/>
+      <c r="H1011" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I1011" s="13" t="inlineStr"/>
+      <c r="J1011" s="15" t="inlineStr"/>
+      <c r="K1011" s="16" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L1011" s="16" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1004"/>
-  <conditionalFormatting sqref="H2:H1004">
+  <autoFilter ref="A1:L1011"/>
+  <conditionalFormatting sqref="H2:H1011">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -51400,13 +51750,13 @@
       <formula>"Duda"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G1004">
+  <conditionalFormatting sqref="G2:G1011">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(LEN(G2)&gt;0,H2="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H1004" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
+    <dataValidation sqref="H2:H1011" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
       <formula1>"Pendiente,OK,Cambiar,Quitar,Duda"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/textos/inventario-textos.xlsx
+++ b/docs/textos/inventario-textos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$933</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$L$934</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario generado de la versión de prueba 0.71 · 932 textos</t>
+          <t>Inventario generado de la versión de prueba 0.71 · 933 textos</t>
         </is>
       </c>
     </row>
@@ -761,23 +761,23 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A21)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A21)</f>
         <v/>
       </c>
       <c r="C21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A21,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A21,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A21,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A21,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A21,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A21,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F21" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A21,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A21,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A21,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A21,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -788,23 +788,23 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A22)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A22)</f>
         <v/>
       </c>
       <c r="C22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A22,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A22,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A22,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A22,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A22,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A22,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F22" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A22,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A22,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A22,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A22,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -815,23 +815,23 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A23)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A23)</f>
         <v/>
       </c>
       <c r="C23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A23,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A23,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A23,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A23,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A23,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A23,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F23" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A23,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A23,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A23,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A23,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -842,23 +842,23 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A24)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A24)</f>
         <v/>
       </c>
       <c r="C24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A24,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A24,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A24,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A24,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A24,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A24,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F24" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A24,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A24,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A24,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A24,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -869,23 +869,23 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A25)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A25)</f>
         <v/>
       </c>
       <c r="C25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A25,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A25,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A25,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A25,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A25,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A25,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F25" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A25,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A25,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A25,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A25,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -896,23 +896,23 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A26)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A26)</f>
         <v/>
       </c>
       <c r="C26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A26,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A26,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A26,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A26,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A26,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A26,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F26" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A26,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A26,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A26,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A26,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -923,23 +923,23 @@
         </is>
       </c>
       <c r="B27" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A27)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A27)</f>
         <v/>
       </c>
       <c r="C27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A27,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A27,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A27,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A27,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A27,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A27,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F27" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A27,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A27,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A27,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A27,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -950,23 +950,23 @@
         </is>
       </c>
       <c r="B28" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A28)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A28)</f>
         <v/>
       </c>
       <c r="C28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A28,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A28,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A28,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A28,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A28,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A28,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F28" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A28,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A28,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A28,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A28,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -977,23 +977,23 @@
         </is>
       </c>
       <c r="B29" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A29)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A29)</f>
         <v/>
       </c>
       <c r="C29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A29,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A29,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A29,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A29,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A29,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A29,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F29" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A29,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A29,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A29,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A29,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="B30" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A30)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A30)</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A30,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A30,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A30,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A30,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A30,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A30,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A30,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A30,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A30,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A30,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1031,23 +1031,23 @@
         </is>
       </c>
       <c r="B31" s="8">
-        <f>COUNTIF(Textos!$B$2:$B$933,A31)</f>
+        <f>COUNTIF(Textos!$B$2:$B$934,A31)</f>
         <v/>
       </c>
       <c r="C31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A31,Textos!$H$2:$H$933,"Pendiente")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A31,Textos!$H$2:$H$934,"Pendiente")</f>
         <v/>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A31,Textos!$H$2:$H$933,"OK")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A31,Textos!$H$2:$H$934,"OK")</f>
         <v/>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A31,Textos!$H$2:$H$933,"Cambiar")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A31,Textos!$H$2:$H$934,"Cambiar")</f>
         <v/>
       </c>
       <c r="F31" s="8">
-        <f>COUNTIFS(Textos!$B$2:$B$933,A31,Textos!$H$2:$H$933,"Quitar")+COUNTIFS(Textos!$B$2:$B$933,A31,Textos!$H$2:$H$933,"Duda")</f>
+        <f>COUNTIFS(Textos!$B$2:$B$934,A31,Textos!$H$2:$H$934,"Quitar")+COUNTIFS(Textos!$B$2:$B$934,A31,Textos!$H$2:$H$934,"Duda")</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L933"/>
+  <dimension ref="A1:L934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="F195" s="15" t="inlineStr">
         <is>
-          <t>Corrige antes del DD/MM/AAAA (20 días hábiles, parámetro dias_habiles_correccion) · Recibiste las observaciones el DD/MM/AAAA. Tienes 20 días hábiles para corregir: si no reenvías tu solicitud a tiempo, se cierra.</t>
+          <t>Corrige a más tardar el DD/MM/AAAA (20 días hábiles, parámetro dias_habiles_correccion) · Recibiste las observaciones el DD/MM/AAAA. Tienes 20 días hábiles para corregir: si no reenvías tu solicitud a tiempo, se cierra.</t>
         </is>
       </c>
       <c r="G195" s="13" t="inlineStr"/>
@@ -34783,12 +34783,12 @@
       </c>
       <c r="E673" s="15" t="inlineStr">
         <is>
-          <t>Regla «curso_inactivo»</t>
+          <t>Regla «grupos_solo_lectura»</t>
         </is>
       </c>
       <c r="F673" s="15" t="inlineStr">
         <is>
-          <t>Este curso no está abriendo grupos</t>
+          <t>Con su perfil los grupos son de consulta: no se crean, cambian ni confirman</t>
         </is>
       </c>
       <c r="G673" s="13" t="inlineStr"/>
@@ -34801,7 +34801,7 @@
       <c r="J673" s="15" t="inlineStr"/>
       <c r="K673" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L673" s="16" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E674" s="12" t="inlineStr">
         <is>
-          <t>Regla «grupo_propio_sin_gobierno»</t>
+          <t>Regla «curso_inactivo»</t>
         </is>
       </c>
       <c r="F674" s="12" t="inlineStr">
         <is>
-          <t>Sólo las instituciones de gobierno (dependencias de la Ciudad, Alcaldías y dependencias federales) tienen grupo propio: empresas, consultorías, particulares, instituciones educativas e independientes van a grupos combinados</t>
+          <t>Este curso no está abriendo grupos</t>
         </is>
       </c>
       <c r="G674" s="13" t="inlineStr"/>
@@ -34851,7 +34851,7 @@
       <c r="J674" s="12" t="inlineStr"/>
       <c r="K674" s="14" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L674" s="14" t="inlineStr">
@@ -34883,12 +34883,12 @@
       </c>
       <c r="E675" s="15" t="inlineStr">
         <is>
-          <t>Regla «instructor_sin_permiso»</t>
+          <t>Regla «grupo_propio_sin_gobierno»</t>
         </is>
       </c>
       <c r="F675" s="15" t="inlineStr">
         <is>
-          <t>La persona instructora la asigna el área de Instructores y Capacitación: cree el grupo sin ella</t>
+          <t>Sólo las instituciones de gobierno (dependencias de la Ciudad, Alcaldías y dependencias federales) tienen grupo propio: empresas, consultorías, particulares, instituciones educativas e independientes van a grupos combinados</t>
         </is>
       </c>
       <c r="G675" s="13" t="inlineStr"/>
@@ -34933,12 +34933,12 @@
       </c>
       <c r="E676" s="12" t="inlineStr">
         <is>
-          <t>Regla «alta_fuera_de_integracion»</t>
+          <t>Regla «instructor_sin_permiso»</t>
         </is>
       </c>
       <c r="F676" s="12" t="inlineStr">
         <is>
-          <t>Un grupo nuevo se crea sin confirmar («En integración»)</t>
+          <t>La persona instructora la asigna el área de Instructores y Capacitación: cree el grupo sin ella</t>
         </is>
       </c>
       <c r="G676" s="13" t="inlineStr"/>
@@ -34983,12 +34983,12 @@
       </c>
       <c r="E677" s="15" t="inlineStr">
         <is>
-          <t>Regla «campo_inmutable»</t>
+          <t>Regla «alta_fuera_de_integracion»</t>
         </is>
       </c>
       <c r="F677" s="15" t="inlineStr">
         <is>
-          <t>El curso, el tipo de grupo (específico o combinado) y los cupos no cambian después de crearlo</t>
+          <t>Un grupo nuevo se crea sin confirmar («En integración»)</t>
         </is>
       </c>
       <c r="G677" s="13" t="inlineStr"/>
@@ -35033,12 +35033,12 @@
       </c>
       <c r="E678" s="12" t="inlineStr">
         <is>
-          <t>Regla «grupo_cerrado»</t>
+          <t>Regla «campo_inmutable»</t>
         </is>
       </c>
       <c r="F678" s="12" t="inlineStr">
         <is>
-          <t>La sede, la fecha y la hora de entrada no cambian una vez iniciado el curso</t>
+          <t>El curso, el tipo de grupo (específico o combinado) y los cupos no cambian después de crearlo</t>
         </is>
       </c>
       <c r="G678" s="13" t="inlineStr"/>
@@ -35083,12 +35083,12 @@
       </c>
       <c r="E679" s="15" t="inlineStr">
         <is>
-          <t>Regla «instructor_sin_permiso»</t>
+          <t>Regla «grupo_cerrado»</t>
         </is>
       </c>
       <c r="F679" s="15" t="inlineStr">
         <is>
-          <t>La persona instructora la asigna o la cambia el área de Instructores y Capacitación</t>
+          <t>La sede, la fecha y la hora de entrada no cambian una vez iniciado el curso</t>
         </is>
       </c>
       <c r="G679" s="13" t="inlineStr"/>
@@ -35133,12 +35133,12 @@
       </c>
       <c r="E680" s="12" t="inlineStr">
         <is>
-          <t>Regla «grupo_cerrado»</t>
+          <t>Regla «instructor_sin_permiso»</t>
         </is>
       </c>
       <c r="F680" s="12" t="inlineStr">
         <is>
-          <t>El instructor no cambia en un grupo concluido o cancelado</t>
+          <t>La persona instructora la asigna o la cambia el área de Instructores y Capacitación</t>
         </is>
       </c>
       <c r="G680" s="13" t="inlineStr"/>
@@ -35183,12 +35183,12 @@
       </c>
       <c r="E681" s="15" t="inlineStr">
         <is>
-          <t>Regla «sin_instructor»</t>
+          <t>Regla «grupo_cerrado»</t>
         </is>
       </c>
       <c r="F681" s="15" t="inlineStr">
         <is>
-          <t>Un grupo confirmado siempre tiene instructor</t>
+          <t>El instructor no cambia en un grupo concluido o cancelado</t>
         </is>
       </c>
       <c r="G681" s="13" t="inlineStr"/>
@@ -35233,12 +35233,12 @@
       </c>
       <c r="E682" s="12" t="inlineStr">
         <is>
-          <t>Regla «transicion_invalida»</t>
+          <t>Regla «sin_instructor»</t>
         </is>
       </c>
       <c r="F682" s="12" t="inlineStr">
         <is>
-          <t>Este cambio no está permitido: un grupo «…» no puede pasar a «…»</t>
+          <t>Un grupo confirmado siempre tiene instructor</t>
         </is>
       </c>
       <c r="G682" s="13" t="inlineStr"/>
@@ -35283,12 +35283,12 @@
       </c>
       <c r="E683" s="15" t="inlineStr">
         <is>
-          <t>Regla «confirmacion_sin_permiso»</t>
+          <t>Regla «transicion_invalida»</t>
         </is>
       </c>
       <c r="F683" s="15" t="inlineStr">
         <is>
-          <t>El grupo lo confirma el área de Instructores y Capacitación</t>
+          <t>Este cambio no está permitido: un grupo «…» no puede pasar a «…»</t>
         </is>
       </c>
       <c r="G683" s="13" t="inlineStr"/>
@@ -35333,12 +35333,12 @@
       </c>
       <c r="E684" s="12" t="inlineStr">
         <is>
-          <t>Regla «datos_para_confirmar»</t>
+          <t>Regla «confirmacion_sin_permiso»</t>
         </is>
       </c>
       <c r="F684" s="12" t="inlineStr">
         <is>
-          <t>Para confirmar el grupo indique el primer día, la hora de entrada y el instructor</t>
+          <t>El grupo lo confirma el área de Instructores y Capacitación</t>
         </is>
       </c>
       <c r="G684" s="13" t="inlineStr"/>
@@ -35383,12 +35383,12 @@
       </c>
       <c r="E685" s="15" t="inlineStr">
         <is>
-          <t>Regla «anticipacion»</t>
+          <t>Regla «datos_para_confirmar»</t>
         </is>
       </c>
       <c r="F685" s="15" t="inlineStr">
         <is>
-          <t>El curso debe empezar al menos … días después de confirmar el grupo</t>
+          <t>Para confirmar el grupo indique el primer día, la hora de entrada y el instructor</t>
         </is>
       </c>
       <c r="G685" s="13" t="inlineStr"/>
@@ -35433,12 +35433,12 @@
       </c>
       <c r="E686" s="12" t="inlineStr">
         <is>
-          <t>Regla «cupo_minimo»</t>
+          <t>Regla «anticipacion»</t>
         </is>
       </c>
       <c r="F686" s="12" t="inlineStr">
         <is>
-          <t>El grupo tiene … personas y necesita al menos …</t>
+          <t>El curso debe empezar al menos … días después de confirmar el grupo</t>
         </is>
       </c>
       <c r="G686" s="13" t="inlineStr"/>
@@ -35483,12 +35483,12 @@
       </c>
       <c r="E687" s="15" t="inlineStr">
         <is>
-          <t>Regla «antes_de_inicio»</t>
+          <t>Regla «cupo_minimo»</t>
         </is>
       </c>
       <c r="F687" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">El curso inicia el </t>
+          <t>El grupo tiene … personas y necesita al menos …</t>
         </is>
       </c>
       <c r="G687" s="13" t="inlineStr"/>
@@ -35533,12 +35533,12 @@
       </c>
       <c r="E688" s="12" t="inlineStr">
         <is>
-          <t>Regla «faltan_calificaciones»</t>
+          <t>Regla «antes_de_inicio»</t>
         </is>
       </c>
       <c r="F688" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falta capturar la calificación de: </t>
+          <t xml:space="preserve">El curso inicia el </t>
         </is>
       </c>
       <c r="G688" s="13" t="inlineStr"/>
@@ -35583,12 +35583,12 @@
       </c>
       <c r="E689" s="15" t="inlineStr">
         <is>
-          <t>Regla «cancelacion_sin_motivo»</t>
+          <t>Regla «faltan_calificaciones»</t>
         </is>
       </c>
       <c r="F689" s="15" t="inlineStr">
         <is>
-          <t>Indique el motivo de la cancelación</t>
+          <t xml:space="preserve">Falta capturar la calificación de: </t>
         </is>
       </c>
       <c r="G689" s="13" t="inlineStr"/>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="E690" s="12" t="inlineStr">
         <is>
-          <t>Regla «grupo_cerrado»</t>
+          <t>Regla «cancelacion_sin_motivo»</t>
         </is>
       </c>
       <c r="F690" s="12" t="inlineStr">
         <is>
-          <t>El grupo ya no recibe personas</t>
+          <t>Indique el motivo de la cancelación</t>
         </is>
       </c>
       <c r="G690" s="13" t="inlineStr"/>
@@ -35683,12 +35683,12 @@
       </c>
       <c r="E691" s="15" t="inlineStr">
         <is>
-          <t>Regla «grupo_por_iniciar»</t>
+          <t>Regla «grupo_cerrado»</t>
         </is>
       </c>
       <c r="F691" s="15" t="inlineStr">
         <is>
-          <t>A un grupo confirmado se agregan personas hasta el día anterior al inicio del curso</t>
+          <t>El grupo ya no recibe personas</t>
         </is>
       </c>
       <c r="G691" s="13" t="inlineStr"/>
@@ -35733,12 +35733,12 @@
       </c>
       <c r="E692" s="12" t="inlineStr">
         <is>
-          <t>Regla «solicitud_no_lista»</t>
+          <t>Regla «grupo_por_iniciar»</t>
         </is>
       </c>
       <c r="F692" s="12" t="inlineStr">
         <is>
-          <t>La solicitud … no se puede agregar: sólo se agregan solicitudes con el cotejo terminado y sin grupo</t>
+          <t>A un grupo confirmado se agregan personas hasta el día anterior al inicio del curso</t>
         </is>
       </c>
       <c r="G692" s="13" t="inlineStr"/>
@@ -35783,12 +35783,12 @@
       </c>
       <c r="E693" s="15" t="inlineStr">
         <is>
-          <t>Regla «otro_curso»</t>
+          <t>Regla «solicitud_no_lista»</t>
         </is>
       </c>
       <c r="F693" s="15" t="inlineStr">
         <is>
-          <t>La solicitud … es de otro curso</t>
+          <t>La solicitud … no se puede agregar: sólo se agregan solicitudes con el cotejo terminado y sin grupo</t>
         </is>
       </c>
       <c r="G693" s="13" t="inlineStr"/>
@@ -35833,12 +35833,12 @@
       </c>
       <c r="E694" s="12" t="inlineStr">
         <is>
-          <t>Regla «otra_organizacion»</t>
+          <t>Regla «otro_curso»</t>
         </is>
       </c>
       <c r="F694" s="12" t="inlineStr">
         <is>
-          <t>La solicitud … no es de la organización del grupo</t>
+          <t>La solicitud … es de otro curso</t>
         </is>
       </c>
       <c r="G694" s="13" t="inlineStr"/>
@@ -35883,12 +35883,12 @@
       </c>
       <c r="E695" s="15" t="inlineStr">
         <is>
-          <t>Regla «cupo_maximo»</t>
+          <t>Regla «otra_organizacion»</t>
         </is>
       </c>
       <c r="F695" s="15" t="inlineStr">
         <is>
-          <t>El grupo está lleno: … de …</t>
+          <t>La solicitud … no es de la organización del grupo</t>
         </is>
       </c>
       <c r="G695" s="13" t="inlineStr"/>
@@ -35933,12 +35933,12 @@
       </c>
       <c r="E696" s="12" t="inlineStr">
         <is>
-          <t>Regla «inscripcion_inmutable»</t>
+          <t>Regla «cupo_maximo»</t>
         </is>
       </c>
       <c r="F696" s="12" t="inlineStr">
         <is>
-          <t>La inscripción a un grupo sólo se modifica para dar de baja a la persona</t>
+          <t>El grupo está lleno: … de …</t>
         </is>
       </c>
       <c r="G696" s="13" t="inlineStr"/>
@@ -35983,12 +35983,12 @@
       </c>
       <c r="E697" s="15" t="inlineStr">
         <is>
-          <t>Regla «baja_sin_motivo»</t>
+          <t>Regla «inscripcion_inmutable»</t>
         </is>
       </c>
       <c r="F697" s="15" t="inlineStr">
         <is>
-          <t>Indique el motivo de la baja</t>
+          <t>La inscripción a un grupo sólo se modifica para dar de baja a la persona</t>
         </is>
       </c>
       <c r="G697" s="13" t="inlineStr"/>
@@ -36033,12 +36033,12 @@
       </c>
       <c r="E698" s="12" t="inlineStr">
         <is>
-          <t>Regla «baja_con_examen»</t>
+          <t>Regla «baja_sin_motivo»</t>
         </is>
       </c>
       <c r="F698" s="12" t="inlineStr">
         <is>
-          <t>No se da de baja a quien ya presentó examen</t>
+          <t>Indique el motivo de la baja</t>
         </is>
       </c>
       <c r="G698" s="13" t="inlineStr"/>
@@ -36083,12 +36083,12 @@
       </c>
       <c r="E699" s="15" t="inlineStr">
         <is>
-          <t>Regla «captura_de_personal»</t>
+          <t>Regla «baja_con_examen»</t>
         </is>
       </c>
       <c r="F699" s="15" t="inlineStr">
         <is>
-          <t>La asistencia la captura el personal de la Secretaría con su cuenta</t>
+          <t>No se da de baja a quien ya presentó examen</t>
         </is>
       </c>
       <c r="G699" s="13" t="inlineStr"/>
@@ -36133,12 +36133,12 @@
       </c>
       <c r="E700" s="12" t="inlineStr">
         <is>
-          <t>Regla «inscripcion_inactiva»</t>
+          <t>Regla «captura_de_personal»</t>
         </is>
       </c>
       <c r="F700" s="12" t="inlineStr">
         <is>
-          <t>La persona ya no está en el grupo</t>
+          <t>La asistencia la captura el personal de la Secretaría con su cuenta</t>
         </is>
       </c>
       <c r="G700" s="13" t="inlineStr"/>
@@ -36183,12 +36183,12 @@
       </c>
       <c r="E701" s="15" t="inlineStr">
         <is>
-          <t>Regla «grupo_no_en_curso»</t>
+          <t>Regla «inscripcion_inactiva»</t>
         </is>
       </c>
       <c r="F701" s="15" t="inlineStr">
         <is>
-          <t>La asistencia se captura mientras el curso está en marcha</t>
+          <t>La persona ya no está en el grupo</t>
         </is>
       </c>
       <c r="G701" s="13" t="inlineStr"/>
@@ -36233,12 +36233,12 @@
       </c>
       <c r="E702" s="12" t="inlineStr">
         <is>
-          <t>Regla «dia_inexistente»</t>
+          <t>Regla «grupo_no_en_curso»</t>
         </is>
       </c>
       <c r="F702" s="12" t="inlineStr">
         <is>
-          <t>El curso dura … días</t>
+          <t>La asistencia se captura mientras el curso está en marcha</t>
         </is>
       </c>
       <c r="G702" s="13" t="inlineStr"/>
@@ -36283,12 +36283,12 @@
       </c>
       <c r="E703" s="15" t="inlineStr">
         <is>
-          <t>Regla «asistencia_cerrada»</t>
+          <t>Regla «dia_inexistente»</t>
         </is>
       </c>
       <c r="F703" s="15" t="inlineStr">
         <is>
-          <t>Con el examen capturado, la asistencia ya no cambia</t>
+          <t>El curso dura … días</t>
         </is>
       </c>
       <c r="G703" s="13" t="inlineStr"/>
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E704" s="12" t="inlineStr">
         <is>
-          <t>Regla «dia_futuro»</t>
+          <t>Regla «asistencia_cerrada»</t>
         </is>
       </c>
       <c r="F704" s="12" t="inlineStr">
         <is>
-          <t>No se captura asistencia de un día que no ha ocurrido</t>
+          <t>Con el examen capturado, la asistencia ya no cambia</t>
         </is>
       </c>
       <c r="G704" s="13" t="inlineStr"/>
@@ -36383,12 +36383,12 @@
       </c>
       <c r="E705" s="15" t="inlineStr">
         <is>
-          <t>Regla «campo_inmutable»</t>
+          <t>Regla «dia_futuro»</t>
         </is>
       </c>
       <c r="F705" s="15" t="inlineStr">
         <is>
-          <t>El día y la persona de una asistencia no cambian</t>
+          <t>No se captura asistencia de un día que no ha ocurrido</t>
         </is>
       </c>
       <c r="G705" s="13" t="inlineStr"/>
@@ -36433,12 +36433,12 @@
       </c>
       <c r="E706" s="12" t="inlineStr">
         <is>
-          <t>Regla «captura_de_personal»</t>
+          <t>Regla «campo_inmutable»</t>
         </is>
       </c>
       <c r="F706" s="12" t="inlineStr">
         <is>
-          <t>La calificación la captura el personal de la Secretaría con su cuenta</t>
+          <t>El día y la persona de una asistencia no cambian</t>
         </is>
       </c>
       <c r="G706" s="13" t="inlineStr"/>
@@ -36483,12 +36483,12 @@
       </c>
       <c r="E707" s="15" t="inlineStr">
         <is>
-          <t>Regla «grupo_no_en_curso»</t>
+          <t>Regla «captura_de_personal»</t>
         </is>
       </c>
       <c r="F707" s="15" t="inlineStr">
         <is>
-          <t>La calificación se captura mientras el curso está en marcha</t>
+          <t>La calificación la captura el personal de la Secretaría con su cuenta</t>
         </is>
       </c>
       <c r="G707" s="13" t="inlineStr"/>
@@ -36533,12 +36533,12 @@
       </c>
       <c r="E708" s="12" t="inlineStr">
         <is>
-          <t>Regla «sin_derecho_examen»</t>
+          <t>Regla «grupo_no_en_curso»</t>
         </is>
       </c>
       <c r="F708" s="12" t="inlineStr">
         <is>
-          <t>Asistió … de … días; se necesitan … para tener derecho a examen</t>
+          <t>La calificación se captura mientras el curso está en marcha</t>
         </is>
       </c>
       <c r="G708" s="13" t="inlineStr"/>
@@ -36583,12 +36583,12 @@
       </c>
       <c r="E709" s="15" t="inlineStr">
         <is>
-          <t>Regla «fecha_examen»</t>
+          <t>Regla «sin_derecho_examen»</t>
         </is>
       </c>
       <c r="F709" s="15" t="inlineStr">
         <is>
-          <t>El examen se presenta el último día del curso (…)</t>
+          <t>Asistió … de … días; se necesitan … para tener derecho a examen</t>
         </is>
       </c>
       <c r="G709" s="13" t="inlineStr"/>
@@ -36633,12 +36633,12 @@
       </c>
       <c r="E710" s="12" t="inlineStr">
         <is>
-          <t>Regla «sin_pase_de_lista»</t>
+          <t>Regla «fecha_examen»</t>
         </is>
       </c>
       <c r="F710" s="12" t="inlineStr">
         <is>
-          <t>Sin el pase de lista del día del examen no hay examen: primero se registra su asistencia de ese día</t>
+          <t>El examen se presenta el último día del curso (…)</t>
         </is>
       </c>
       <c r="G710" s="13" t="inlineStr"/>
@@ -36683,12 +36683,12 @@
       </c>
       <c r="E711" s="15" t="inlineStr">
         <is>
-          <t>Regla «carga_de_personal»</t>
+          <t>Regla «sin_pase_de_lista»</t>
         </is>
       </c>
       <c r="F711" s="15" t="inlineStr">
         <is>
-          <t>El material de estudio lo carga el personal de la Secretaría</t>
+          <t>Sin el pase de lista del día del examen no hay examen: primero se registra su asistencia de ese día</t>
         </is>
       </c>
       <c r="G711" s="13" t="inlineStr"/>
@@ -36733,12 +36733,12 @@
       </c>
       <c r="E712" s="12" t="inlineStr">
         <is>
-          <t>Regla «formato_no_admitido»</t>
+          <t>Regla «carga_de_personal»</t>
         </is>
       </c>
       <c r="F712" s="12" t="inlineStr">
         <is>
-          <t>El material de estudio se carga en PDF</t>
+          <t>El material de estudio lo carga el personal de la Secretaría</t>
         </is>
       </c>
       <c r="G712" s="13" t="inlineStr"/>
@@ -36751,7 +36751,7 @@
       <c r="J712" s="12" t="inlineStr"/>
       <c r="K712" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L712" s="14" t="inlineStr">
@@ -36783,12 +36783,12 @@
       </c>
       <c r="E713" s="15" t="inlineStr">
         <is>
-          <t>Regla «documento_inmutable»</t>
+          <t>Regla «formato_no_admitido»</t>
         </is>
       </c>
       <c r="F713" s="15" t="inlineStr">
         <is>
-          <t>Un archivo cargado no se modifica: se carga uno nuevo</t>
+          <t>El material de estudio se carga en PDF</t>
         </is>
       </c>
       <c r="G713" s="13" t="inlineStr"/>
@@ -36801,7 +36801,7 @@
       <c r="J713" s="15" t="inlineStr"/>
       <c r="K713" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L713" s="16" t="inlineStr">
@@ -36833,12 +36833,12 @@
       </c>
       <c r="E714" s="12" t="inlineStr">
         <is>
-          <t>Regla «documento_sustituido»</t>
+          <t>Regla «documento_inmutable»</t>
         </is>
       </c>
       <c r="F714" s="12" t="inlineStr">
         <is>
-          <t>Sólo se cambia la carga vigente</t>
+          <t>Un archivo cargado no se modifica: se carga uno nuevo</t>
         </is>
       </c>
       <c r="G714" s="13" t="inlineStr"/>
@@ -36883,12 +36883,12 @@
       </c>
       <c r="E715" s="15" t="inlineStr">
         <is>
-          <t>Regla «carga_de_personal»</t>
+          <t>Regla «documento_sustituido»</t>
         </is>
       </c>
       <c r="F715" s="15" t="inlineStr">
         <is>
-          <t>El material de estudio lo cambia el personal de la Secretaría</t>
+          <t>Sólo se cambia la carga vigente</t>
         </is>
       </c>
       <c r="G715" s="13" t="inlineStr"/>
@@ -36918,27 +36918,27 @@
       </c>
       <c r="B716" s="12" t="inlineStr">
         <is>
-          <t>Mi perfil</t>
+          <t>Mensajes al guardar o enviar</t>
         </is>
       </c>
       <c r="C716" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reglas de la base</t>
         </is>
       </c>
       <c r="D716" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E716" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Regla «carga_de_personal»</t>
         </is>
       </c>
       <c r="F716" s="12" t="inlineStr">
         <is>
-          <t>Mis trámites</t>
+          <t>El material de estudio lo cambia el personal de la Secretaría</t>
         </is>
       </c>
       <c r="G716" s="13" t="inlineStr"/>
@@ -36951,12 +36951,12 @@
       <c r="J716" s="12" t="inlineStr"/>
       <c r="K716" s="14" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L716" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/datos.html)</t>
+          <t>Base de datos (db/apd/03-apd-reglas.sql)</t>
         </is>
       </c>
     </row>
@@ -36973,12 +36973,12 @@
       </c>
       <c r="C717" s="15" t="inlineStr">
         <is>
-          <t>Mi perfil</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D717" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E717" s="15" t="inlineStr">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="F717" s="15" t="inlineStr">
         <is>
-          <t>Mi perfil</t>
+          <t>Mis trámites</t>
         </is>
       </c>
       <c r="G717" s="13" t="inlineStr"/>
@@ -37028,7 +37028,7 @@
       </c>
       <c r="D718" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E718" s="12" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="F718" s="12" t="inlineStr">
         <is>
-          <t>Cargando tus datos…</t>
+          <t>Mi perfil</t>
         </is>
       </c>
       <c r="G718" s="13" t="inlineStr"/>
@@ -37048,11 +37048,7 @@
         </is>
       </c>
       <c r="I718" s="13" t="inlineStr"/>
-      <c r="J718" s="18" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J718" s="12" t="inlineStr"/>
       <c r="K718" s="14" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -37082,17 +37078,17 @@
       </c>
       <c r="D719" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E719" s="15" t="inlineStr">
         <is>
-          <t>Mientras la fotografía no está confirmada</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F719" s="15" t="inlineStr">
         <is>
-          <t>Cambiar fotografía</t>
+          <t>Cargando tus datos…</t>
         </is>
       </c>
       <c r="G719" s="13" t="inlineStr"/>
@@ -37102,7 +37098,11 @@
         </is>
       </c>
       <c r="I719" s="13" t="inlineStr"/>
-      <c r="J719" s="15" t="inlineStr"/>
+      <c r="J719" s="17" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K719" s="16" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -37132,17 +37132,17 @@
       </c>
       <c r="D720" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E720" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Mientras la fotografía no está confirmada</t>
         </is>
       </c>
       <c r="F720" s="12" t="inlineStr">
         <is>
-          <t>Tu nueva fotografía</t>
+          <t>Cambiar fotografía</t>
         </is>
       </c>
       <c r="G720" s="13" t="inlineStr"/>
@@ -37182,7 +37182,7 @@
       </c>
       <c r="D721" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E721" s="15" t="inlineStr">
@@ -37192,7 +37192,7 @@
       </c>
       <c r="F721" s="15" t="inlineStr">
         <is>
-          <t>De frente y con el rostro descubierto (sin lentes oscuros, gorra ni cubrebocas), fondo claro y buena luz. Tiene que verse clara: el día del examen, quien lo aplica la usa para confirmar que eres tú y tomarte asistencia.</t>
+          <t>Tu nueva fotografía</t>
         </is>
       </c>
       <c r="G721" s="13" t="inlineStr"/>
@@ -37232,7 +37232,7 @@
       </c>
       <c r="D722" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E722" s="12" t="inlineStr">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="F722" s="12" t="inlineStr">
         <is>
-          <t>Elegir fotografía</t>
+          <t>De frente y con el rostro descubierto (sin lentes oscuros, gorra ni cubrebocas), fondo claro y buena luz. Tiene que verse clara: el día del examen, quien lo aplica la usa para confirmar que eres tú y tomarte asistencia.</t>
         </is>
       </c>
       <c r="G722" s="13" t="inlineStr"/>
@@ -37287,12 +37287,12 @@
       </c>
       <c r="E723" s="15" t="inlineStr">
         <is>
-          <t>En teléfono o equipo con cámara</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F723" s="15" t="inlineStr">
         <is>
-          <t>Tomar fotografía</t>
+          <t>Elegir fotografía</t>
         </is>
       </c>
       <c r="G723" s="13" t="inlineStr"/>
@@ -37337,12 +37337,12 @@
       </c>
       <c r="E724" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>En teléfono o equipo con cámara</t>
         </is>
       </c>
       <c r="F724" s="12" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Tomar fotografía</t>
         </is>
       </c>
       <c r="G724" s="13" t="inlineStr"/>
@@ -37392,7 +37392,7 @@
       </c>
       <c r="F725" s="15" t="inlineStr">
         <is>
-          <t>Guardar fotografía</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="G725" s="13" t="inlineStr"/>
@@ -37427,12 +37427,12 @@
       </c>
       <c r="C726" s="12" t="inlineStr">
         <is>
-          <t>Datos de identidad</t>
+          <t>Mi perfil</t>
         </is>
       </c>
       <c r="D726" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E726" s="12" t="inlineStr">
@@ -37442,7 +37442,7 @@
       </c>
       <c r="F726" s="12" t="inlineStr">
         <is>
-          <t>Datos de identidad</t>
+          <t>Guardar fotografía</t>
         </is>
       </c>
       <c r="G726" s="13" t="inlineStr"/>
@@ -37482,7 +37482,7 @@
       </c>
       <c r="D727" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E727" s="15" t="inlineStr">
@@ -37492,7 +37492,7 @@
       </c>
       <c r="F727" s="15" t="inlineStr">
         <is>
-          <t>Van ligados a tu CURP. Si alguno está mal, dilo en tu cita de cotejo: ahí la Secretaría revisa tu identificación oficial y puede corregirlo. Informes en la Secretaría: de lunes a viernes, de 9:00 a 15:00. Pendiente (P132): teléfono y correo para aclaraciones antes de la cita.</t>
+          <t>Datos de identidad</t>
         </is>
       </c>
       <c r="G727" s="13" t="inlineStr"/>
@@ -37527,12 +37527,12 @@
       </c>
       <c r="C728" s="12" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Datos de identidad</t>
         </is>
       </c>
       <c r="D728" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E728" s="12" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="F728" s="12" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Van ligados a tu CURP. Si alguno está mal, dilo en tu cita de cotejo: ahí la Secretaría revisa tu identificación oficial y puede corregirlo. Informes en la Secretaría: de lunes a viernes, de 9:00 a 15:00. Pendiente (P132): teléfono y correo para aclaraciones antes de la cita.</t>
         </is>
       </c>
       <c r="G728" s="13" t="inlineStr"/>
@@ -37582,7 +37582,7 @@
       </c>
       <c r="D729" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E729" s="15" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="F729" s="15" t="inlineStr">
         <is>
-          <t>Editar</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="G729" s="13" t="inlineStr"/>
@@ -37632,7 +37632,7 @@
       </c>
       <c r="D730" s="12" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E730" s="12" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="F730" s="12" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Editar</t>
         </is>
       </c>
       <c r="G730" s="13" t="inlineStr"/>
@@ -37682,7 +37682,7 @@
       </c>
       <c r="D731" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E731" s="15" t="inlineStr">
@@ -37692,7 +37692,7 @@
       </c>
       <c r="F731" s="15" t="inlineStr">
         <is>
-          <t>Correo electrónico</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G731" s="13" t="inlineStr"/>
@@ -37742,7 +37742,7 @@
       </c>
       <c r="F732" s="12" t="inlineStr">
         <is>
-          <t>Confirma tu correo</t>
+          <t>Correo electrónico</t>
         </is>
       </c>
       <c r="G732" s="13" t="inlineStr"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="F733" s="15" t="inlineStr">
         <is>
-          <t>Teléfono</t>
+          <t>Confirma tu correo</t>
         </is>
       </c>
       <c r="G733" s="13" t="inlineStr"/>
@@ -37832,7 +37832,7 @@
       </c>
       <c r="D734" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E734" s="12" t="inlineStr">
@@ -37842,7 +37842,7 @@
       </c>
       <c r="F734" s="12" t="inlineStr">
         <is>
-          <t>Diez dígitos, de preferencia un celular.</t>
+          <t>Teléfono</t>
         </is>
       </c>
       <c r="G734" s="13" t="inlineStr"/>
@@ -37882,7 +37882,7 @@
       </c>
       <c r="D735" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E735" s="15" t="inlineStr">
@@ -37892,7 +37892,7 @@
       </c>
       <c r="F735" s="15" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Diez dígitos, de preferencia un celular.</t>
         </is>
       </c>
       <c r="G735" s="13" t="inlineStr"/>
@@ -37942,7 +37942,7 @@
       </c>
       <c r="F736" s="12" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="G736" s="13" t="inlineStr"/>
@@ -37977,12 +37977,12 @@
       </c>
       <c r="C737" s="15" t="inlineStr">
         <is>
-          <t>Adscripción</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="D737" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E737" s="15" t="inlineStr">
@@ -37992,7 +37992,7 @@
       </c>
       <c r="F737" s="15" t="inlineStr">
         <is>
-          <t>Adscripción</t>
+          <t>Guardar cambios</t>
         </is>
       </c>
       <c r="G737" s="13" t="inlineStr"/>
@@ -38032,7 +38032,7 @@
       </c>
       <c r="D738" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E738" s="12" t="inlineStr">
@@ -38042,7 +38042,7 @@
       </c>
       <c r="F738" s="12" t="inlineStr">
         <is>
-          <t>Editar</t>
+          <t>Adscripción</t>
         </is>
       </c>
       <c r="G738" s="13" t="inlineStr"/>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="D739" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E739" s="15" t="inlineStr">
@@ -38092,7 +38092,7 @@
       </c>
       <c r="F739" s="15" t="inlineStr">
         <is>
-          <t>Puedes cambiarla cuando quieras: tus siguientes solicitudes se envían con la nueva. Las que ya enviaste se quedan con la adscripción que tenías al enviarlas.</t>
+          <t>Editar</t>
         </is>
       </c>
       <c r="G739" s="13" t="inlineStr"/>
@@ -38132,7 +38132,7 @@
       </c>
       <c r="D740" s="12" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E740" s="12" t="inlineStr">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="F740" s="12" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Puedes cambiarla cuando quieras: tus siguientes solicitudes se envían con la nueva. Las que ya enviaste se quedan con la adscripción que tenías al enviarlas.</t>
         </is>
       </c>
       <c r="G740" s="13" t="inlineStr"/>
@@ -38182,7 +38182,7 @@
       </c>
       <c r="D741" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E741" s="15" t="inlineStr">
@@ -38192,7 +38192,7 @@
       </c>
       <c r="F741" s="15" t="inlineStr">
         <is>
-          <t>¿Trabajas para alguna empresa, institución o dependencia?</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G741" s="13" t="inlineStr"/>
@@ -38232,7 +38232,7 @@
       </c>
       <c r="D742" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E742" s="12" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="F742" s="12" t="inlineStr">
         <is>
-          <t>Cuenta también si trabajas para un particular. Si trabajas por tu cuenta, sin depender de nadie, elige «No, soy independiente».</t>
+          <t>¿Trabajas para alguna empresa, institución o dependencia?</t>
         </is>
       </c>
       <c r="G742" s="13" t="inlineStr"/>
@@ -38282,7 +38282,7 @@
       </c>
       <c r="D743" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E743" s="15" t="inlineStr">
@@ -38292,7 +38292,7 @@
       </c>
       <c r="F743" s="15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Cuenta también si trabajas para un particular. Si trabajas por tu cuenta, sin depender de nadie, elige «No, soy independiente».</t>
         </is>
       </c>
       <c r="G743" s="13" t="inlineStr"/>
@@ -38342,7 +38342,7 @@
       </c>
       <c r="F744" s="12" t="inlineStr">
         <is>
-          <t>No, soy independiente</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G744" s="13" t="inlineStr"/>
@@ -38382,17 +38382,17 @@
       </c>
       <c r="D745" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E745" s="15" t="inlineStr">
         <is>
-          <t>Si «¿Trabajas para alguna empresa, institución o dependencia?» es «Sí»</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F745" s="15" t="inlineStr">
         <is>
-          <t>¿De qué tipo es?</t>
+          <t>No, soy independiente</t>
         </is>
       </c>
       <c r="G745" s="13" t="inlineStr"/>
@@ -38432,7 +38432,7 @@
       </c>
       <c r="D746" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E746" s="12" t="inlineStr">
@@ -38442,7 +38442,7 @@
       </c>
       <c r="F746" s="12" t="inlineStr">
         <is>
-          <t>Empresa, consultoría o particular — Persona moral o física: empresas, consultoras o trabajo para un particular.</t>
+          <t>¿De qué tipo es?</t>
         </is>
       </c>
       <c r="G746" s="13" t="inlineStr"/>
@@ -38492,7 +38492,7 @@
       </c>
       <c r="F747" s="15" t="inlineStr">
         <is>
-          <t>Dependencia del Gobierno de la Ciudad de México</t>
+          <t>Empresa, consultoría o particular — Persona moral o física: empresas, consultoras o trabajo para un particular.</t>
         </is>
       </c>
       <c r="G747" s="13" t="inlineStr"/>
@@ -38542,7 +38542,7 @@
       </c>
       <c r="F748" s="12" t="inlineStr">
         <is>
-          <t>Alcaldía</t>
+          <t>Dependencia del Gobierno de la Ciudad de México</t>
         </is>
       </c>
       <c r="G748" s="13" t="inlineStr"/>
@@ -38592,7 +38592,7 @@
       </c>
       <c r="F749" s="15" t="inlineStr">
         <is>
-          <t>Dependencia del Gobierno Federal — Por ejemplo, la CFE.</t>
+          <t>Alcaldía</t>
         </is>
       </c>
       <c r="G749" s="13" t="inlineStr"/>
@@ -38642,7 +38642,7 @@
       </c>
       <c r="F750" s="12" t="inlineStr">
         <is>
-          <t>Institución educativa — Por ejemplo, la UNAM o Chapingo.</t>
+          <t>Dependencia del Gobierno Federal — Por ejemplo, la CFE.</t>
         </is>
       </c>
       <c r="G750" s="13" t="inlineStr"/>
@@ -38682,17 +38682,17 @@
       </c>
       <c r="D751" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E751" s="15" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Empresa, consultoría o particular»</t>
+          <t>Si «¿Trabajas para alguna empresa, institución o dependencia?» es «Sí»</t>
         </is>
       </c>
       <c r="F751" s="15" t="inlineStr">
         <is>
-          <t>Nombre de la empresa, consultoría o persona física</t>
+          <t>Institución educativa — Por ejemplo, la UNAM o Chapingo.</t>
         </is>
       </c>
       <c r="G751" s="13" t="inlineStr"/>
@@ -38732,7 +38732,7 @@
       </c>
       <c r="D752" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E752" s="12" t="inlineStr">
@@ -38742,7 +38742,7 @@
       </c>
       <c r="F752" s="12" t="inlineStr">
         <is>
-          <t>El nombre o la razón social, tal como aparece en su constancia de situación fiscal. Escribe las primeras letras: si ya está registrada, elígela de la lista; si no, escríbela completa.</t>
+          <t>Nombre de la empresa, consultoría o persona física</t>
         </is>
       </c>
       <c r="G752" s="13" t="inlineStr"/>
@@ -38782,17 +38782,17 @@
       </c>
       <c r="D753" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E753" s="15" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Dependencia del Gobierno de la Ciudad de México»</t>
+          <t>Si «¿De qué tipo es?» es «Empresa, consultoría o particular»</t>
         </is>
       </c>
       <c r="F753" s="15" t="inlineStr">
         <is>
-          <t>¿A qué dependencia del Gobierno de la Ciudad de México perteneces?</t>
+          <t>El nombre o la razón social, tal como aparece en su constancia de situación fiscal. Escribe las primeras letras: si ya está registrada, elígela de la lista; si no, escríbela completa.</t>
         </is>
       </c>
       <c r="G753" s="13" t="inlineStr"/>
@@ -38832,7 +38832,7 @@
       </c>
       <c r="D754" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E754" s="12" t="inlineStr">
@@ -38842,7 +38842,7 @@
       </c>
       <c r="F754" s="12" t="inlineStr">
         <is>
-          <t>Secretaría de Obras y Servicios (SOBSE)</t>
+          <t>¿A qué dependencia del Gobierno de la Ciudad de México perteneces?</t>
         </is>
       </c>
       <c r="G754" s="13" t="inlineStr"/>
@@ -38892,7 +38892,7 @@
       </c>
       <c r="F755" s="15" t="inlineStr">
         <is>
-          <t>Secretaría del Medio Ambiente (SEDEMA)</t>
+          <t>Secretaría de Obras y Servicios (SOBSE)</t>
         </is>
       </c>
       <c r="G755" s="13" t="inlineStr"/>
@@ -38942,7 +38942,7 @@
       </c>
       <c r="F756" s="12" t="inlineStr">
         <is>
-          <t>Procuraduría Ambiental y del Ordenamiento Territorial (PAOT)</t>
+          <t>Secretaría del Medio Ambiente (SEDEMA)</t>
         </is>
       </c>
       <c r="G756" s="13" t="inlineStr"/>
@@ -38987,12 +38987,12 @@
       </c>
       <c r="E757" s="15" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Institución educativa»</t>
+          <t>Si «¿De qué tipo es?» es «Dependencia del Gobierno de la Ciudad de México»</t>
         </is>
       </c>
       <c r="F757" s="15" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Procuraduría Ambiental y del Ordenamiento Territorial (PAOT)</t>
         </is>
       </c>
       <c r="G757" s="13" t="inlineStr"/>
@@ -39032,17 +39032,17 @@
       </c>
       <c r="D758" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E758" s="12" t="inlineStr">
         <is>
-          <t>Si «¿A qué dependencia del Gobierno Federal perteneces?» es «Otra»</t>
+          <t>Si «¿De qué tipo es?» es «Institución educativa»</t>
         </is>
       </c>
       <c r="F758" s="12" t="inlineStr">
         <is>
-          <t>Nombre de la dependencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="G758" s="13" t="inlineStr"/>
@@ -39087,12 +39087,12 @@
       </c>
       <c r="E759" s="15" t="inlineStr">
         <is>
-          <t>Si «¿A qué dependencia del Gobierno de la Ciudad de México perteneces?» es «Secretaría del Medio Ambiente (SEDEMA)»</t>
+          <t>Si «¿A qué dependencia del Gobierno Federal perteneces?» es «Otra»</t>
         </is>
       </c>
       <c r="F759" s="15" t="inlineStr">
         <is>
-          <t>¿A qué Dirección General de la SEDEMA perteneces?</t>
+          <t>Nombre de la dependencia</t>
         </is>
       </c>
       <c r="G759" s="13" t="inlineStr"/>
@@ -39132,7 +39132,7 @@
       </c>
       <c r="D760" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E760" s="12" t="inlineStr">
@@ -39142,7 +39142,7 @@
       </c>
       <c r="F760" s="12" t="inlineStr">
         <is>
-          <t>Dirección General del Sistema de Áreas Naturales Protegidas y Áreas de Valor Ambiental (DGSANPAVA)</t>
+          <t>¿A qué Dirección General de la SEDEMA perteneces?</t>
         </is>
       </c>
       <c r="G760" s="13" t="inlineStr"/>
@@ -39192,7 +39192,7 @@
       </c>
       <c r="F761" s="15" t="inlineStr">
         <is>
-          <t>Dirección General de la Comisión de Recursos Naturales y Desarrollo Rural (DGCORENADR)</t>
+          <t>Dirección General del Sistema de Áreas Naturales Protegidas y Áreas de Valor Ambiental (DGSANPAVA)</t>
         </is>
       </c>
       <c r="G761" s="13" t="inlineStr"/>
@@ -39242,7 +39242,7 @@
       </c>
       <c r="F762" s="12" t="inlineStr">
         <is>
-          <t>Dirección General de Evaluación de Impacto y Regulación Ambiental (DGEIRA)</t>
+          <t>Dirección General de la Comisión de Recursos Naturales y Desarrollo Rural (DGCORENADR)</t>
         </is>
       </c>
       <c r="G762" s="13" t="inlineStr"/>
@@ -39292,7 +39292,7 @@
       </c>
       <c r="F763" s="15" t="inlineStr">
         <is>
-          <t>Dirección General de Vigilancia Ambiental (DGIVA)</t>
+          <t>Dirección General de Evaluación de Impacto y Regulación Ambiental (DGEIRA)</t>
         </is>
       </c>
       <c r="G763" s="13" t="inlineStr"/>
@@ -39342,7 +39342,7 @@
       </c>
       <c r="F764" s="12" t="inlineStr">
         <is>
-          <t>Dirección General de Coordinación de Políticas y Cultura Ambiental (DGCPCA)</t>
+          <t>Dirección General de Vigilancia Ambiental (DGIVA)</t>
         </is>
       </c>
       <c r="G764" s="13" t="inlineStr"/>
@@ -39392,7 +39392,7 @@
       </c>
       <c r="F765" s="15" t="inlineStr">
         <is>
-          <t>Dirección General de Zoológicos y Conservación de la Fauna Silvestre (DGZCFS)</t>
+          <t>Dirección General de Coordinación de Políticas y Cultura Ambiental (DGCPCA)</t>
         </is>
       </c>
       <c r="G765" s="13" t="inlineStr"/>
@@ -39432,17 +39432,17 @@
       </c>
       <c r="D766" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E766" s="12" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Alcaldía»</t>
+          <t>Si «¿A qué dependencia del Gobierno de la Ciudad de México perteneces?» es «Secretaría del Medio Ambiente (SEDEMA)»</t>
         </is>
       </c>
       <c r="F766" s="12" t="inlineStr">
         <is>
-          <t>¿En qué alcaldía trabajas?</t>
+          <t>Dirección General de Zoológicos y Conservación de la Fauna Silvestre (DGZCFS)</t>
         </is>
       </c>
       <c r="G766" s="13" t="inlineStr"/>
@@ -39482,7 +39482,7 @@
       </c>
       <c r="D767" s="15" t="inlineStr">
         <is>
-          <t>Indicación de lista</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E767" s="15" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="F767" s="15" t="inlineStr">
         <is>
-          <t>Elige la alcaldía</t>
+          <t>¿En qué alcaldía trabajas?</t>
         </is>
       </c>
       <c r="G767" s="13" t="inlineStr"/>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="D768" s="12" t="inlineStr">
         <is>
-          <t>Opción de lista</t>
+          <t>Indicación de lista</t>
         </is>
       </c>
       <c r="E768" s="12" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="F768" s="12" t="inlineStr">
         <is>
-          <t>Álvaro Obregón</t>
+          <t>Elige la alcaldía</t>
         </is>
       </c>
       <c r="G768" s="13" t="inlineStr"/>
@@ -39592,7 +39592,7 @@
       </c>
       <c r="F769" s="15" t="inlineStr">
         <is>
-          <t>Azcapotzalco</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="G769" s="13" t="inlineStr"/>
@@ -39642,7 +39642,7 @@
       </c>
       <c r="F770" s="12" t="inlineStr">
         <is>
-          <t>Benito Juárez</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="G770" s="13" t="inlineStr"/>
@@ -39692,7 +39692,7 @@
       </c>
       <c r="F771" s="15" t="inlineStr">
         <is>
-          <t>Coyoacán</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="G771" s="13" t="inlineStr"/>
@@ -39742,7 +39742,7 @@
       </c>
       <c r="F772" s="12" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Coyoacán</t>
         </is>
       </c>
       <c r="G772" s="13" t="inlineStr"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="F773" s="15" t="inlineStr">
         <is>
-          <t>Cuauhtémoc</t>
+          <t>Cuajimalpa de Morelos</t>
         </is>
       </c>
       <c r="G773" s="13" t="inlineStr"/>
@@ -39842,7 +39842,7 @@
       </c>
       <c r="F774" s="12" t="inlineStr">
         <is>
-          <t>Gustavo A. Madero</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="G774" s="13" t="inlineStr"/>
@@ -39892,7 +39892,7 @@
       </c>
       <c r="F775" s="15" t="inlineStr">
         <is>
-          <t>Iztacalco</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="G775" s="13" t="inlineStr"/>
@@ -39942,7 +39942,7 @@
       </c>
       <c r="F776" s="12" t="inlineStr">
         <is>
-          <t>Iztapalapa</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="G776" s="13" t="inlineStr"/>
@@ -39992,7 +39992,7 @@
       </c>
       <c r="F777" s="15" t="inlineStr">
         <is>
-          <t>La Magdalena Contreras</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="G777" s="13" t="inlineStr"/>
@@ -40042,7 +40042,7 @@
       </c>
       <c r="F778" s="12" t="inlineStr">
         <is>
-          <t>Miguel Hidalgo</t>
+          <t>La Magdalena Contreras</t>
         </is>
       </c>
       <c r="G778" s="13" t="inlineStr"/>
@@ -40092,7 +40092,7 @@
       </c>
       <c r="F779" s="15" t="inlineStr">
         <is>
-          <t>Milpa Alta</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="G779" s="13" t="inlineStr"/>
@@ -40142,7 +40142,7 @@
       </c>
       <c r="F780" s="12" t="inlineStr">
         <is>
-          <t>Tláhuac</t>
+          <t>Milpa Alta</t>
         </is>
       </c>
       <c r="G780" s="13" t="inlineStr"/>
@@ -40192,7 +40192,7 @@
       </c>
       <c r="F781" s="15" t="inlineStr">
         <is>
-          <t>Tlalpan</t>
+          <t>Tláhuac</t>
         </is>
       </c>
       <c r="G781" s="13" t="inlineStr"/>
@@ -40242,7 +40242,7 @@
       </c>
       <c r="F782" s="12" t="inlineStr">
         <is>
-          <t>Venustiano Carranza</t>
+          <t>Tlalpan</t>
         </is>
       </c>
       <c r="G782" s="13" t="inlineStr"/>
@@ -40292,7 +40292,7 @@
       </c>
       <c r="F783" s="15" t="inlineStr">
         <is>
-          <t>Xochimilco</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="G783" s="13" t="inlineStr"/>
@@ -40332,17 +40332,17 @@
       </c>
       <c r="D784" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción de lista</t>
         </is>
       </c>
       <c r="E784" s="12" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Dependencia del Gobierno Federal»</t>
+          <t>Si «¿De qué tipo es?» es «Alcaldía»</t>
         </is>
       </c>
       <c r="F784" s="12" t="inlineStr">
         <is>
-          <t>¿A qué dependencia del Gobierno Federal perteneces?</t>
+          <t>Xochimilco</t>
         </is>
       </c>
       <c r="G784" s="13" t="inlineStr"/>
@@ -40382,7 +40382,7 @@
       </c>
       <c r="D785" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E785" s="15" t="inlineStr">
@@ -40392,7 +40392,7 @@
       </c>
       <c r="F785" s="15" t="inlineStr">
         <is>
-          <t>Comisión Federal de Electricidad (CFE)</t>
+          <t>¿A qué dependencia del Gobierno Federal perteneces?</t>
         </is>
       </c>
       <c r="G785" s="13" t="inlineStr"/>
@@ -40432,17 +40432,17 @@
       </c>
       <c r="D786" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E786" s="12" t="inlineStr">
         <is>
-          <t>Si «¿De qué tipo es?» es «Institución educativa»</t>
+          <t>Si «¿De qué tipo es?» es «Dependencia del Gobierno Federal»</t>
         </is>
       </c>
       <c r="F786" s="12" t="inlineStr">
         <is>
-          <t>¿A qué institución educativa perteneces?</t>
+          <t>Comisión Federal de Electricidad (CFE)</t>
         </is>
       </c>
       <c r="G786" s="13" t="inlineStr"/>
@@ -40482,7 +40482,7 @@
       </c>
       <c r="D787" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E787" s="15" t="inlineStr">
@@ -40492,7 +40492,7 @@
       </c>
       <c r="F787" s="15" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de México (UNAM)</t>
+          <t>¿A qué institución educativa perteneces?</t>
         </is>
       </c>
       <c r="G787" s="13" t="inlineStr"/>
@@ -40542,7 +40542,7 @@
       </c>
       <c r="F788" s="12" t="inlineStr">
         <is>
-          <t>Universidad Autónoma Chapingo</t>
+          <t>Universidad Nacional Autónoma de México (UNAM)</t>
         </is>
       </c>
       <c r="G788" s="13" t="inlineStr"/>
@@ -40582,17 +40582,17 @@
       </c>
       <c r="D789" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E789" s="15" t="inlineStr">
         <is>
-          <t>Si «¿A qué institución educativa perteneces?» es «Otra»</t>
+          <t>Si «¿De qué tipo es?» es «Institución educativa»</t>
         </is>
       </c>
       <c r="F789" s="15" t="inlineStr">
         <is>
-          <t>Nombre de la institución</t>
+          <t>Universidad Autónoma Chapingo</t>
         </is>
       </c>
       <c r="G789" s="13" t="inlineStr"/>
@@ -40632,17 +40632,17 @@
       </c>
       <c r="D790" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E790" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Si «¿A qué institución educativa perteneces?» es «Otra»</t>
         </is>
       </c>
       <c r="F790" s="12" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Nombre de la institución</t>
         </is>
       </c>
       <c r="G790" s="13" t="inlineStr"/>
@@ -40692,7 +40692,7 @@
       </c>
       <c r="F791" s="15" t="inlineStr">
         <is>
-          <t>Guardar cambios</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="G791" s="13" t="inlineStr"/>
@@ -40722,12 +40722,12 @@
       </c>
       <c r="B792" s="12" t="inlineStr">
         <is>
-          <t>Cargar el documento correcto</t>
+          <t>Mi perfil</t>
         </is>
       </c>
       <c r="C792" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Adscripción</t>
         </is>
       </c>
       <c r="D792" s="12" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="F792" s="12" t="inlineStr">
         <is>
-          <t>Mis trámites</t>
+          <t>Guardar cambios</t>
         </is>
       </c>
       <c r="G792" s="13" t="inlineStr"/>
@@ -40760,7 +40760,7 @@
       </c>
       <c r="L792" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/corregir.html)</t>
+          <t>Página (sitio/datos.html)</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="D793" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E793" s="15" t="inlineStr">
@@ -40792,7 +40792,7 @@
       </c>
       <c r="F793" s="15" t="inlineStr">
         <is>
-          <t>Cargando tu cita…</t>
+          <t>Mis trámites</t>
         </is>
       </c>
       <c r="G793" s="13" t="inlineStr"/>
@@ -40802,11 +40802,7 @@
         </is>
       </c>
       <c r="I793" s="13" t="inlineStr"/>
-      <c r="J793" s="17" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J793" s="15" t="inlineStr"/>
       <c r="K793" s="16" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -40831,12 +40827,12 @@
       </c>
       <c r="C794" s="12" t="inlineStr">
         <is>
-          <t>Carga el documento correcto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D794" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E794" s="12" t="inlineStr">
@@ -40846,7 +40842,7 @@
       </c>
       <c r="F794" s="12" t="inlineStr">
         <is>
-          <t>Carga el documento correcto</t>
+          <t>Cargando tu cita…</t>
         </is>
       </c>
       <c r="G794" s="13" t="inlineStr"/>
@@ -40856,7 +40852,11 @@
         </is>
       </c>
       <c r="I794" s="13" t="inlineStr"/>
-      <c r="J794" s="12" t="inlineStr"/>
+      <c r="J794" s="18" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K794" s="14" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -40886,7 +40886,7 @@
       </c>
       <c r="D795" s="15" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E795" s="15" t="inlineStr">
@@ -40896,7 +40896,7 @@
       </c>
       <c r="F795" s="15" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Carga el documento correcto</t>
         </is>
       </c>
       <c r="G795" s="13" t="inlineStr"/>
@@ -40936,7 +40936,7 @@
       </c>
       <c r="D796" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E796" s="12" t="inlineStr">
@@ -40946,7 +40946,7 @@
       </c>
       <c r="F796" s="12" t="inlineStr">
         <is>
-          <t>Sólo PDF, de hasta 5 MB. Debe ser el mismo documento que llevas a tu cita.</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G796" s="13" t="inlineStr"/>
@@ -40986,17 +40986,17 @@
       </c>
       <c r="D797" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E797" s="15" t="inlineStr">
         <is>
-          <t>Si «cargar_identificacion_oficial» es «si»</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F797" s="15" t="inlineStr">
         <is>
-          <t>Identificación oficial</t>
+          <t>Sólo PDF, de hasta 5 MB. Debe ser el mismo documento que llevas a tu cita.</t>
         </is>
       </c>
       <c r="G797" s="13" t="inlineStr"/>
@@ -41014,7 +41014,7 @@
       </c>
       <c r="L797" s="16" t="inlineStr">
         <is>
-          <t>Catálogo de requisitos de la base (db/apd/04-apd-catalogos.sql)</t>
+          <t>Página (sitio/corregir.html)</t>
         </is>
       </c>
     </row>
@@ -41036,17 +41036,17 @@
       </c>
       <c r="D798" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E798" s="12" t="inlineStr">
         <is>
-          <t>Si «cargar_identificacion_oficial» es «si» | Si «cargar_curp» es «si» | Si «cargar_comprobante_domicilio» es «si» | Si «cargar_constancia_situacion_fiscal» es «si» | Si «cargar_comprobante_estudios» es «si» | Si «cargar_curriculum_vitae» es «si» | Si «cargar_comprobantes_experiencia» es «si»</t>
+          <t>Si «cargar_identificacion_oficial» es «si»</t>
         </is>
       </c>
       <c r="F798" s="12" t="inlineStr">
         <is>
-          <t>Elegir archivo</t>
+          <t>Identificación oficial</t>
         </is>
       </c>
       <c r="G798" s="13" t="inlineStr"/>
@@ -41064,7 +41064,7 @@
       </c>
       <c r="L798" s="14" t="inlineStr">
         <is>
-          <t>Página (sitio/corregir.html)</t>
+          <t>Catálogo de requisitos de la base (db/apd/04-apd-catalogos.sql)</t>
         </is>
       </c>
     </row>
@@ -41086,17 +41086,17 @@
       </c>
       <c r="D799" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E799" s="15" t="inlineStr">
         <is>
-          <t>Si «cargar_curp» es «si»</t>
+          <t>Si «cargar_identificacion_oficial» es «si» | Si «cargar_curp» es «si» | Si «cargar_comprobante_domicilio» es «si» | Si «cargar_constancia_situacion_fiscal» es «si» | Si «cargar_comprobante_estudios» es «si» | Si «cargar_curriculum_vitae» es «si» | Si «cargar_comprobantes_experiencia» es «si»</t>
         </is>
       </c>
       <c r="F799" s="15" t="inlineStr">
         <is>
-          <t>Clave Única de Registro de Población (CURP)</t>
+          <t>Elegir archivo</t>
         </is>
       </c>
       <c r="G799" s="13" t="inlineStr"/>
@@ -41114,7 +41114,7 @@
       </c>
       <c r="L799" s="16" t="inlineStr">
         <is>
-          <t>Catálogo de requisitos de la base (db/apd/04-apd-catalogos.sql)</t>
+          <t>Página (sitio/corregir.html)</t>
         </is>
       </c>
     </row>
@@ -41141,12 +41141,12 @@
       </c>
       <c r="E800" s="12" t="inlineStr">
         <is>
-          <t>Si «cargar_comprobante_domicilio» es «si»</t>
+          <t>Si «cargar_curp» es «si»</t>
         </is>
       </c>
       <c r="F800" s="12" t="inlineStr">
         <is>
-          <t>Comprobante de domicilio</t>
+          <t>Clave Única de Registro de Población (CURP)</t>
         </is>
       </c>
       <c r="G800" s="13" t="inlineStr"/>
@@ -41191,12 +41191,12 @@
       </c>
       <c r="E801" s="15" t="inlineStr">
         <is>
-          <t>Si «cargar_constancia_situacion_fiscal» es «si»</t>
+          <t>Si «cargar_comprobante_domicilio» es «si»</t>
         </is>
       </c>
       <c r="F801" s="15" t="inlineStr">
         <is>
-          <t>Constancia de situación fiscal</t>
+          <t>Comprobante de domicilio</t>
         </is>
       </c>
       <c r="G801" s="13" t="inlineStr"/>
@@ -41241,12 +41241,12 @@
       </c>
       <c r="E802" s="12" t="inlineStr">
         <is>
-          <t>Si «cargar_comprobante_estudios» es «si»</t>
+          <t>Si «cargar_constancia_situacion_fiscal» es «si»</t>
         </is>
       </c>
       <c r="F802" s="12" t="inlineStr">
         <is>
-          <t>Comprobante de estudios</t>
+          <t>Constancia de situación fiscal</t>
         </is>
       </c>
       <c r="G802" s="13" t="inlineStr"/>
@@ -41291,12 +41291,12 @@
       </c>
       <c r="E803" s="15" t="inlineStr">
         <is>
-          <t>Si «cargar_curriculum_vitae» es «si»</t>
+          <t>Si «cargar_comprobante_estudios» es «si»</t>
         </is>
       </c>
       <c r="F803" s="15" t="inlineStr">
         <is>
-          <t>Currículum vitae</t>
+          <t>Comprobante de estudios</t>
         </is>
       </c>
       <c r="G803" s="13" t="inlineStr"/>
@@ -41341,12 +41341,12 @@
       </c>
       <c r="E804" s="12" t="inlineStr">
         <is>
-          <t>Si «cargar_comprobantes_experiencia» es «si»</t>
+          <t>Si «cargar_curriculum_vitae» es «si»</t>
         </is>
       </c>
       <c r="F804" s="12" t="inlineStr">
         <is>
-          <t>Comprobantes de experiencia</t>
+          <t>Currículum vitae</t>
         </is>
       </c>
       <c r="G804" s="13" t="inlineStr"/>
@@ -41386,17 +41386,17 @@
       </c>
       <c r="D805" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E805" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Si «cargar_comprobantes_experiencia» es «si»</t>
         </is>
       </c>
       <c r="F805" s="15" t="inlineStr">
         <is>
-          <t>Cargar el documento</t>
+          <t>Comprobantes de experiencia</t>
         </is>
       </c>
       <c r="G805" s="13" t="inlineStr"/>
@@ -41414,7 +41414,7 @@
       </c>
       <c r="L805" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/corregir.html)</t>
+          <t>Catálogo de requisitos de la base (db/apd/04-apd-catalogos.sql)</t>
         </is>
       </c>
     </row>
@@ -41436,7 +41436,7 @@
       </c>
       <c r="D806" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E806" s="12" t="inlineStr">
@@ -41446,7 +41446,7 @@
       </c>
       <c r="F806" s="12" t="inlineStr">
         <is>
-          <t>¿Necesitas ayuda para corregir tu documento? Puedes pedirle a un familiar, a un amigo o al personal de la Secretaría que te ayude. También puedes ir al Vivero Nezahualcóyotl (Canal de Chalco s/n, colonia Ciénega Grande, Alcaldía Xochimilco), de lunes a viernes, de 9:00 a 15:00, y ahí te ayudamos.</t>
+          <t>Cargar el documento</t>
         </is>
       </c>
       <c r="G806" s="13" t="inlineStr"/>
@@ -41486,7 +41486,7 @@
       </c>
       <c r="D807" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E807" s="15" t="inlineStr">
@@ -41496,7 +41496,7 @@
       </c>
       <c r="F807" s="15" t="inlineStr">
         <is>
-          <t>Versión de prueba: el archivo se guarda sólo en este navegador.</t>
+          <t>¿Necesitas ayuda para corregir tu documento? Puedes pedirle a un familiar, a un amigo o al personal de la Secretaría que te ayude. También puedes ir al Vivero Nezahualcóyotl (Canal de Chalco s/n, colonia Ciénega Grande, Alcaldía Xochimilco), de lunes a viernes, de 9:00 a 15:00, y ahí te ayudamos.</t>
         </is>
       </c>
       <c r="G807" s="13" t="inlineStr"/>
@@ -41536,7 +41536,7 @@
       </c>
       <c r="D808" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E808" s="12" t="inlineStr">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="F808" s="12" t="inlineStr">
         <is>
-          <t>Ir a Mis trámites</t>
+          <t>Versión de prueba: el archivo se guarda sólo en este navegador.</t>
         </is>
       </c>
       <c r="G808" s="13" t="inlineStr"/>
@@ -41576,12 +41576,12 @@
       </c>
       <c r="B809" s="15" t="inlineStr">
         <is>
-          <t>Material de estudio</t>
+          <t>Cargar el documento correcto</t>
         </is>
       </c>
       <c r="C809" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Carga el documento correcto</t>
         </is>
       </c>
       <c r="D809" s="15" t="inlineStr">
@@ -41596,7 +41596,7 @@
       </c>
       <c r="F809" s="15" t="inlineStr">
         <is>
-          <t>Inicio</t>
+          <t>Ir a Mis trámites</t>
         </is>
       </c>
       <c r="G809" s="13" t="inlineStr"/>
@@ -41614,7 +41614,7 @@
       </c>
       <c r="L809" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/material.html)</t>
+          <t>Página (sitio/corregir.html)</t>
         </is>
       </c>
     </row>
@@ -41631,12 +41631,12 @@
       </c>
       <c r="C810" s="12" t="inlineStr">
         <is>
-          <t>Material de estudio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D810" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E810" s="12" t="inlineStr">
@@ -41646,7 +41646,7 @@
       </c>
       <c r="F810" s="12" t="inlineStr">
         <is>
-          <t>Material de estudio</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="G810" s="13" t="inlineStr"/>
@@ -41686,7 +41686,7 @@
       </c>
       <c r="D811" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E811" s="15" t="inlineStr">
@@ -41696,7 +41696,7 @@
       </c>
       <c r="F811" s="15" t="inlineStr">
         <is>
-          <t>Los documentos de la Secretaría para preparar el examen de acreditación. No necesitas cuenta.</t>
+          <t>Material de estudio</t>
         </is>
       </c>
       <c r="G811" s="13" t="inlineStr"/>
@@ -41736,7 +41736,7 @@
       </c>
       <c r="D812" s="12" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E812" s="12" t="inlineStr">
@@ -41746,7 +41746,7 @@
       </c>
       <c r="F812" s="12" t="inlineStr">
         <is>
-          <t>El examen es a libro cerrado Estudia estos documentos antes del examen: durante el examen no se pueden consultar.</t>
+          <t>Los documentos de la Secretaría para preparar el examen de acreditación. No necesitas cuenta.</t>
         </is>
       </c>
       <c r="G812" s="13" t="inlineStr"/>
@@ -41786,7 +41786,7 @@
       </c>
       <c r="D813" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E813" s="15" t="inlineStr">
@@ -41796,7 +41796,7 @@
       </c>
       <c r="F813" s="15" t="inlineStr">
         <is>
-          <t>Poda y derribo</t>
+          <t>El examen es a libro cerrado Estudia estos documentos antes del examen: durante el examen no se pueden consultar.</t>
         </is>
       </c>
       <c r="G813" s="13" t="inlineStr"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="F814" s="12" t="inlineStr">
         <is>
-          <t>Dictaminador técnico</t>
+          <t>Poda y derribo</t>
         </is>
       </c>
       <c r="G814" s="13" t="inlineStr"/>
@@ -41886,7 +41886,7 @@
       </c>
       <c r="D815" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E815" s="15" t="inlineStr">
@@ -41896,7 +41896,7 @@
       </c>
       <c r="F815" s="15" t="inlineStr">
         <is>
-          <t>Pendiente (P136): el temario del examen por tema. Los apartados de cada documento son una propuesta tomada de su índice.</t>
+          <t>Dictaminador técnico</t>
         </is>
       </c>
       <c r="G815" s="13" t="inlineStr"/>
@@ -41936,7 +41936,7 @@
       </c>
       <c r="D816" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E816" s="12" t="inlineStr">
@@ -41946,7 +41946,7 @@
       </c>
       <c r="F816" s="12" t="inlineStr">
         <is>
-          <t>Todavía no hay material publicado. Vuelve a consultar más adelante.</t>
+          <t>Pendiente (P136): el temario del examen por tema. Los apartados de cada documento son una propuesta tomada de su índice.</t>
         </is>
       </c>
       <c r="G816" s="13" t="inlineStr"/>
@@ -41976,17 +41976,17 @@
       </c>
       <c r="B817" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Material de estudio</t>
         </is>
       </c>
       <c r="C817" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Material de estudio</t>
         </is>
       </c>
       <c r="D817" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E817" s="15" t="inlineStr">
@@ -41996,7 +41996,7 @@
       </c>
       <c r="F817" s="15" t="inlineStr">
         <is>
-          <t>Mis trámites</t>
+          <t>Todavía no hay material publicado. Vuelve a consultar más adelante.</t>
         </is>
       </c>
       <c r="G817" s="13" t="inlineStr"/>
@@ -42014,7 +42014,7 @@
       </c>
       <c r="L817" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/reposicion.html)</t>
+          <t>Página (sitio/material.html)</t>
         </is>
       </c>
     </row>
@@ -42036,7 +42036,7 @@
       </c>
       <c r="D818" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E818" s="12" t="inlineStr">
@@ -42046,7 +42046,7 @@
       </c>
       <c r="F818" s="12" t="inlineStr">
         <is>
-          <t>Cargando tu acreditación…</t>
+          <t>Mis trámites</t>
         </is>
       </c>
       <c r="G818" s="13" t="inlineStr"/>
@@ -42056,11 +42056,7 @@
         </is>
       </c>
       <c r="I818" s="13" t="inlineStr"/>
-      <c r="J818" s="18" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J818" s="12" t="inlineStr"/>
       <c r="K818" s="14" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -42085,12 +42081,12 @@
       </c>
       <c r="C819" s="15" t="inlineStr">
         <is>
-          <t>Pide la reposición de tu credencial</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D819" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E819" s="15" t="inlineStr">
@@ -42100,7 +42096,7 @@
       </c>
       <c r="F819" s="15" t="inlineStr">
         <is>
-          <t>Pide la reposición de tu credencial</t>
+          <t>Cargando tu acreditación…</t>
         </is>
       </c>
       <c r="G819" s="13" t="inlineStr"/>
@@ -42110,7 +42106,11 @@
         </is>
       </c>
       <c r="I819" s="13" t="inlineStr"/>
-      <c r="J819" s="15" t="inlineStr"/>
+      <c r="J819" s="17" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K819" s="16" t="inlineStr">
         <is>
           <t>Persona solicitante</t>
@@ -42140,7 +42140,7 @@
       </c>
       <c r="D820" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E820" s="12" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="F820" s="12" t="inlineStr">
         <is>
-          <t>Si perdiste tu credencial o te la robaron, carga el acta que levantaste. La Secretaría la revisa y te dice cuánto pagar y dónde recoger tu credencial nueva.</t>
+          <t>Pide la reposición de tu credencial</t>
         </is>
       </c>
       <c r="G820" s="13" t="inlineStr"/>
@@ -42190,7 +42190,7 @@
       </c>
       <c r="D821" s="15" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E821" s="15" t="inlineStr">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="F821" s="15" t="inlineStr">
         <is>
-          <t>Las preguntas con * son obligatorias.</t>
+          <t>Si perdiste tu credencial o te la robaron, carga el acta que levantaste. La Secretaría la revisa y te dice cuánto pagar y dónde recoger tu credencial nueva.</t>
         </is>
       </c>
       <c r="G821" s="13" t="inlineStr"/>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="D822" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="E822" s="12" t="inlineStr">
@@ -42250,7 +42250,7 @@
       </c>
       <c r="F822" s="12" t="inlineStr">
         <is>
-          <t>¿Qué pasó con tu credencial?</t>
+          <t>Las preguntas con * son obligatorias.</t>
         </is>
       </c>
       <c r="G822" s="13" t="inlineStr"/>
@@ -42290,7 +42290,7 @@
       </c>
       <c r="D823" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E823" s="15" t="inlineStr">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="F823" s="15" t="inlineStr">
         <is>
-          <t>La perdí</t>
+          <t>¿Qué pasó con tu credencial?</t>
         </is>
       </c>
       <c r="G823" s="13" t="inlineStr"/>
@@ -42350,7 +42350,7 @@
       </c>
       <c r="F824" s="12" t="inlineStr">
         <is>
-          <t>Me la robaron</t>
+          <t>La perdí</t>
         </is>
       </c>
       <c r="G824" s="13" t="inlineStr"/>
@@ -42390,7 +42390,7 @@
       </c>
       <c r="D825" s="15" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E825" s="15" t="inlineStr">
@@ -42400,7 +42400,7 @@
       </c>
       <c r="F825" s="15" t="inlineStr">
         <is>
-          <t>Acta que levantaste por la pérdida o el robo</t>
+          <t>Me la robaron</t>
         </is>
       </c>
       <c r="G825" s="13" t="inlineStr"/>
@@ -42440,7 +42440,7 @@
       </c>
       <c r="D826" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E826" s="12" t="inlineStr">
@@ -42450,7 +42450,7 @@
       </c>
       <c r="F826" s="12" t="inlineStr">
         <is>
-          <t>En PDF o en foto (JPG o PNG), de hasta 5 MB. Que se lean completos tu nombre, la fecha y los datos de quien la levantó.</t>
+          <t>Acta que levantaste por la pérdida o el robo</t>
         </is>
       </c>
       <c r="G826" s="13" t="inlineStr"/>
@@ -42490,7 +42490,7 @@
       </c>
       <c r="D827" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E827" s="15" t="inlineStr">
@@ -42500,7 +42500,7 @@
       </c>
       <c r="F827" s="15" t="inlineStr">
         <is>
-          <t>Elegir archivo</t>
+          <t>En PDF o en foto (JPG o PNG), de hasta 5 MB. Que se lean completos tu nombre, la fecha y los datos de quien la levantó.</t>
         </is>
       </c>
       <c r="G827" s="13" t="inlineStr"/>
@@ -42550,7 +42550,7 @@
       </c>
       <c r="F828" s="12" t="inlineStr">
         <is>
-          <t>Pedir la reposición</t>
+          <t>Elegir archivo</t>
         </is>
       </c>
       <c r="G828" s="13" t="inlineStr"/>
@@ -42590,7 +42590,7 @@
       </c>
       <c r="D829" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E829" s="15" t="inlineStr">
@@ -42600,7 +42600,7 @@
       </c>
       <c r="F829" s="15" t="inlineStr">
         <is>
-          <t>Versión de prueba: el acta se guarda sólo en este navegador.</t>
+          <t>Pedir la reposición</t>
         </is>
       </c>
       <c r="G829" s="13" t="inlineStr"/>
@@ -42640,7 +42640,7 @@
       </c>
       <c r="D830" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E830" s="12" t="inlineStr">
@@ -42650,7 +42650,7 @@
       </c>
       <c r="F830" s="12" t="inlineStr">
         <is>
-          <t>Ir a Mis trámites</t>
+          <t>Versión de prueba: el acta se guarda sólo en este navegador.</t>
         </is>
       </c>
       <c r="G830" s="13" t="inlineStr"/>
@@ -42680,17 +42680,17 @@
       </c>
       <c r="B831" s="15" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C831" s="15" t="inlineStr">
         <is>
-          <t>Grupos</t>
+          <t>Pide la reposición de tu credencial</t>
         </is>
       </c>
       <c r="D831" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E831" s="15" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="F831" s="15" t="inlineStr">
         <is>
-          <t>Grupos</t>
+          <t>Ir a Mis trámites</t>
         </is>
       </c>
       <c r="G831" s="13" t="inlineStr"/>
@@ -42713,12 +42713,12 @@
       <c r="J831" s="15" t="inlineStr"/>
       <c r="K831" s="16" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L831" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/grupos.html)</t>
+          <t>Página (sitio/reposicion.html)</t>
         </is>
       </c>
     </row>
@@ -42740,7 +42740,7 @@
       </c>
       <c r="D832" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E832" s="12" t="inlineStr">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="F832" s="12" t="inlineStr">
         <is>
-          <t>Cargando los grupos…</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="G832" s="13" t="inlineStr"/>
@@ -42760,11 +42760,7 @@
         </is>
       </c>
       <c r="I832" s="13" t="inlineStr"/>
-      <c r="J832" s="18" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J832" s="12" t="inlineStr"/>
       <c r="K832" s="14" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -42794,7 +42790,7 @@
       </c>
       <c r="D833" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E833" s="15" t="inlineStr">
@@ -42804,7 +42800,7 @@
       </c>
       <c r="F833" s="15" t="inlineStr">
         <is>
-          <t>Ver los grupos programados</t>
+          <t>Cargando los grupos…</t>
         </is>
       </c>
       <c r="G833" s="13" t="inlineStr"/>
@@ -42814,7 +42810,11 @@
         </is>
       </c>
       <c r="I833" s="13" t="inlineStr"/>
-      <c r="J833" s="15" t="inlineStr"/>
+      <c r="J833" s="17" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K833" s="16" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -42854,7 +42854,7 @@
       </c>
       <c r="F834" s="12" t="inlineStr">
         <is>
-          <t>Armar un grupo</t>
+          <t>Ver los grupos programados</t>
         </is>
       </c>
       <c r="G834" s="13" t="inlineStr"/>
@@ -42904,7 +42904,7 @@
       </c>
       <c r="F835" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Armar un grupo</t>
         </is>
       </c>
       <c r="G835" s="13" t="inlineStr"/>
@@ -42954,7 +42954,7 @@
       </c>
       <c r="F836" s="12" t="inlineStr">
         <is>
-          <t>Ya terminaron</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="G836" s="13" t="inlineStr"/>
@@ -42989,12 +42989,12 @@
       </c>
       <c r="C837" s="15" t="inlineStr">
         <is>
-          <t>Armar un grupo</t>
+          <t>Grupos</t>
         </is>
       </c>
       <c r="D837" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E837" s="15" t="inlineStr">
@@ -43004,7 +43004,7 @@
       </c>
       <c r="F837" s="15" t="inlineStr">
         <is>
-          <t>Armar un grupo</t>
+          <t>Ya terminaron</t>
         </is>
       </c>
       <c r="G837" s="13" t="inlineStr"/>
@@ -43039,7 +43039,7 @@
       </c>
       <c r="C838" s="12" t="inlineStr">
         <is>
-          <t>El curso</t>
+          <t>Armar un grupo</t>
         </is>
       </c>
       <c r="D838" s="12" t="inlineStr">
@@ -43054,7 +43054,7 @@
       </c>
       <c r="F838" s="12" t="inlineStr">
         <is>
-          <t>¿Para qué curso?</t>
+          <t>Armar un grupo</t>
         </is>
       </c>
       <c r="G838" s="13" t="inlineStr"/>
@@ -43094,7 +43094,7 @@
       </c>
       <c r="D839" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E839" s="15" t="inlineStr">
@@ -43104,7 +43104,7 @@
       </c>
       <c r="F839" s="15" t="inlineStr">
         <is>
-          <t>Cada curso arma sus grupos por separado: nunca se mezclan.</t>
+          <t>¿Para qué curso?</t>
         </is>
       </c>
       <c r="G839" s="13" t="inlineStr"/>
@@ -43144,7 +43144,7 @@
       </c>
       <c r="D840" s="12" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E840" s="12" t="inlineStr">
@@ -43154,7 +43154,7 @@
       </c>
       <c r="F840" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poda y derribo · nueva — </t>
+          <t>Cada curso arma sus grupos por separado: nunca se mezclan.</t>
         </is>
       </c>
       <c r="G840" s="13" t="inlineStr"/>
@@ -43204,7 +43204,7 @@
       </c>
       <c r="F841" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poda y derribo · renovación — </t>
+          <t xml:space="preserve">Poda y derribo · nueva — </t>
         </is>
       </c>
       <c r="G841" s="13" t="inlineStr"/>
@@ -43254,7 +43254,7 @@
       </c>
       <c r="F842" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dictaminador técnico · nueva — </t>
+          <t xml:space="preserve">Poda y derribo · renovación — </t>
         </is>
       </c>
       <c r="G842" s="13" t="inlineStr"/>
@@ -43304,7 +43304,7 @@
       </c>
       <c r="F843" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dictaminador técnico · renovación — </t>
+          <t xml:space="preserve">Dictaminador técnico · nueva — </t>
         </is>
       </c>
       <c r="G843" s="13" t="inlineStr"/>
@@ -43344,7 +43344,7 @@
       </c>
       <c r="D844" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E844" s="12" t="inlineStr">
@@ -43354,7 +43354,7 @@
       </c>
       <c r="F844" s="12" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t xml:space="preserve">Dictaminador técnico · renovación — </t>
         </is>
       </c>
       <c r="G844" s="13" t="inlineStr"/>
@@ -43389,12 +43389,12 @@
       </c>
       <c r="C845" s="15" t="inlineStr">
         <is>
-          <t>La semana</t>
+          <t>El curso</t>
         </is>
       </c>
       <c r="D845" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E845" s="15" t="inlineStr">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="F845" s="15" t="inlineStr">
         <is>
-          <t>¿Qué semana?</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G845" s="13" t="inlineStr"/>
@@ -43444,7 +43444,7 @@
       </c>
       <c r="D846" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E846" s="12" t="inlineStr">
@@ -43454,7 +43454,7 @@
       </c>
       <c r="F846" s="12" t="inlineStr">
         <is>
-          <t>Semana elegida</t>
+          <t>¿Qué semana?</t>
         </is>
       </c>
       <c r="G846" s="13" t="inlineStr"/>
@@ -43504,7 +43504,7 @@
       </c>
       <c r="F847" s="15" t="inlineStr">
         <is>
-          <t>Ninguna todavía</t>
+          <t>Semana elegida</t>
         </is>
       </c>
       <c r="G847" s="13" t="inlineStr"/>
@@ -43544,7 +43544,7 @@
       </c>
       <c r="D848" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E848" s="12" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="F848" s="12" t="inlineStr">
         <is>
-          <t>Primer día del curso</t>
+          <t>Ninguna todavía</t>
         </is>
       </c>
       <c r="G848" s="13" t="inlineStr"/>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="D849" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E849" s="15" t="inlineStr">
@@ -43604,7 +43604,7 @@
       </c>
       <c r="F849" s="15" t="inlineStr">
         <is>
-          <t>Se llena al elegir la semana en el calendario.</t>
+          <t>Primer día del curso</t>
         </is>
       </c>
       <c r="G849" s="13" t="inlineStr"/>
@@ -43644,7 +43644,7 @@
       </c>
       <c r="D850" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E850" s="12" t="inlineStr">
@@ -43654,7 +43654,7 @@
       </c>
       <c r="F850" s="12" t="inlineStr">
         <is>
-          <t>Semana libre: toque «Libre» para elegirla</t>
+          <t>Se llena al elegir la semana en el calendario.</t>
         </is>
       </c>
       <c r="G850" s="13" t="inlineStr"/>
@@ -43704,7 +43704,7 @@
       </c>
       <c r="F851" s="15" t="inlineStr">
         <is>
-          <t>El grupo nuevo</t>
+          <t>Semana libre: toque «Libre» para elegirla</t>
         </is>
       </c>
       <c r="G851" s="13" t="inlineStr"/>
@@ -43754,7 +43754,7 @@
       </c>
       <c r="F852" s="12" t="inlineStr">
         <is>
-          <t>Grupo por confirmar</t>
+          <t>El grupo nuevo</t>
         </is>
       </c>
       <c r="G852" s="13" t="inlineStr"/>
@@ -43804,7 +43804,7 @@
       </c>
       <c r="F853" s="15" t="inlineStr">
         <is>
-          <t>Grupo confirmado</t>
+          <t>Grupo por confirmar</t>
         </is>
       </c>
       <c r="G853" s="13" t="inlineStr"/>
@@ -43854,7 +43854,7 @@
       </c>
       <c r="F854" s="12" t="inlineStr">
         <is>
-          <t>Grupo en curso</t>
+          <t>Grupo confirmado</t>
         </is>
       </c>
       <c r="G854" s="13" t="inlineStr"/>
@@ -43904,7 +43904,7 @@
       </c>
       <c r="F855" s="15" t="inlineStr">
         <is>
-          <t>Grupo que ya terminó</t>
+          <t>Grupo en curso</t>
         </is>
       </c>
       <c r="G855" s="13" t="inlineStr"/>
@@ -43954,7 +43954,7 @@
       </c>
       <c r="F856" s="12" t="inlineStr">
         <is>
-          <t>Grupo de otro curso: también cuenta para el máximo</t>
+          <t>Grupo que ya terminó</t>
         </is>
       </c>
       <c r="G856" s="13" t="inlineStr"/>
@@ -44004,7 +44004,7 @@
       </c>
       <c r="F857" s="15" t="inlineStr">
         <is>
-          <t>No disponible: ya pasó, faltan menos de 7 días o ya hay 2 grupos</t>
+          <t>Grupo de otro curso: también cuenta para el máximo</t>
         </is>
       </c>
       <c r="G857" s="13" t="inlineStr"/>
@@ -44054,7 +44054,7 @@
       </c>
       <c r="F858" s="12" t="inlineStr">
         <is>
-          <t>Sábado y domingo: no hay curso</t>
+          <t>No disponible: ya pasó, faltan menos de 7 días o ya hay 2 grupos</t>
         </is>
       </c>
       <c r="G858" s="13" t="inlineStr"/>
@@ -44104,7 +44104,7 @@
       </c>
       <c r="F859" s="15" t="inlineStr">
         <is>
-          <t>Día inhábil [por confirmar con el calendario oficial de la Secretaría]</t>
+          <t>Sábado y domingo: no hay curso</t>
         </is>
       </c>
       <c r="G859" s="13" t="inlineStr"/>
@@ -44144,7 +44144,7 @@
       </c>
       <c r="D860" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E860" s="12" t="inlineStr">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="F860" s="12" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Día inhábil [por confirmar con el calendario oficial de la Secretaría]</t>
         </is>
       </c>
       <c r="G860" s="13" t="inlineStr"/>
@@ -44204,7 +44204,7 @@
       </c>
       <c r="F861" s="15" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G861" s="13" t="inlineStr"/>
@@ -44239,12 +44239,12 @@
       </c>
       <c r="C862" s="12" t="inlineStr">
         <is>
-          <t>Quiénes van</t>
+          <t>La semana</t>
         </is>
       </c>
       <c r="D862" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E862" s="12" t="inlineStr">
@@ -44254,7 +44254,7 @@
       </c>
       <c r="F862" s="12" t="inlineStr">
         <is>
-          <t>¿Quiénes van?</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G862" s="13" t="inlineStr"/>
@@ -44294,7 +44294,7 @@
       </c>
       <c r="D863" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E863" s="15" t="inlineStr">
@@ -44304,7 +44304,7 @@
       </c>
       <c r="F863" s="15" t="inlineStr">
         <is>
-          <t>Si hay más de 25, entran las que más esperan y las de una misma institución de gobierno van juntas; el resto sigue en espera para otra semana.</t>
+          <t>¿Quiénes van?</t>
         </is>
       </c>
       <c r="G863" s="13" t="inlineStr"/>
@@ -44344,7 +44344,7 @@
       </c>
       <c r="D864" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E864" s="12" t="inlineStr">
@@ -44354,7 +44354,7 @@
       </c>
       <c r="F864" s="12" t="inlineStr">
         <is>
-          <t>¿De quiénes es el grupo?</t>
+          <t>Si hay más de 25, entran las que más esperan y las de una misma institución de gobierno van juntas; el resto sigue en espera para otra semana.</t>
         </is>
       </c>
       <c r="G864" s="13" t="inlineStr"/>
@@ -44394,7 +44394,7 @@
       </c>
       <c r="D865" s="15" t="inlineStr">
         <is>
-          <t>Opción</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E865" s="15" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="F865" s="15" t="inlineStr">
         <is>
-          <t>Combinado — Recibe personas de cualquier organización e independientes.</t>
+          <t>¿De quiénes es el grupo?</t>
         </is>
       </c>
       <c r="G865" s="13" t="inlineStr"/>
@@ -44454,7 +44454,7 @@
       </c>
       <c r="F866" s="12" t="inlineStr">
         <is>
-          <t>Sólo de una institución de gobierno — Recibe únicamente a la gente de esa institución: todas las elegidas tienen que ser de ella.</t>
+          <t>Combinado — Recibe personas de cualquier organización e independientes.</t>
         </is>
       </c>
       <c r="G866" s="13" t="inlineStr"/>
@@ -44494,7 +44494,7 @@
       </c>
       <c r="D867" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Opción</t>
         </is>
       </c>
       <c r="E867" s="15" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="F867" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Sólo de una institución de gobierno — Recibe únicamente a la gente de esa institución: todas las elegidas tienen que ser de ella.</t>
         </is>
       </c>
       <c r="G867" s="13" t="inlineStr"/>
@@ -44554,7 +44554,7 @@
       </c>
       <c r="F868" s="12" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G868" s="13" t="inlineStr"/>
@@ -44589,12 +44589,12 @@
       </c>
       <c r="C869" s="15" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Quiénes van</t>
         </is>
       </c>
       <c r="D869" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E869" s="15" t="inlineStr">
@@ -44604,7 +44604,7 @@
       </c>
       <c r="F869" s="15" t="inlineStr">
         <is>
-          <t>Revise y confirme</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G869" s="13" t="inlineStr"/>
@@ -44644,7 +44644,7 @@
       </c>
       <c r="D870" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E870" s="12" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="F870" s="12" t="inlineStr">
         <is>
-          <t>La persona instructora la asigna el área de Instructores y Capacitación, que también confirma el grupo.</t>
+          <t>Revise y confirme</t>
         </is>
       </c>
       <c r="G870" s="13" t="inlineStr"/>
@@ -44694,7 +44694,7 @@
       </c>
       <c r="D871" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E871" s="15" t="inlineStr">
@@ -44704,7 +44704,7 @@
       </c>
       <c r="F871" s="15" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>La persona instructora la asigna el área de Instructores y Capacitación, que también confirma el grupo.</t>
         </is>
       </c>
       <c r="G871" s="13" t="inlineStr"/>
@@ -44754,7 +44754,7 @@
       </c>
       <c r="F872" s="12" t="inlineStr">
         <is>
-          <t>Crear el grupo</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G872" s="13" t="inlineStr"/>
@@ -44789,12 +44789,12 @@
       </c>
       <c r="C873" s="15" t="inlineStr">
         <is>
-          <t>Tu grupo</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="D873" s="15" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E873" s="15" t="inlineStr">
@@ -44804,7 +44804,7 @@
       </c>
       <c r="F873" s="15" t="inlineStr">
         <is>
-          <t>Tu grupo</t>
+          <t>Crear el grupo</t>
         </is>
       </c>
       <c r="G873" s="13" t="inlineStr"/>
@@ -44844,7 +44844,7 @@
       </c>
       <c r="D874" s="12" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E874" s="12" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="F874" s="12" t="inlineStr">
         <is>
-          <t>Atrás</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="G874" s="13" t="inlineStr"/>
@@ -44904,7 +44904,7 @@
       </c>
       <c r="F875" s="15" t="inlineStr">
         <is>
-          <t>Siguiente</t>
+          <t>Atrás</t>
         </is>
       </c>
       <c r="G875" s="13" t="inlineStr"/>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="C876" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Tu grupo</t>
         </is>
       </c>
       <c r="D876" s="12" t="inlineStr">
         <is>
-          <t>Subtítulo</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E876" s="12" t="inlineStr">
@@ -44954,7 +44954,7 @@
       </c>
       <c r="F876" s="12" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Siguiente</t>
         </is>
       </c>
       <c r="G876" s="13" t="inlineStr"/>
@@ -44994,7 +44994,7 @@
       </c>
       <c r="D877" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Subtítulo</t>
         </is>
       </c>
       <c r="E877" s="15" t="inlineStr">
@@ -45004,7 +45004,7 @@
       </c>
       <c r="F877" s="15" t="inlineStr">
         <is>
-          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="G877" s="13" t="inlineStr"/>
@@ -45044,7 +45044,7 @@
       </c>
       <c r="D878" s="12" t="inlineStr">
         <is>
-          <t>Título desplegable</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E878" s="12" t="inlineStr">
@@ -45054,7 +45054,7 @@
       </c>
       <c r="F878" s="12" t="inlineStr">
         <is>
-          <t>Grupos que ya terminaron</t>
+          <t>Por curso: los grupos por confirmar, confirmados y en curso, con lo que les falta. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
         </is>
       </c>
       <c r="G878" s="13" t="inlineStr"/>
@@ -45094,7 +45094,7 @@
       </c>
       <c r="D879" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Título desplegable</t>
         </is>
       </c>
       <c r="E879" s="15" t="inlineStr">
@@ -45104,7 +45104,7 @@
       </c>
       <c r="F879" s="15" t="inlineStr">
         <is>
-          <t>Todavía no hay grupos que hayan terminado.</t>
+          <t>Grupos que ya terminaron</t>
         </is>
       </c>
       <c r="G879" s="13" t="inlineStr"/>
@@ -45144,7 +45144,7 @@
       </c>
       <c r="D880" s="12" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E880" s="12" t="inlineStr">
@@ -45154,7 +45154,7 @@
       </c>
       <c r="F880" s="12" t="inlineStr">
         <is>
-          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas y su persona instructora, y recibe hasta 25. Sólo las instituciones de gobierno tienen grupo propio. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
+          <t>Todavía no hay grupos que hayan terminado.</t>
         </is>
       </c>
       <c r="G880" s="13" t="inlineStr"/>
@@ -45184,17 +45184,17 @@
       </c>
       <c r="B881" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C881" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D881" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E881" s="15" t="inlineStr">
@@ -45204,7 +45204,7 @@
       </c>
       <c r="F881" s="15" t="inlineStr">
         <is>
-          <t>Grupos por asignar y confirmar</t>
+          <t>Los cuatro cursos nunca se mezclan; un grupo se confirma con al menos 5 personas y su persona instructora, y recibe hasta 25. Sólo las instituciones de gobierno tienen grupo propio. La persona instructora la asigna y el grupo lo confirma el área de Instructores y Capacitación.</t>
         </is>
       </c>
       <c r="G881" s="13" t="inlineStr"/>
@@ -45222,7 +45222,7 @@
       </c>
       <c r="L881" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/capacitacion.html)</t>
+          <t>Página (sitio/grupos.html)</t>
         </is>
       </c>
     </row>
@@ -45244,7 +45244,7 @@
       </c>
       <c r="D882" s="12" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E882" s="12" t="inlineStr">
@@ -45254,7 +45254,7 @@
       </c>
       <c r="F882" s="12" t="inlineStr">
         <is>
-          <t>Los grupos que esperan persona instructora o confirmación, del que empieza antes al más lejano. En la ficha de cada uno se asigna a la persona instructora, libre esas fechas, y se confirma el grupo.</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="G882" s="13" t="inlineStr"/>
@@ -45294,7 +45294,7 @@
       </c>
       <c r="D883" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E883" s="15" t="inlineStr">
@@ -45304,7 +45304,7 @@
       </c>
       <c r="F883" s="15" t="inlineStr">
         <is>
-          <t>Cargando los grupos…</t>
+          <t>Los grupos que esperan persona instructora o confirmación, del que empieza antes al más lejano. En la ficha de cada uno se asigna a la persona instructora, libre esas fechas, y se confirma el grupo.</t>
         </is>
       </c>
       <c r="G883" s="13" t="inlineStr"/>
@@ -45314,11 +45314,7 @@
         </is>
       </c>
       <c r="I883" s="13" t="inlineStr"/>
-      <c r="J883" s="17" t="inlineStr">
-        <is>
-          <t>Texto momentáneo mientras cargan los datos.</t>
-        </is>
-      </c>
+      <c r="J883" s="15" t="inlineStr"/>
       <c r="K883" s="16" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -45348,7 +45344,7 @@
       </c>
       <c r="D884" s="12" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E884" s="12" t="inlineStr">
@@ -45358,7 +45354,7 @@
       </c>
       <c r="F884" s="12" t="inlineStr">
         <is>
-          <t>Grupo</t>
+          <t>Cargando los grupos…</t>
         </is>
       </c>
       <c r="G884" s="13" t="inlineStr"/>
@@ -45368,7 +45364,11 @@
         </is>
       </c>
       <c r="I884" s="13" t="inlineStr"/>
-      <c r="J884" s="12" t="inlineStr"/>
+      <c r="J884" s="18" t="inlineStr">
+        <is>
+          <t>Texto momentáneo mientras cargan los datos.</t>
+        </is>
+      </c>
       <c r="K884" s="14" t="inlineStr">
         <is>
           <t>Personal de la Secretaría</t>
@@ -45408,7 +45408,7 @@
       </c>
       <c r="F885" s="15" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Grupo</t>
         </is>
       </c>
       <c r="G885" s="13" t="inlineStr"/>
@@ -45458,7 +45458,7 @@
       </c>
       <c r="F886" s="12" t="inlineStr">
         <is>
-          <t>Personas</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="G886" s="13" t="inlineStr"/>
@@ -45508,7 +45508,7 @@
       </c>
       <c r="F887" s="15" t="inlineStr">
         <is>
-          <t>Persona instructora</t>
+          <t>Personas</t>
         </is>
       </c>
       <c r="G887" s="13" t="inlineStr"/>
@@ -45558,7 +45558,7 @@
       </c>
       <c r="F888" s="12" t="inlineStr">
         <is>
-          <t>Lo que falta</t>
+          <t>Persona instructora</t>
         </is>
       </c>
       <c r="G888" s="13" t="inlineStr"/>
@@ -45598,7 +45598,7 @@
       </c>
       <c r="D889" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E889" s="15" t="inlineStr">
@@ -45608,7 +45608,7 @@
       </c>
       <c r="F889" s="15" t="inlineStr">
         <is>
-          <t>Ningún grupo espera persona instructora ni confirmación.</t>
+          <t>Lo que falta</t>
         </is>
       </c>
       <c r="G889" s="13" t="inlineStr"/>
@@ -45643,12 +45643,12 @@
       </c>
       <c r="C890" s="12" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Grupos por asignar y confirmar</t>
         </is>
       </c>
       <c r="D890" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E890" s="12" t="inlineStr">
@@ -45658,7 +45658,7 @@
       </c>
       <c r="F890" s="12" t="inlineStr">
         <is>
-          <t>Grupos confirmados y en curso</t>
+          <t>Ningún grupo espera persona instructora ni confirmación.</t>
         </is>
       </c>
       <c r="G890" s="13" t="inlineStr"/>
@@ -45698,7 +45698,7 @@
       </c>
       <c r="D891" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E891" s="15" t="inlineStr">
@@ -45708,7 +45708,7 @@
       </c>
       <c r="F891" s="15" t="inlineStr">
         <is>
-          <t>Si hace falta, cambie a la persona instructora, también durante el curso: el cambio queda en la bitácora.</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="G891" s="13" t="inlineStr"/>
@@ -45748,7 +45748,7 @@
       </c>
       <c r="D892" s="12" t="inlineStr">
         <is>
-          <t>Encabezado de tabla</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E892" s="12" t="inlineStr">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="F892" s="12" t="inlineStr">
         <is>
-          <t>Grupo</t>
+          <t>Si hace falta, cambie a la persona instructora, también durante el curso: el cambio queda en la bitácora.</t>
         </is>
       </c>
       <c r="G892" s="13" t="inlineStr"/>
@@ -45808,7 +45808,7 @@
       </c>
       <c r="F893" s="15" t="inlineStr">
         <is>
-          <t>Semana</t>
+          <t>Grupo</t>
         </is>
       </c>
       <c r="G893" s="13" t="inlineStr"/>
@@ -45858,7 +45858,7 @@
       </c>
       <c r="F894" s="12" t="inlineStr">
         <is>
-          <t>Situación</t>
+          <t>Semana</t>
         </is>
       </c>
       <c r="G894" s="13" t="inlineStr"/>
@@ -45908,7 +45908,7 @@
       </c>
       <c r="F895" s="15" t="inlineStr">
         <is>
-          <t>Persona instructora</t>
+          <t>Situación</t>
         </is>
       </c>
       <c r="G895" s="13" t="inlineStr"/>
@@ -45948,7 +45948,7 @@
       </c>
       <c r="D896" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Encabezado de tabla</t>
         </is>
       </c>
       <c r="E896" s="12" t="inlineStr">
@@ -45958,7 +45958,7 @@
       </c>
       <c r="F896" s="12" t="inlineStr">
         <is>
-          <t>No hay grupos confirmados ni en curso.</t>
+          <t>Persona instructora</t>
         </is>
       </c>
       <c r="G896" s="13" t="inlineStr"/>
@@ -45988,17 +45988,17 @@
       </c>
       <c r="B897" s="15" t="inlineStr">
         <is>
-          <t>Consultar un trámite (personal)</t>
+          <t>Grupos por asignar y confirmar (personal)</t>
         </is>
       </c>
       <c r="C897" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grupos confirmados y en curso</t>
         </is>
       </c>
       <c r="D897" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E897" s="15" t="inlineStr">
@@ -46008,7 +46008,7 @@
       </c>
       <c r="F897" s="15" t="inlineStr">
         <is>
-          <t>Inicio del personal</t>
+          <t>No hay grupos confirmados ni en curso.</t>
         </is>
       </c>
       <c r="G897" s="13" t="inlineStr"/>
@@ -46026,7 +46026,7 @@
       </c>
       <c r="L897" s="16" t="inlineStr">
         <is>
-          <t>Página (sitio/ventanilla.html)</t>
+          <t>Página (sitio/capacitacion.html)</t>
         </is>
       </c>
     </row>
@@ -46043,12 +46043,12 @@
       </c>
       <c r="C898" s="12" t="inlineStr">
         <is>
-          <t>Consultar un trámite</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D898" s="12" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E898" s="12" t="inlineStr">
@@ -46058,7 +46058,7 @@
       </c>
       <c r="F898" s="12" t="inlineStr">
         <is>
-          <t>Consultar un trámite</t>
+          <t>Inicio del personal</t>
         </is>
       </c>
       <c r="G898" s="13" t="inlineStr"/>
@@ -46098,7 +46098,7 @@
       </c>
       <c r="D899" s="15" t="inlineStr">
         <is>
-          <t>Introducción</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E899" s="15" t="inlineStr">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="F899" s="15" t="inlineStr">
         <is>
-          <t>Busque a la persona y dígale en qué va su trámite. Lo de «Qué decirle» va escrito para ella, en palabras sencillas.</t>
+          <t>Consultar un trámite</t>
         </is>
       </c>
       <c r="G899" s="13" t="inlineStr"/>
@@ -46148,7 +46148,7 @@
       </c>
       <c r="D900" s="12" t="inlineStr">
         <is>
-          <t>Pregunta</t>
+          <t>Introducción</t>
         </is>
       </c>
       <c r="E900" s="12" t="inlineStr">
@@ -46158,7 +46158,7 @@
       </c>
       <c r="F900" s="12" t="inlineStr">
         <is>
-          <t>CURP, nombre o folio</t>
+          <t>Busque a la persona y dígale en qué va su trámite. Lo de «Qué decirle» va escrito para ella, en palabras sencillas.</t>
         </is>
       </c>
       <c r="G900" s="13" t="inlineStr"/>
@@ -46198,7 +46198,7 @@
       </c>
       <c r="D901" s="15" t="inlineStr">
         <is>
-          <t>Ayuda</t>
+          <t>Pregunta</t>
         </is>
       </c>
       <c r="E901" s="15" t="inlineStr">
@@ -46208,7 +46208,7 @@
       </c>
       <c r="F901" s="15" t="inlineStr">
         <is>
-          <t>La CURP, el nombre (al menos 3 letras), el folio de su solicitud (APD-S-…) o su número de expediente (EXP-…).</t>
+          <t>CURP, nombre o folio</t>
         </is>
       </c>
       <c r="G901" s="13" t="inlineStr"/>
@@ -46248,7 +46248,7 @@
       </c>
       <c r="D902" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Ayuda</t>
         </is>
       </c>
       <c r="E902" s="12" t="inlineStr">
@@ -46258,7 +46258,7 @@
       </c>
       <c r="F902" s="12" t="inlineStr">
         <is>
-          <t>Escriba para buscar.</t>
+          <t>La CURP, el nombre (al menos 3 letras), el folio de su solicitud (APD-S-…) o su número de expediente (EXP-…).</t>
         </is>
       </c>
       <c r="G902" s="13" t="inlineStr"/>
@@ -46288,27 +46288,27 @@
       </c>
       <c r="B903" s="15" t="inlineStr">
         <is>
-          <t>Reposición de tu credencial</t>
+          <t>Consultar un trámite (personal)</t>
         </is>
       </c>
       <c r="C903" s="15" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Consultar un trámite</t>
         </is>
       </c>
       <c r="D903" s="15" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E903" s="15" t="inlineStr">
         <is>
-          <t>Al pedirla o al cargar el acta corregida</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F903" s="15" t="inlineStr">
         <is>
-          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
+          <t>Escriba para buscar.</t>
         </is>
       </c>
       <c r="G903" s="13" t="inlineStr"/>
@@ -46321,12 +46321,12 @@
       <c r="J903" s="15" t="inlineStr"/>
       <c r="K903" s="16" t="inlineStr">
         <is>
-          <t>Persona solicitante</t>
+          <t>Personal de la Secretaría</t>
         </is>
       </c>
       <c r="L903" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/reposicion.js)</t>
+          <t>Página (sitio/ventanilla.html)</t>
         </is>
       </c>
     </row>
@@ -46348,17 +46348,17 @@
       </c>
       <c r="D904" s="12" t="inlineStr">
         <is>
-          <t>Pasos</t>
+          <t>Título</t>
         </is>
       </c>
       <c r="E904" s="12" t="inlineStr">
         <is>
-          <t>Al pedirla</t>
+          <t>Al pedirla o al cargar el acta corregida</t>
         </is>
       </c>
       <c r="F904" s="12" t="inlineStr">
         <is>
-          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
+          <t>Recibimos tu solicitud de reposición · Recibimos tu acta corregida</t>
         </is>
       </c>
       <c r="G904" s="13" t="inlineStr"/>
@@ -46393,22 +46393,22 @@
       </c>
       <c r="C905" s="15" t="inlineStr">
         <is>
-          <t>Acreditación</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="D905" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Pasos</t>
         </is>
       </c>
       <c r="E905" s="15" t="inlineStr">
         <is>
-          <t>Credencial del sistema que todavía no se entrega</t>
+          <t>Al pedirla</t>
         </is>
       </c>
       <c r="F905" s="15" t="inlineStr">
         <is>
-          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
+          <t>La Secretaría revisa tu acta. · Te indica en «Mis trámites» si debes corregir algo o, si está completa, cuánto pagar. · Pagas la cuota de reposición y recoges tu credencial en la oficina del Vivero Nezahualcóyotl, con el mismo número y la misma vigencia.</t>
         </is>
       </c>
       <c r="G905" s="13" t="inlineStr"/>
@@ -46438,27 +46438,27 @@
       </c>
       <c r="B906" s="12" t="inlineStr">
         <is>
-          <t>Grupos (personal)</t>
+          <t>Reposición de tu credencial</t>
         </is>
       </c>
       <c r="C906" s="12" t="inlineStr">
         <is>
-          <t>Cabecera</t>
+          <t>Acreditación</t>
         </is>
       </c>
       <c r="D906" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E906" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Credencial del sistema que todavía no se entrega</t>
         </is>
       </c>
       <c r="F906" s="12" t="inlineStr">
         <is>
-          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
+          <t>Tu credencial todavía no se te entrega: recógela en la oficina del Vivero. La reposición es para una credencial que ya recibiste y perdiste o te robaron.</t>
         </is>
       </c>
       <c r="G906" s="13" t="inlineStr"/>
@@ -46471,12 +46471,12 @@
       <c r="J906" s="12" t="inlineStr"/>
       <c r="K906" s="14" t="inlineStr">
         <is>
-          <t>Personal de la Secretaría</t>
+          <t>Persona solicitante</t>
         </is>
       </c>
       <c r="L906" s="14" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/grupos.js)</t>
+          <t>Código del sitio (sitio/app/reposicion.js)</t>
         </is>
       </c>
     </row>
@@ -46493,7 +46493,7 @@
       </c>
       <c r="C907" s="15" t="inlineStr">
         <is>
-          <t>Paso 1 · el curso</t>
+          <t>Cabecera</t>
         </is>
       </c>
       <c r="D907" s="15" t="inlineStr">
@@ -46503,12 +46503,12 @@
       </c>
       <c r="E907" s="15" t="inlineStr">
         <is>
-          <t>En cada curso</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F907" s="15" t="inlineStr">
         <is>
-          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
+          <t>Hoy es DÍA N de MES de AAAA. Arme un grupo en cuatro pasos: el curso, la semana, quiénes van y confirmar.</t>
         </is>
       </c>
       <c r="G907" s="13" t="inlineStr"/>
@@ -46543,7 +46543,7 @@
       </c>
       <c r="C908" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · la semana</t>
+          <t>Paso 1 · el curso</t>
         </is>
       </c>
       <c r="D908" s="12" t="inlineStr">
@@ -46553,12 +46553,12 @@
       </c>
       <c r="E908" s="12" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>En cada curso</t>
         </is>
       </c>
       <c r="F908" s="12" t="inlineStr">
         <is>
-          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
+          <t>N personas en espera · N esperan 15 días o más · N ya vencidas · Falta gente para un grupo (mínimo 5) / Alcanza para N grupos nuevos de hasta 25 / Nadie espera por ahora</t>
         </is>
       </c>
       <c r="G908" s="13" t="inlineStr"/>
@@ -46593,22 +46593,22 @@
       </c>
       <c r="C909" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · columna «Semana»</t>
+          <t>Paso 2 · la semana</t>
         </is>
       </c>
       <c r="D909" s="15" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E909" s="15" t="inlineStr">
         <is>
-          <t>Semana que se puede elegir</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F909" s="15" t="inlineStr">
         <is>
-          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
+          <t>CURSO · lunes a viernes, de 9:00 a 15:00 (o «un día, de 9:00 a 15:00»). Puede haber 2 grupos al mismo tiempo, de cualquier curso; el curso empieza al menos 7 días después de confirmarlo.</t>
         </is>
       </c>
       <c r="G909" s="13" t="inlineStr"/>
@@ -46648,17 +46648,17 @@
       </c>
       <c r="D910" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E910" s="12" t="inlineStr">
         <is>
-          <t>Semana que no se puede elegir</t>
+          <t>Semana que se puede elegir</t>
         </is>
       </c>
       <c r="F910" s="12" t="inlineStr">
         <is>
-          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
+          <t>Libre · 2 lugares libres / 1 lugar libre de 2 (elegida: «Elegida»). Nombre para el lector: «Elegir la semana del 2 al 6 de noviembre de 2026: 2 lugares libres»</t>
         </is>
       </c>
       <c r="G910" s="13" t="inlineStr"/>
@@ -46693,22 +46693,22 @@
       </c>
       <c r="C911" s="15" t="inlineStr">
         <is>
-          <t>Paso 2 · calendario</t>
+          <t>Paso 2 · columna «Semana»</t>
         </is>
       </c>
       <c r="D911" s="15" t="inlineStr">
         <is>
-          <t>Etiqueta</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E911" s="15" t="inlineStr">
         <is>
-          <t>En los días</t>
+          <t>Semana que no se puede elegir</t>
         </is>
       </c>
       <c r="F911" s="15" t="inlineStr">
         <is>
-          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
+          <t>No disponible · Ya pasó / Ya empezó / Faltan menos de 7 días / Ya hay 2 grupos / Día inhábil / Falta más de un año</t>
         </is>
       </c>
       <c r="G911" s="13" t="inlineStr"/>
@@ -46743,22 +46743,22 @@
       </c>
       <c r="C912" s="12" t="inlineStr">
         <is>
-          <t>Paso 2 · semana elegida</t>
+          <t>Paso 2 · calendario</t>
         </is>
       </c>
       <c r="D912" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Etiqueta</t>
         </is>
       </c>
       <c r="E912" s="12" t="inlineStr">
         <is>
-          <t>Con una semana elegida</t>
+          <t>En los días</t>
         </is>
       </c>
       <c r="F912" s="12" t="inlineStr">
         <is>
-          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
+          <t>G-AAAA-NNN (folio, el primer día) · Examen (el último) · Nuevo grupo (la semana elegida) · Hoy · Inhábil</t>
         </is>
       </c>
       <c r="G912" s="13" t="inlineStr"/>
@@ -46803,12 +46803,12 @@
       </c>
       <c r="E913" s="15" t="inlineStr">
         <is>
-          <t>Sin semana</t>
+          <t>Con una semana elegida</t>
         </is>
       </c>
       <c r="F913" s="15" t="inlineStr">
         <is>
-          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
+          <t>Del 2 al 6 de noviembre · Del lunes 2 de noviembre de 2026 al viernes 6 de noviembre de 2026, de 9:00 a 15:00. El viernes, repaso de conocimientos y examen final en el PILARES. (Curso de un día: «El DÍA…, de 9:00 a 15:00, con el examen ese mismo día en el PILARES».)</t>
         </is>
       </c>
       <c r="G913" s="13" t="inlineStr"/>
@@ -46843,22 +46843,22 @@
       </c>
       <c r="C914" s="12" t="inlineStr">
         <is>
-          <t>Paso 2</t>
+          <t>Paso 2 · semana elegida</t>
         </is>
       </c>
       <c r="D914" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E914" s="12" t="inlineStr">
         <is>
-          <t>Siguiente sin semana</t>
+          <t>Sin semana</t>
         </is>
       </c>
       <c r="F914" s="12" t="inlineStr">
         <is>
-          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
+          <t>Ninguna todavía · Toque «Libre» en la semana que quiere. (Grupo que ya existe: «Sin semana todavía · … o siga sin semana: el grupo la conserva como está».)</t>
         </is>
       </c>
       <c r="G914" s="13" t="inlineStr"/>
@@ -46898,17 +46898,17 @@
       </c>
       <c r="D915" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E915" s="15" t="inlineStr">
         <is>
-          <t>Al tocar un día que no se puede</t>
+          <t>Siguiente sin semana</t>
         </is>
       </c>
       <c r="F915" s="15" t="inlineStr">
         <is>
-          <t>El DÍA no se puede: RAZÓN.</t>
+          <t>Elija una semana libre en el calendario: toque «Libre» en la semana que quiere.</t>
         </is>
       </c>
       <c r="G915" s="13" t="inlineStr"/>
@@ -46943,22 +46943,22 @@
       </c>
       <c r="C916" s="12" t="inlineStr">
         <is>
-          <t>Paso 3 · quiénes van</t>
+          <t>Paso 2</t>
         </is>
       </c>
       <c r="D916" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E916" s="12" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Al tocar un día que no se puede</t>
         </is>
       </c>
       <c r="F916" s="12" t="inlineStr">
         <is>
-          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
+          <t>El DÍA no se puede: RAZÓN.</t>
         </is>
       </c>
       <c r="G916" s="13" t="inlineStr"/>
@@ -47003,12 +47003,12 @@
       </c>
       <c r="E917" s="15" t="inlineStr">
         <is>
-          <t>Siempre</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F917" s="15" t="inlineStr">
         <is>
-          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
+          <t>Se proponen las N personas que más esperan, primero las prioritarias y las de una misma institución de gobierno juntas. Quite o agregue a quien haga falta.</t>
         </is>
       </c>
       <c r="G917" s="13" t="inlineStr"/>
@@ -47048,17 +47048,17 @@
       </c>
       <c r="D918" s="12" t="inlineStr">
         <is>
-          <t>Plegable</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E918" s="12" t="inlineStr">
         <is>
-          <t>Con más en espera que las propuestas</t>
+          <t>Siempre</t>
         </is>
       </c>
       <c r="F918" s="12" t="inlineStr">
         <is>
-          <t>Cambiar a quiénes van (N más en espera)</t>
+          <t>N de 25 lugares · se confirma con al menos 5 personas</t>
         </is>
       </c>
       <c r="G918" s="13" t="inlineStr"/>
@@ -47093,22 +47093,22 @@
       </c>
       <c r="C919" s="15" t="inlineStr">
         <is>
-          <t>Paso 3</t>
+          <t>Paso 3 · quiénes van</t>
         </is>
       </c>
       <c r="D919" s="15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Plegable</t>
         </is>
       </c>
       <c r="E919" s="15" t="inlineStr">
         <is>
-          <t>Siguiente sin nadie</t>
+          <t>Con más en espera que las propuestas</t>
         </is>
       </c>
       <c r="F919" s="15" t="inlineStr">
         <is>
-          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
+          <t>Cambiar a quiénes van (N más en espera)</t>
         </is>
       </c>
       <c r="G919" s="13" t="inlineStr"/>
@@ -47143,22 +47143,22 @@
       </c>
       <c r="C920" s="12" t="inlineStr">
         <is>
-          <t>Paso 4 · confirmar</t>
+          <t>Paso 3</t>
         </is>
       </c>
       <c r="D920" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E920" s="12" t="inlineStr">
         <is>
-          <t>Antes de crearlo</t>
+          <t>Siguiente sin nadie</t>
         </is>
       </c>
       <c r="F920" s="12" t="inlineStr">
         <is>
-          <t>Se crea por confirmar / Sigue por confirmar · Le falta: …; después, el área de Instructores y Capacitación le asigna la persona instructora y lo confirma. Lo puede completar en «Grupos programados» o en su ficha; mientras, las personas no ven la fecha como segura.</t>
+          <t>Elija a quién va · Marque la casilla junto al nombre de al menos una persona. El grupo se confirma con al menos 5.</t>
         </is>
       </c>
       <c r="G920" s="13" t="inlineStr"/>
@@ -47198,17 +47198,17 @@
       </c>
       <c r="D921" s="15" t="inlineStr">
         <is>
-          <t>Botón</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E921" s="15" t="inlineStr">
         <is>
-          <t>Grupo nuevo</t>
+          <t>Antes de crearlo</t>
         </is>
       </c>
       <c r="F921" s="15" t="inlineStr">
         <is>
-          <t>Crear el grupo</t>
+          <t>Se crea por confirmar / Sigue por confirmar · Le falta: …; después, el área de Instructores y Capacitación le asigna la persona instructora y lo confirma. Lo puede completar en «Grupos programados» o en su ficha; mientras, las personas no ven la fecha como segura.</t>
         </is>
       </c>
       <c r="G921" s="13" t="inlineStr"/>
@@ -47253,12 +47253,12 @@
       </c>
       <c r="E922" s="12" t="inlineStr">
         <is>
-          <t>Grupo que ya existe</t>
+          <t>Grupo nuevo</t>
         </is>
       </c>
       <c r="F922" s="12" t="inlineStr">
         <is>
-          <t>Guardar los cambios / Agregar al grupo (confirmado)</t>
+          <t>Crear el grupo</t>
         </is>
       </c>
       <c r="G922" s="13" t="inlineStr"/>
@@ -47293,22 +47293,22 @@
       </c>
       <c r="C923" s="15" t="inlineStr">
         <is>
-          <t>Paso 4 · resumen</t>
+          <t>Paso 4 · confirmar</t>
         </is>
       </c>
       <c r="D923" s="15" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Botón</t>
         </is>
       </c>
       <c r="E923" s="15" t="inlineStr">
         <is>
-          <t>Grupo sin persona instructora</t>
+          <t>Grupo que ya existe</t>
         </is>
       </c>
       <c r="F923" s="15" t="inlineStr">
         <is>
-          <t>Persona instructora · La asigna el área de Instructores y Capacitación</t>
+          <t>Guardar los cambios / Agregar al grupo (confirmado)</t>
         </is>
       </c>
       <c r="G923" s="13" t="inlineStr"/>
@@ -47343,22 +47343,22 @@
       </c>
       <c r="C924" s="12" t="inlineStr">
         <is>
-          <t>Paso 1 · tipo de grupo</t>
+          <t>Paso 4 · resumen</t>
         </is>
       </c>
       <c r="D924" s="12" t="inlineStr">
         <is>
-          <t>Ayuda (cambia)</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E924" s="12" t="inlineStr">
         <is>
-          <t>Elegidas de una organización que no es de gobierno</t>
+          <t>Grupo sin persona instructora</t>
         </is>
       </c>
       <c r="F924" s="12" t="inlineStr">
         <is>
-          <t>NOMBRE no es una institución de gobierno: su gente va a un grupo combinado. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio.</t>
+          <t>Persona instructora · La asigna el área de Instructores y Capacitación</t>
         </is>
       </c>
       <c r="G924" s="13" t="inlineStr"/>
@@ -47403,12 +47403,12 @@
       </c>
       <c r="E925" s="15" t="inlineStr">
         <is>
-          <t>Elegidas de varias organizaciones o independientes</t>
+          <t>Elegidas de una organización que no es de gobierno</t>
         </is>
       </c>
       <c r="F925" s="15" t="inlineStr">
         <is>
-          <t>El grupo es combinado: las elegidas son de varias organizaciones o independientes. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio, con toda su gente.</t>
+          <t>NOMBRE no es una institución de gobierno: su gente va a un grupo combinado. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio.</t>
         </is>
       </c>
       <c r="G925" s="13" t="inlineStr"/>
@@ -47443,22 +47443,22 @@
       </c>
       <c r="C926" s="12" t="inlineStr">
         <is>
-          <t>Paso 4</t>
+          <t>Paso 1 · tipo de grupo</t>
         </is>
       </c>
       <c r="D926" s="12" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Ayuda (cambia)</t>
         </is>
       </c>
       <c r="E926" s="12" t="inlineStr">
         <is>
-          <t>Grupo propio de quien no es de gobierno</t>
+          <t>Elegidas de varias organizaciones o independientes</t>
         </is>
       </c>
       <c r="F926" s="12" t="inlineStr">
         <is>
-          <t>Un grupo propio es sólo de una institución de gobierno, con toda su gente. Elija «Combinado» o quite a quien no sea de esa institución.</t>
+          <t>El grupo es combinado: las elegidas son de varias organizaciones o independientes. Sólo las dependencias de la Ciudad, las Alcaldías y las dependencias federales tienen grupo propio, con toda su gente.</t>
         </is>
       </c>
       <c r="G926" s="13" t="inlineStr"/>
@@ -47493,22 +47493,22 @@
       </c>
       <c r="C927" s="15" t="inlineStr">
         <is>
-          <t>Grupos programados</t>
+          <t>Paso 4</t>
         </is>
       </c>
       <c r="D927" s="15" t="inlineStr">
         <is>
-          <t>Aviso</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E927" s="15" t="inlineStr">
         <is>
-          <t>Al crear un grupo</t>
+          <t>Grupo propio de quien no es de gobierno</t>
         </is>
       </c>
       <c r="F927" s="15" t="inlineStr">
         <is>
-          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
+          <t>Un grupo propio es sólo de una institución de gobierno, con toda su gente. Elija «Combinado» o quite a quien no sea de esa institución.</t>
         </is>
       </c>
       <c r="G927" s="13" t="inlineStr"/>
@@ -47548,17 +47548,17 @@
       </c>
       <c r="D928" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Aviso</t>
         </is>
       </c>
       <c r="E928" s="12" t="inlineStr">
         <is>
-          <t>Situación de cada grupo</t>
+          <t>Al crear un grupo</t>
         </is>
       </c>
       <c r="F928" s="12" t="inlineStr">
         <is>
-          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
+          <t>Grupo creado y confirmado: NOMBRE / Grupo creado, por confirmar: NOMBRE · FOLIO · N personas · entrada a las 09:00 · INSTRUCTOR. · Ver la ficha del grupo · Qué sigue</t>
         </is>
       </c>
       <c r="G928" s="13" t="inlineStr"/>
@@ -47598,17 +47598,17 @@
       </c>
       <c r="D929" s="15" t="inlineStr">
         <is>
-          <t>Botón o enlace</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E929" s="15" t="inlineStr">
         <is>
-          <t>Acciones de cada grupo</t>
+          <t>Situación de cada grupo</t>
         </is>
       </c>
       <c r="F929" s="15" t="inlineStr">
         <is>
-          <t>Completar con las N que más esperan · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
+          <t>En curso · día N de 5 / Confirmado / Por confirmar / Sin semana / Propuesta vencida / Confirmado · no inició</t>
         </is>
       </c>
       <c r="G929" s="13" t="inlineStr"/>
@@ -47648,17 +47648,17 @@
       </c>
       <c r="D930" s="12" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Botón o enlace</t>
         </is>
       </c>
       <c r="E930" s="12" t="inlineStr">
         <is>
-          <t>Lo que falta</t>
+          <t>Acciones de cada grupo</t>
         </is>
       </c>
       <c r="F930" s="12" t="inlineStr">
         <is>
-          <t>Semana, N personas, hora y persona instructora / Que Capacitación lo confirme / —</t>
+          <t>Completar con las N que más esperan · Elegir semana / Cambiar la semana / Elegir otra semana · Agregar personas</t>
         </is>
       </c>
       <c r="G930" s="13" t="inlineStr"/>
@@ -47688,12 +47688,12 @@
       </c>
       <c r="B931" s="15" t="inlineStr">
         <is>
-          <t>Consultar un trámite (personal)</t>
+          <t>Grupos (personal)</t>
         </is>
       </c>
       <c r="C931" s="15" t="inlineStr">
         <is>
-          <t>Búsqueda</t>
+          <t>Grupos programados</t>
         </is>
       </c>
       <c r="D931" s="15" t="inlineStr">
@@ -47703,12 +47703,12 @@
       </c>
       <c r="E931" s="15" t="inlineStr">
         <is>
-          <t>Al buscar</t>
+          <t>Lo que falta</t>
         </is>
       </c>
       <c r="F931" s="15" t="inlineStr">
         <is>
-          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
+          <t>Semana, N personas, hora y persona instructora / Que Capacitación lo confirme / —</t>
         </is>
       </c>
       <c r="G931" s="13" t="inlineStr"/>
@@ -47726,7 +47726,7 @@
       </c>
       <c r="L931" s="16" t="inlineStr">
         <is>
-          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+          <t>Código del sitio (sitio/app/grupos.js)</t>
         </is>
       </c>
     </row>
@@ -47743,22 +47743,22 @@
       </c>
       <c r="C932" s="12" t="inlineStr">
         <is>
-          <t>Ficha</t>
+          <t>Búsqueda</t>
         </is>
       </c>
       <c r="D932" s="12" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Texto</t>
         </is>
       </c>
       <c r="E932" s="12" t="inlineStr">
         <is>
-          <t>Según la cuenta</t>
+          <t>Al buscar</t>
         </is>
       </c>
       <c r="F932" s="12" t="inlineStr">
         <is>
-          <t>Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
+          <t>Escriba al menos 3 caracteres para buscar. / N personas encontradas. / Nadie coincide con la búsqueda. Revise lo que escribió.</t>
         </is>
       </c>
       <c r="G932" s="13" t="inlineStr"/>
@@ -47793,22 +47793,22 @@
       </c>
       <c r="C933" s="15" t="inlineStr">
         <is>
-          <t>Ficha · Qué decirle (de tú)</t>
+          <t>Ficha</t>
         </is>
       </c>
       <c r="D933" s="15" t="inlineStr">
         <is>
-          <t>Texto</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="E933" s="15" t="inlineStr">
         <is>
-          <t>Según el estado</t>
+          <t>Según la cuenta</t>
         </is>
       </c>
       <c r="F933" s="15" t="inlineStr">
         <is>
-          <t>Tu solicitud todavía no se envía: termina de cargar tus documentos y envíala desde «Mis trámites». / La Secretaría está revisando tus documentos. Si falta algo, te avisamos por correo y lo ves en «Mis trámites»; si todo está completo, te damos una cita de cotejo. / A tu solicitud le falta corregir un documento: … Corrígelos en línea, en «Mis trámites», y vuelve a enviar tu solicitud. Hay un plazo para corregir. Te quedan N oportunidades para corregir. (o: Esta es tu última oportunidad para corregir. …) / Tu solicitud se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva en línea. / Tu cita está en pausa: carga hoy en «Mis trámites» el documento que no coincidió (…). / Tu cita de cotejo es el … / Tu curso empieza el … Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Tu cotejo terminó. Estás en espera de un grupo del curso: te avisamos las fechas por correo y en «Mis trámites». (y los «qué sigue» de «Mis trámites»)</t>
+          <t>Registro anterior · sin cuenta en línea / Cuenta bloqueada / Cuenta en línea</t>
         </is>
       </c>
       <c r="G933" s="13" t="inlineStr"/>
@@ -47830,9 +47830,59 @@
         </is>
       </c>
     </row>
+    <row r="934">
+      <c r="A934" s="12" t="inlineStr">
+        <is>
+          <t>T933</t>
+        </is>
+      </c>
+      <c r="B934" s="12" t="inlineStr">
+        <is>
+          <t>Consultar un trámite (personal)</t>
+        </is>
+      </c>
+      <c r="C934" s="12" t="inlineStr">
+        <is>
+          <t>Ficha · Qué decirle (de tú)</t>
+        </is>
+      </c>
+      <c r="D934" s="12" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="E934" s="12" t="inlineStr">
+        <is>
+          <t>Según el estado</t>
+        </is>
+      </c>
+      <c r="F934" s="12" t="inlineStr">
+        <is>
+          <t>Tu solicitud todavía no se envía: termina de cargar tus documentos y envíala desde «Mis trámites». / La Secretaría está revisando tus documentos. Si falta algo, te avisamos por correo y lo ves en «Mis trámites»; si todo está completo, te damos una cita de cotejo. / A tu solicitud le falta corregir un documento: … Corrígelos en línea, en «Mis trámites», y vuelve a enviar tu solicitud. Hay un plazo para corregir. Te quedan N oportunidades para corregir. (o: Esta es tu última oportunidad para corregir. …) / Tu solicitud se cerró porque, después de tu última oportunidad para corregir, tus documentos siguieron con observaciones. No pagaste nada y puedes iniciar una solicitud nueva en línea. / Tu cita está en pausa: carga hoy en «Mis trámites» el documento que no coincidió (…). / Tu cita de cotejo es el … / Tu curso empieza el … Son 5 días, de lunes a viernes; el día 5 es de repaso de conocimientos y examen final. / Tu cotejo terminó. Estás en espera de un grupo del curso: te avisamos las fechas por correo y en «Mis trámites». (y los «qué sigue» de «Mis trámites»)</t>
+        </is>
+      </c>
+      <c r="G934" s="13" t="inlineStr"/>
+      <c r="H934" s="13" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I934" s="13" t="inlineStr"/>
+      <c r="J934" s="12" t="inlineStr"/>
+      <c r="K934" s="14" t="inlineStr">
+        <is>
+          <t>Personal de la Secretaría</t>
+        </is>
+      </c>
+      <c r="L934" s="14" t="inlineStr">
+        <is>
+          <t>Código del sitio (sitio/app/ventanilla.js)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L933"/>
-  <conditionalFormatting sqref="H2:H933">
+  <autoFilter ref="A1:L934"/>
+  <conditionalFormatting sqref="H2:H934">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -47846,13 +47896,13 @@
       <formula>"Duda"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G933">
+  <conditionalFormatting sqref="G2:G934">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(LEN(G2)&gt;0,H2="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H933" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
+    <dataValidation sqref="H2:H934" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Estado" error="Elige: Pendiente, OK, Cambiar, Quitar o Duda." type="list">
       <formula1>"Pendiente,OK,Cambiar,Quitar,Duda"</formula1>
     </dataValidation>
   </dataValidations>
